--- a/document/編集機能_結合テスト仕様書.xlsx
+++ b/document/編集機能_結合テスト仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66415D45-5132-4ABF-AAF6-4BCD7E2436F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9DE562-2512-46C5-BD7C-C4D201B09329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="888" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="389">
   <si>
     <t>作成者</t>
   </si>
@@ -1793,7 +1793,881 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>エラーメッセージ「編集するタスクを選択してください。」が赤文字で表示されている</t>
+    <t>エラーメッセージ「必須項目を入力してください」が赤文字で表示されている</t>
+    <rPh sb="9" eb="11">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の50文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>編集実行ボタンを押下する</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンシュウジッコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名：01234567890123456789012345678901234567890123456789</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・タスク編集完了画面が表示されている
+・表示されているタスク名が「01234567890123456789012345678901234567890123456789」になっている</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入力観点</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクカンテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の51文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の52文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の53文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の54文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の55文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の56文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の57文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の58文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の59文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の60文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の61文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の62文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の63文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の64文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の65文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の66文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の67文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の68文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の69文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の70文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の71文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の72文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の73文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の74文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の75文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の76文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の77文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の78文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の79文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の80文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の81文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の82文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の83文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の84文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の85文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の86文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の87文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の88文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の89文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の90文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の91文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の92文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク名に最大入力文字数の93文字を入力する</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>ニュウリョクモジスウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2245,9 +3119,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2257,20 +3128,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2281,17 +3152,23 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2305,14 +3182,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2320,32 +3194,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2707,7 +3581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S230"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.875" style="4" customWidth="1"/>
@@ -2720,16 +3594,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65" t="s">
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="48" t="s">
         <v>301</v>
       </c>
       <c r="G1" s="66"/>
@@ -2738,31 +3612,31 @@
       <c r="J1" s="66"/>
       <c r="K1" s="66"/>
       <c r="L1" s="66"/>
-      <c r="M1" s="67"/>
+      <c r="M1" s="49"/>
       <c r="N1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="65" t="s">
+      <c r="O1" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="67"/>
+      <c r="P1" s="49"/>
       <c r="Q1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="65" t="s">
+      <c r="R1" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="67"/>
+      <c r="S1" s="49"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="65" t="s">
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="48" t="s">
         <v>303</v>
       </c>
       <c r="G2" s="66"/>
@@ -2771,19 +3645,19 @@
       <c r="J2" s="66"/>
       <c r="K2" s="66"/>
       <c r="L2" s="66"/>
-      <c r="M2" s="67"/>
+      <c r="M2" s="49"/>
       <c r="N2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77">
+      <c r="O2" s="50">
         <v>46201</v>
       </c>
-      <c r="P2" s="78"/>
+      <c r="P2" s="51"/>
       <c r="Q2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="75"/>
-      <c r="S2" s="76"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="71"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="5"/>
@@ -2813,51 +3687,51 @@
       <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="54" t="s">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="54" t="s">
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="55"/>
-      <c r="P4" s="56"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="55"/>
       <c r="Q4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="54" t="s">
+      <c r="R4" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="56"/>
+      <c r="S4" s="55"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="74"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="58"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="68"/>
       <c r="S5" s="69"/>
@@ -2869,318 +3743,318 @@
       <c r="B6" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50" t="s">
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67" t="s">
         <v>310</v>
       </c>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="51" t="s">
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="59" t="s">
         <v>318</v>
       </c>
-      <c r="O6" s="52"/>
-      <c r="P6" s="53"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="61"/>
       <c r="Q6" s="11"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
     </row>
     <row r="7" spans="1:19" ht="57" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50" t="s">
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67" t="s">
         <v>311</v>
       </c>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="51" t="s">
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="59" t="s">
         <v>319</v>
       </c>
-      <c r="O7" s="52"/>
-      <c r="P7" s="53"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="61"/>
       <c r="Q7" s="11"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
     </row>
     <row r="8" spans="1:19" ht="99.6" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
       <c r="N8" s="42"/>
       <c r="O8" s="43"/>
       <c r="P8" s="44"/>
       <c r="Q8" s="10"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="52"/>
     </row>
     <row r="9" spans="1:19" ht="36.6" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49" t="s">
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75" t="s">
         <v>312</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="51" t="s">
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="59" t="s">
         <v>320</v>
       </c>
       <c r="O9" s="43"/>
       <c r="P9" s="44"/>
       <c r="Q9" s="11"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
     </row>
     <row r="10" spans="1:19" ht="130.15" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="50" t="s">
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="67" t="s">
         <v>313</v>
       </c>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="51" t="s">
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="59" t="s">
         <v>321</v>
       </c>
       <c r="O10" s="43"/>
       <c r="P10" s="44"/>
       <c r="Q10" s="10"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="48"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="47"/>
       <c r="N11" s="42"/>
       <c r="O11" s="43"/>
       <c r="P11" s="44"/>
       <c r="Q11" s="11"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="75" t="s">
         <v>314</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="48"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="47"/>
       <c r="N12" s="42"/>
       <c r="O12" s="43"/>
       <c r="P12" s="44"/>
       <c r="Q12" s="10"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
     </row>
     <row r="13" spans="1:19" ht="61.15" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="75" t="s">
         <v>316</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="46" t="s">
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="45" t="s">
         <v>317</v>
       </c>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="51" t="s">
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="59" t="s">
         <v>322</v>
       </c>
       <c r="O13" s="43"/>
       <c r="P13" s="44"/>
       <c r="Q13" s="10"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="75" t="s">
         <v>323</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="46" t="s">
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="45" t="s">
         <v>324</v>
       </c>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="48"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
       <c r="N14" s="42" t="s">
         <v>325</v>
       </c>
       <c r="O14" s="43"/>
       <c r="P14" s="44"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="48"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="47"/>
       <c r="N15" s="42"/>
       <c r="O15" s="43"/>
       <c r="P15" s="44"/>
       <c r="Q15" s="10"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
+      <c r="R15" s="52"/>
+      <c r="S15" s="52"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="10">
         <v>2</v>
       </c>
       <c r="B16" s="10"/>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="75" t="s">
         <v>326</v>
       </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="48"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="47"/>
       <c r="N16" s="42"/>
       <c r="O16" s="43"/>
       <c r="P16" s="44"/>
       <c r="Q16" s="10"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
+      <c r="R16" s="52"/>
+      <c r="S16" s="52"/>
     </row>
     <row r="17" spans="1:19" ht="50.45" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="75" t="s">
         <v>327</v>
       </c>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="58" t="s">
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="72" t="s">
         <v>328</v>
       </c>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="51" t="s">
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="59" t="s">
         <v>329</v>
       </c>
-      <c r="O17" s="52"/>
-      <c r="P17" s="53"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="61"/>
       <c r="Q17" s="10"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="52"/>
     </row>
     <row r="18" spans="1:19" ht="50.45" customHeight="1">
       <c r="A18" s="10"/>
@@ -3200,21 +4074,21 @@
       <c r="O18" s="37"/>
       <c r="P18" s="38"/>
       <c r="Q18" s="10"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
+      <c r="R18" s="52"/>
+      <c r="S18" s="52"/>
     </row>
     <row r="19" spans="1:19" ht="50.45" customHeight="1">
       <c r="A19" s="10">
         <v>3</v>
       </c>
       <c r="B19" s="10"/>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
       <c r="J19" s="40"/>
@@ -3225,888 +4099,5260 @@
       <c r="O19" s="37"/>
       <c r="P19" s="38"/>
       <c r="Q19" s="10"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="52"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="48"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="47"/>
       <c r="N20" s="42"/>
       <c r="O20" s="43"/>
       <c r="P20" s="44"/>
       <c r="Q20" s="10"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="52"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="48"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="47"/>
       <c r="N21" s="42"/>
       <c r="O21" s="43"/>
       <c r="P21" s="44"/>
       <c r="Q21" s="10"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="48"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="47"/>
       <c r="N22" s="42"/>
       <c r="O22" s="43"/>
       <c r="P22" s="44"/>
       <c r="Q22" s="10"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
     </row>
     <row r="23" spans="1:19" ht="15.75">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="48"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="47"/>
       <c r="N23" s="42"/>
       <c r="O23" s="43"/>
       <c r="P23" s="44"/>
       <c r="Q23" s="10"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="52"/>
     </row>
     <row r="24" spans="1:19" ht="62.45" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="75" t="s">
         <v>332</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="46" t="s">
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="45" t="s">
         <v>333</v>
       </c>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="48"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="47"/>
       <c r="N24" s="42" t="s">
         <v>334</v>
       </c>
       <c r="O24" s="43"/>
       <c r="P24" s="44"/>
       <c r="Q24" s="10"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="52"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="48"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="47"/>
       <c r="N25" s="42"/>
       <c r="O25" s="43"/>
       <c r="P25" s="44"/>
       <c r="Q25" s="10"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="71"/>
+      <c r="R25" s="77"/>
+      <c r="S25" s="78"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="10">
         <v>4</v>
       </c>
       <c r="B26" s="10"/>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="48"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="47"/>
       <c r="N26" s="42"/>
       <c r="O26" s="43"/>
       <c r="P26" s="44"/>
       <c r="Q26" s="10"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="52"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="48"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="47"/>
       <c r="N27" s="42"/>
       <c r="O27" s="43"/>
       <c r="P27" s="44"/>
       <c r="Q27" s="10"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
     </row>
     <row r="28" spans="1:19" ht="108.6" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="48"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="47"/>
       <c r="N28" s="42"/>
       <c r="O28" s="43"/>
       <c r="P28" s="44"/>
       <c r="Q28" s="10"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="52"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="48"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="47"/>
       <c r="N29" s="42"/>
       <c r="O29" s="43"/>
       <c r="P29" s="44"/>
       <c r="Q29" s="10"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="48"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="47"/>
       <c r="N30" s="42"/>
       <c r="O30" s="43"/>
       <c r="P30" s="44"/>
       <c r="Q30" s="10"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="45" t="s">
         <v>330</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="48"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="47"/>
       <c r="N31" s="42"/>
       <c r="O31" s="43"/>
       <c r="P31" s="44"/>
       <c r="Q31" s="10"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="52"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="45" t="s">
         <v>331</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="46" t="s">
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="47"/>
-      <c r="M32" s="48"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="47"/>
       <c r="N32" s="42" t="s">
         <v>336</v>
       </c>
       <c r="O32" s="43"/>
       <c r="P32" s="44"/>
       <c r="Q32" s="10"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="48"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="47"/>
       <c r="N33" s="42"/>
       <c r="O33" s="43"/>
       <c r="P33" s="44"/>
       <c r="Q33" s="10"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="52"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="10">
         <v>5</v>
       </c>
       <c r="B34" s="10"/>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="48"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="47"/>
       <c r="N34" s="42"/>
       <c r="O34" s="43"/>
       <c r="P34" s="44"/>
       <c r="Q34" s="10"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
+      <c r="R34" s="52"/>
+      <c r="S34" s="52"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="67" t="s">
         <v>306</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="48"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="47"/>
       <c r="N35" s="42"/>
       <c r="O35" s="43"/>
       <c r="P35" s="44"/>
       <c r="Q35" s="10"/>
-      <c r="R35" s="45"/>
-      <c r="S35" s="45"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
     </row>
     <row r="36" spans="1:19" ht="97.15" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="48"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="47"/>
       <c r="N36" s="42"/>
       <c r="O36" s="43"/>
       <c r="P36" s="44"/>
       <c r="Q36" s="10"/>
-      <c r="R36" s="45"/>
-      <c r="S36" s="45"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="67" t="s">
         <v>309</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="47"/>
-      <c r="K37" s="47"/>
-      <c r="L37" s="47"/>
-      <c r="M37" s="48"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="47"/>
       <c r="N37" s="42"/>
       <c r="O37" s="43"/>
       <c r="P37" s="44"/>
       <c r="Q37" s="10"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="49" t="s">
+      <c r="C38" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
-      <c r="M38" s="48"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="47"/>
       <c r="N38" s="42"/>
       <c r="O38" s="43"/>
       <c r="P38" s="44"/>
       <c r="Q38" s="10"/>
-      <c r="R38" s="45"/>
-      <c r="S38" s="45"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
-      <c r="C39" s="46" t="s">
+      <c r="C39" s="45" t="s">
         <v>337</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="48"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="47"/>
       <c r="N39" s="42"/>
       <c r="O39" s="43"/>
       <c r="P39" s="44"/>
       <c r="Q39" s="10"/>
-      <c r="R39" s="45"/>
-      <c r="S39" s="45"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="46" t="s">
+      <c r="B40" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C40" s="45" t="s">
         <v>338</v>
       </c>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="58" t="s">
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="72" t="s">
         <v>339</v>
       </c>
-      <c r="I40" s="59"/>
-      <c r="J40" s="59"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="59"/>
-      <c r="M40" s="60"/>
-      <c r="N40" s="42" t="s">
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="73"/>
+      <c r="L40" s="73"/>
+      <c r="M40" s="74"/>
+      <c r="N40" s="59" t="s">
         <v>340</v>
       </c>
-      <c r="O40" s="43"/>
-      <c r="P40" s="44"/>
+      <c r="O40" s="60"/>
+      <c r="P40" s="61"/>
       <c r="Q40" s="10"/>
-      <c r="R40" s="45"/>
-      <c r="S40" s="45"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="47"/>
-      <c r="K41" s="47"/>
-      <c r="L41" s="47"/>
-      <c r="M41" s="48"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="47"/>
       <c r="N41" s="42"/>
       <c r="O41" s="43"/>
       <c r="P41" s="44"/>
       <c r="Q41" s="10"/>
-      <c r="R41" s="45"/>
-      <c r="S41" s="45"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="52"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
-      <c r="A42" s="10"/>
+      <c r="A42" s="10">
+        <v>6</v>
+      </c>
       <c r="B42" s="10"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="48"/>
+      <c r="C42" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
+      <c r="M42" s="47"/>
       <c r="N42" s="42"/>
       <c r="O42" s="43"/>
       <c r="P42" s="44"/>
       <c r="Q42" s="10"/>
-      <c r="R42" s="45"/>
-      <c r="S42" s="45"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="47"/>
-      <c r="M43" s="48"/>
+      <c r="C43" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="46"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="47"/>
       <c r="N43" s="42"/>
       <c r="O43" s="43"/>
       <c r="P43" s="44"/>
       <c r="Q43" s="10"/>
-      <c r="R43" s="45"/>
-      <c r="S43" s="45"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="48"/>
+      <c r="C44" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
+      <c r="F44" s="75"/>
+      <c r="G44" s="75"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
       <c r="N44" s="42"/>
       <c r="O44" s="43"/>
       <c r="P44" s="44"/>
       <c r="Q44" s="10"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="45"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="48"/>
+      <c r="C45" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="D45" s="75"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="75"/>
+      <c r="G45" s="75"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="47"/>
       <c r="N45" s="42"/>
       <c r="O45" s="43"/>
       <c r="P45" s="44"/>
       <c r="Q45" s="10"/>
-      <c r="R45" s="45"/>
-      <c r="S45" s="45"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="47"/>
-      <c r="M46" s="48"/>
+      <c r="C46" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="75"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="47"/>
       <c r="N46" s="42"/>
       <c r="O46" s="43"/>
       <c r="P46" s="44"/>
       <c r="Q46" s="10"/>
-      <c r="R46" s="45"/>
-      <c r="S46" s="45"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="52"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
-      <c r="L47" s="47"/>
-      <c r="M47" s="48"/>
+      <c r="C47" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="46"/>
+      <c r="K47" s="46"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="47"/>
       <c r="N47" s="42"/>
       <c r="O47" s="43"/>
       <c r="P47" s="44"/>
       <c r="Q47" s="10"/>
-      <c r="R47" s="45"/>
-      <c r="S47" s="45"/>
-    </row>
-    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="R47" s="52"/>
+      <c r="S47" s="52"/>
+    </row>
+    <row r="48" spans="1:19" ht="45" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
-      <c r="L48" s="47"/>
-      <c r="M48" s="48"/>
+      <c r="C48" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="46"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="47"/>
       <c r="N48" s="42"/>
       <c r="O48" s="43"/>
       <c r="P48" s="44"/>
       <c r="Q48" s="10"/>
-      <c r="R48" s="45"/>
-      <c r="S48" s="45"/>
-    </row>
-    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="R48" s="52"/>
+      <c r="S48" s="52"/>
+    </row>
+    <row r="49" spans="1:19" ht="75.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
-      <c r="M49" s="48"/>
-      <c r="N49" s="42"/>
+      <c r="B49" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
+      <c r="M49" s="47"/>
+      <c r="N49" s="59" t="s">
+        <v>344</v>
+      </c>
       <c r="O49" s="43"/>
       <c r="P49" s="44"/>
       <c r="Q49" s="10"/>
-      <c r="R49" s="45"/>
-      <c r="S49" s="45"/>
+      <c r="R49" s="52"/>
+      <c r="S49" s="52"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="47"/>
-      <c r="M50" s="48"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="46"/>
+      <c r="L50" s="46"/>
+      <c r="M50" s="47"/>
       <c r="N50" s="42"/>
       <c r="O50" s="43"/>
       <c r="P50" s="44"/>
       <c r="Q50" s="10"/>
-      <c r="R50" s="45"/>
-      <c r="S50" s="45"/>
+      <c r="R50" s="52"/>
+      <c r="S50" s="52"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
-      <c r="A51" s="10"/>
+      <c r="A51" s="10">
+        <v>7</v>
+      </c>
       <c r="B51" s="10"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="47"/>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47"/>
-      <c r="M51" s="48"/>
+      <c r="C51" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="67"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="47"/>
       <c r="N51" s="42"/>
       <c r="O51" s="43"/>
       <c r="P51" s="44"/>
       <c r="Q51" s="10"/>
-      <c r="R51" s="45"/>
-      <c r="S51" s="45"/>
+      <c r="R51" s="52"/>
+      <c r="S51" s="52"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="47"/>
-      <c r="J52" s="47"/>
-      <c r="K52" s="47"/>
-      <c r="L52" s="47"/>
-      <c r="M52" s="48"/>
+      <c r="C52" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="45"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="47"/>
       <c r="N52" s="42"/>
       <c r="O52" s="43"/>
       <c r="P52" s="44"/>
       <c r="Q52" s="10"/>
-      <c r="R52" s="45"/>
-      <c r="S52" s="45"/>
+      <c r="R52" s="52"/>
+      <c r="S52" s="52"/>
     </row>
     <row r="53" spans="1:19" ht="30" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="47"/>
-      <c r="K53" s="47"/>
-      <c r="L53" s="47"/>
-      <c r="M53" s="48"/>
+      <c r="C53" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="D53" s="75"/>
+      <c r="E53" s="75"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="75"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
+      <c r="K53" s="46"/>
+      <c r="L53" s="46"/>
+      <c r="M53" s="47"/>
       <c r="N53" s="42"/>
       <c r="O53" s="43"/>
       <c r="P53" s="44"/>
       <c r="Q53" s="10"/>
-      <c r="R53" s="45"/>
-      <c r="S53" s="45"/>
+      <c r="R53" s="52"/>
+      <c r="S53" s="52"/>
     </row>
     <row r="54" spans="1:19" ht="30" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="47"/>
-      <c r="L54" s="47"/>
-      <c r="M54" s="48"/>
+      <c r="C54" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="D54" s="75"/>
+      <c r="E54" s="75"/>
+      <c r="F54" s="75"/>
+      <c r="G54" s="75"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="46"/>
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="46"/>
+      <c r="M54" s="47"/>
       <c r="N54" s="42"/>
       <c r="O54" s="43"/>
       <c r="P54" s="44"/>
       <c r="Q54" s="10"/>
-      <c r="R54" s="45"/>
-      <c r="S54" s="45"/>
+      <c r="R54" s="52"/>
+      <c r="S54" s="52"/>
     </row>
     <row r="55" spans="1:19" ht="30" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="47"/>
-      <c r="J55" s="47"/>
-      <c r="K55" s="47"/>
-      <c r="L55" s="47"/>
-      <c r="M55" s="48"/>
+      <c r="C55" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D55" s="75"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="75"/>
+      <c r="H55" s="45"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="46"/>
+      <c r="M55" s="47"/>
       <c r="N55" s="42"/>
       <c r="O55" s="43"/>
       <c r="P55" s="44"/>
       <c r="Q55" s="10"/>
-      <c r="R55" s="45"/>
-      <c r="S55" s="45"/>
+      <c r="R55" s="52"/>
+      <c r="S55" s="52"/>
     </row>
     <row r="56" spans="1:19" ht="30" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="47"/>
-      <c r="J56" s="47"/>
-      <c r="K56" s="47"/>
-      <c r="L56" s="47"/>
-      <c r="M56" s="48"/>
+      <c r="C56" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
+      <c r="L56" s="46"/>
+      <c r="M56" s="47"/>
       <c r="N56" s="42"/>
       <c r="O56" s="43"/>
       <c r="P56" s="44"/>
       <c r="Q56" s="10"/>
-      <c r="R56" s="45"/>
-      <c r="S56" s="45"/>
+      <c r="R56" s="52"/>
+      <c r="S56" s="52"/>
     </row>
     <row r="57" spans="1:19" ht="30" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="47"/>
-      <c r="J57" s="47"/>
-      <c r="K57" s="47"/>
-      <c r="L57" s="47"/>
-      <c r="M57" s="48"/>
+      <c r="C57" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="45"/>
+      <c r="I57" s="46"/>
+      <c r="J57" s="46"/>
+      <c r="K57" s="46"/>
+      <c r="L57" s="46"/>
+      <c r="M57" s="47"/>
       <c r="N57" s="42"/>
       <c r="O57" s="43"/>
       <c r="P57" s="44"/>
       <c r="Q57" s="10"/>
-      <c r="R57" s="45"/>
-      <c r="S57" s="45"/>
+      <c r="R57" s="52"/>
+      <c r="S57" s="52"/>
     </row>
     <row r="58" spans="1:19" ht="30" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="47"/>
-      <c r="J58" s="47"/>
-      <c r="K58" s="47"/>
-      <c r="L58" s="47"/>
-      <c r="M58" s="48"/>
+      <c r="C58" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="46"/>
+      <c r="M58" s="47"/>
       <c r="N58" s="42"/>
       <c r="O58" s="43"/>
       <c r="P58" s="44"/>
       <c r="Q58" s="10"/>
-      <c r="R58" s="45"/>
-      <c r="S58" s="45"/>
+      <c r="R58" s="52"/>
+      <c r="S58" s="52"/>
+    </row>
+    <row r="59" spans="1:19" ht="30" customHeight="1">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75"/>
+      <c r="H59" s="45"/>
+      <c r="I59" s="46"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="46"/>
+      <c r="L59" s="46"/>
+      <c r="M59" s="47"/>
+      <c r="N59" s="42"/>
+      <c r="O59" s="43"/>
+      <c r="P59" s="44"/>
+      <c r="Q59" s="10"/>
+    </row>
+    <row r="60" spans="1:19" ht="30" customHeight="1">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="45" t="s">
+        <v>346</v>
+      </c>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="45"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
+      <c r="M60" s="47"/>
+      <c r="N60" s="42"/>
+      <c r="O60" s="43"/>
+      <c r="P60" s="44"/>
+      <c r="Q60" s="10"/>
+    </row>
+    <row r="61" spans="1:19" ht="30" customHeight="1">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="45"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46"/>
+      <c r="K61" s="46"/>
+      <c r="L61" s="46"/>
+      <c r="M61" s="47"/>
+      <c r="N61" s="42"/>
+      <c r="O61" s="43"/>
+      <c r="P61" s="44"/>
+      <c r="Q61" s="10"/>
+    </row>
+    <row r="62" spans="1:19" ht="30" customHeight="1">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="47"/>
+      <c r="H62" s="45"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46"/>
+      <c r="K62" s="46"/>
+      <c r="L62" s="46"/>
+      <c r="M62" s="47"/>
+      <c r="N62" s="42"/>
+      <c r="O62" s="43"/>
+      <c r="P62" s="44"/>
+      <c r="Q62" s="10"/>
+    </row>
+    <row r="63" spans="1:19" ht="30" customHeight="1">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="46"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="46"/>
+      <c r="L63" s="46"/>
+      <c r="M63" s="47"/>
+      <c r="N63" s="42"/>
+      <c r="O63" s="43"/>
+      <c r="P63" s="44"/>
+      <c r="Q63" s="10"/>
+    </row>
+    <row r="64" spans="1:19" ht="30" customHeight="1">
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="45" t="s">
+        <v>347</v>
+      </c>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="47"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
+      <c r="M64" s="47"/>
+      <c r="N64" s="42"/>
+      <c r="O64" s="43"/>
+      <c r="P64" s="44"/>
+      <c r="Q64" s="10"/>
+    </row>
+    <row r="65" spans="1:17" ht="30" customHeight="1">
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D65" s="73"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="73"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="46"/>
+      <c r="J65" s="46"/>
+      <c r="K65" s="46"/>
+      <c r="L65" s="46"/>
+      <c r="M65" s="47"/>
+      <c r="N65" s="42"/>
+      <c r="O65" s="43"/>
+      <c r="P65" s="44"/>
+      <c r="Q65" s="10"/>
+    </row>
+    <row r="66" spans="1:17" ht="30" customHeight="1">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="46"/>
+      <c r="K66" s="46"/>
+      <c r="L66" s="46"/>
+      <c r="M66" s="47"/>
+      <c r="N66" s="42"/>
+      <c r="O66" s="43"/>
+      <c r="P66" s="44"/>
+      <c r="Q66" s="10"/>
+    </row>
+    <row r="67" spans="1:17" ht="30" customHeight="1">
+      <c r="A67" s="10"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="45"/>
+      <c r="I67" s="46"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="46"/>
+      <c r="L67" s="46"/>
+      <c r="M67" s="47"/>
+      <c r="N67" s="42"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="44"/>
+      <c r="Q67" s="10"/>
+    </row>
+    <row r="68" spans="1:17" ht="30" customHeight="1">
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="46"/>
+      <c r="G68" s="47"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="46"/>
+      <c r="J68" s="46"/>
+      <c r="K68" s="46"/>
+      <c r="L68" s="46"/>
+      <c r="M68" s="47"/>
+      <c r="N68" s="42"/>
+      <c r="O68" s="43"/>
+      <c r="P68" s="44"/>
+      <c r="Q68" s="10"/>
+    </row>
+    <row r="69" spans="1:17" ht="30" customHeight="1">
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="46"/>
+      <c r="J69" s="46"/>
+      <c r="K69" s="46"/>
+      <c r="L69" s="46"/>
+      <c r="M69" s="47"/>
+      <c r="N69" s="42"/>
+      <c r="O69" s="43"/>
+      <c r="P69" s="44"/>
+      <c r="Q69" s="10"/>
+    </row>
+    <row r="70" spans="1:17" ht="30" customHeight="1">
+      <c r="A70" s="10"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="46"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="46"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="42"/>
+      <c r="O70" s="43"/>
+      <c r="P70" s="44"/>
+      <c r="Q70" s="10"/>
+    </row>
+    <row r="71" spans="1:17" ht="30" customHeight="1">
+      <c r="A71" s="10"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="46"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
+      <c r="M71" s="47"/>
+      <c r="N71" s="42"/>
+      <c r="O71" s="43"/>
+      <c r="P71" s="44"/>
+      <c r="Q71" s="10"/>
+    </row>
+    <row r="72" spans="1:17" ht="30" customHeight="1">
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="47"/>
+      <c r="H72" s="45"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
+      <c r="K72" s="46"/>
+      <c r="L72" s="46"/>
+      <c r="M72" s="47"/>
+      <c r="N72" s="42"/>
+      <c r="O72" s="43"/>
+      <c r="P72" s="44"/>
+      <c r="Q72" s="10"/>
+    </row>
+    <row r="73" spans="1:17" ht="30" customHeight="1">
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D73" s="73"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="73"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="45"/>
+      <c r="I73" s="46"/>
+      <c r="J73" s="46"/>
+      <c r="K73" s="46"/>
+      <c r="L73" s="46"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="42"/>
+      <c r="O73" s="43"/>
+      <c r="P73" s="44"/>
+      <c r="Q73" s="10"/>
+    </row>
+    <row r="74" spans="1:17" ht="30" customHeight="1">
+      <c r="A74" s="10"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="47"/>
+      <c r="H74" s="45"/>
+      <c r="I74" s="46"/>
+      <c r="J74" s="46"/>
+      <c r="K74" s="46"/>
+      <c r="L74" s="46"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="42"/>
+      <c r="O74" s="43"/>
+      <c r="P74" s="44"/>
+      <c r="Q74" s="10"/>
+    </row>
+    <row r="75" spans="1:17" ht="30" customHeight="1">
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D75" s="75"/>
+      <c r="E75" s="75"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="75"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="46"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="46"/>
+      <c r="L75" s="46"/>
+      <c r="M75" s="47"/>
+      <c r="N75" s="42"/>
+      <c r="O75" s="43"/>
+      <c r="P75" s="44"/>
+      <c r="Q75" s="10"/>
+    </row>
+    <row r="76" spans="1:17" ht="30" customHeight="1">
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="45" t="s">
+        <v>350</v>
+      </c>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="47"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="46"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="42"/>
+      <c r="O76" s="43"/>
+      <c r="P76" s="44"/>
+      <c r="Q76" s="10"/>
+    </row>
+    <row r="77" spans="1:17" ht="30" customHeight="1">
+      <c r="A77" s="10"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D77" s="73"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="45"/>
+      <c r="I77" s="46"/>
+      <c r="J77" s="46"/>
+      <c r="K77" s="46"/>
+      <c r="L77" s="46"/>
+      <c r="M77" s="47"/>
+      <c r="N77" s="42"/>
+      <c r="O77" s="43"/>
+      <c r="P77" s="44"/>
+      <c r="Q77" s="10"/>
+    </row>
+    <row r="78" spans="1:17" ht="30" customHeight="1">
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D78" s="46"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="46"/>
+      <c r="G78" s="47"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="46"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
+      <c r="L78" s="46"/>
+      <c r="M78" s="47"/>
+      <c r="N78" s="42"/>
+      <c r="O78" s="43"/>
+      <c r="P78" s="44"/>
+      <c r="Q78" s="10"/>
+    </row>
+    <row r="79" spans="1:17" ht="30" customHeight="1">
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
+      <c r="M79" s="47"/>
+      <c r="N79" s="42"/>
+      <c r="O79" s="43"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="10"/>
+    </row>
+    <row r="80" spans="1:17" ht="30" customHeight="1">
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="45" t="s">
+        <v>351</v>
+      </c>
+      <c r="D80" s="46"/>
+      <c r="E80" s="46"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="47"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
+      <c r="L80" s="46"/>
+      <c r="M80" s="47"/>
+      <c r="N80" s="42"/>
+      <c r="O80" s="43"/>
+      <c r="P80" s="44"/>
+      <c r="Q80" s="10"/>
+    </row>
+    <row r="81" spans="1:17" ht="30" customHeight="1">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D81" s="73"/>
+      <c r="E81" s="73"/>
+      <c r="F81" s="73"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="46"/>
+      <c r="J81" s="46"/>
+      <c r="K81" s="46"/>
+      <c r="L81" s="46"/>
+      <c r="M81" s="47"/>
+      <c r="N81" s="42"/>
+      <c r="O81" s="43"/>
+      <c r="P81" s="44"/>
+      <c r="Q81" s="10"/>
+    </row>
+    <row r="82" spans="1:17" ht="30" customHeight="1">
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D82" s="46"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="47"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="46"/>
+      <c r="K82" s="46"/>
+      <c r="L82" s="46"/>
+      <c r="M82" s="47"/>
+      <c r="N82" s="42"/>
+      <c r="O82" s="43"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="10"/>
+    </row>
+    <row r="83" spans="1:17" ht="30" customHeight="1">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D83" s="75"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="45"/>
+      <c r="I83" s="46"/>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="47"/>
+      <c r="N83" s="42"/>
+      <c r="O83" s="43"/>
+      <c r="P83" s="44"/>
+      <c r="Q83" s="10"/>
+    </row>
+    <row r="84" spans="1:17" ht="30" customHeight="1">
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="45" t="s">
+        <v>352</v>
+      </c>
+      <c r="D84" s="46"/>
+      <c r="E84" s="46"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="47"/>
+      <c r="H84" s="45"/>
+      <c r="I84" s="46"/>
+      <c r="J84" s="46"/>
+      <c r="K84" s="46"/>
+      <c r="L84" s="46"/>
+      <c r="M84" s="47"/>
+      <c r="N84" s="42"/>
+      <c r="O84" s="43"/>
+      <c r="P84" s="44"/>
+      <c r="Q84" s="10"/>
+    </row>
+    <row r="85" spans="1:17" ht="30" customHeight="1">
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D85" s="73"/>
+      <c r="E85" s="73"/>
+      <c r="F85" s="73"/>
+      <c r="G85" s="74"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="46"/>
+      <c r="J85" s="46"/>
+      <c r="K85" s="46"/>
+      <c r="L85" s="46"/>
+      <c r="M85" s="47"/>
+      <c r="N85" s="42"/>
+      <c r="O85" s="43"/>
+      <c r="P85" s="44"/>
+      <c r="Q85" s="10"/>
+    </row>
+    <row r="86" spans="1:17" ht="30" customHeight="1">
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D86" s="46"/>
+      <c r="E86" s="46"/>
+      <c r="F86" s="46"/>
+      <c r="G86" s="47"/>
+      <c r="H86" s="45"/>
+      <c r="I86" s="46"/>
+      <c r="J86" s="46"/>
+      <c r="K86" s="46"/>
+      <c r="L86" s="46"/>
+      <c r="M86" s="47"/>
+      <c r="N86" s="42"/>
+      <c r="O86" s="43"/>
+      <c r="P86" s="44"/>
+      <c r="Q86" s="10"/>
+    </row>
+    <row r="87" spans="1:17" ht="30" customHeight="1">
+      <c r="A87" s="10"/>
+      <c r="B87" s="10"/>
+      <c r="C87" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="45"/>
+      <c r="I87" s="46"/>
+      <c r="J87" s="46"/>
+      <c r="K87" s="46"/>
+      <c r="L87" s="46"/>
+      <c r="M87" s="47"/>
+      <c r="N87" s="42"/>
+      <c r="O87" s="43"/>
+      <c r="P87" s="44"/>
+      <c r="Q87" s="10"/>
+    </row>
+    <row r="88" spans="1:17" ht="30" customHeight="1">
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="45" t="s">
+        <v>353</v>
+      </c>
+      <c r="D88" s="46"/>
+      <c r="E88" s="46"/>
+      <c r="F88" s="46"/>
+      <c r="G88" s="47"/>
+      <c r="H88" s="45"/>
+      <c r="I88" s="46"/>
+      <c r="J88" s="46"/>
+      <c r="K88" s="46"/>
+      <c r="L88" s="46"/>
+      <c r="M88" s="47"/>
+      <c r="N88" s="42"/>
+      <c r="O88" s="43"/>
+      <c r="P88" s="44"/>
+      <c r="Q88" s="10"/>
+    </row>
+    <row r="89" spans="1:17" ht="30" customHeight="1">
+      <c r="A89" s="10"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D89" s="73"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="73"/>
+      <c r="G89" s="74"/>
+      <c r="H89" s="45"/>
+      <c r="I89" s="46"/>
+      <c r="J89" s="46"/>
+      <c r="K89" s="46"/>
+      <c r="L89" s="46"/>
+      <c r="M89" s="47"/>
+      <c r="N89" s="42"/>
+      <c r="O89" s="43"/>
+      <c r="P89" s="44"/>
+      <c r="Q89" s="10"/>
+    </row>
+    <row r="90" spans="1:17" ht="30" customHeight="1">
+      <c r="A90" s="10"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D90" s="46"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="46"/>
+      <c r="G90" s="47"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="46"/>
+      <c r="K90" s="46"/>
+      <c r="L90" s="46"/>
+      <c r="M90" s="47"/>
+      <c r="N90" s="42"/>
+      <c r="O90" s="43"/>
+      <c r="P90" s="44"/>
+      <c r="Q90" s="10"/>
+    </row>
+    <row r="91" spans="1:17" ht="30" customHeight="1">
+      <c r="A91" s="10"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D91" s="75"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="46"/>
+      <c r="K91" s="46"/>
+      <c r="L91" s="46"/>
+      <c r="M91" s="47"/>
+      <c r="N91" s="42"/>
+      <c r="O91" s="43"/>
+      <c r="P91" s="44"/>
+      <c r="Q91" s="10"/>
+    </row>
+    <row r="92" spans="1:17" ht="15.75">
+      <c r="A92" s="10"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="D92" s="46"/>
+      <c r="E92" s="46"/>
+      <c r="F92" s="46"/>
+      <c r="G92" s="47"/>
+      <c r="H92" s="45"/>
+      <c r="I92" s="46"/>
+      <c r="J92" s="46"/>
+      <c r="K92" s="46"/>
+      <c r="L92" s="46"/>
+      <c r="M92" s="47"/>
+      <c r="N92" s="42"/>
+      <c r="O92" s="43"/>
+      <c r="P92" s="44"/>
+      <c r="Q92" s="10"/>
+    </row>
+    <row r="93" spans="1:17" ht="15.75">
+      <c r="A93" s="10"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D93" s="73"/>
+      <c r="E93" s="73"/>
+      <c r="F93" s="73"/>
+      <c r="G93" s="74"/>
+      <c r="H93" s="45"/>
+      <c r="I93" s="46"/>
+      <c r="J93" s="46"/>
+      <c r="K93" s="46"/>
+      <c r="L93" s="46"/>
+      <c r="M93" s="47"/>
+      <c r="N93" s="42"/>
+      <c r="O93" s="43"/>
+      <c r="P93" s="44"/>
+      <c r="Q93" s="10"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75">
+      <c r="A94" s="10"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D94" s="46"/>
+      <c r="E94" s="46"/>
+      <c r="F94" s="46"/>
+      <c r="G94" s="47"/>
+      <c r="H94" s="45"/>
+      <c r="I94" s="46"/>
+      <c r="J94" s="46"/>
+      <c r="K94" s="46"/>
+      <c r="L94" s="46"/>
+      <c r="M94" s="47"/>
+      <c r="N94" s="42"/>
+      <c r="O94" s="43"/>
+      <c r="P94" s="44"/>
+      <c r="Q94" s="10"/>
+    </row>
+    <row r="95" spans="1:17" ht="15.75">
+      <c r="A95" s="10"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
+      <c r="F95" s="75"/>
+      <c r="G95" s="75"/>
+      <c r="H95" s="45"/>
+      <c r="I95" s="46"/>
+      <c r="J95" s="46"/>
+      <c r="K95" s="46"/>
+      <c r="L95" s="46"/>
+      <c r="M95" s="47"/>
+      <c r="N95" s="42"/>
+      <c r="O95" s="43"/>
+      <c r="P95" s="44"/>
+      <c r="Q95" s="10"/>
+    </row>
+    <row r="96" spans="1:17" ht="15.75">
+      <c r="A96" s="10"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="45" t="s">
+        <v>355</v>
+      </c>
+      <c r="D96" s="46"/>
+      <c r="E96" s="46"/>
+      <c r="F96" s="46"/>
+      <c r="G96" s="47"/>
+      <c r="H96" s="45"/>
+      <c r="I96" s="46"/>
+      <c r="J96" s="46"/>
+      <c r="K96" s="46"/>
+      <c r="L96" s="46"/>
+      <c r="M96" s="47"/>
+      <c r="N96" s="42"/>
+      <c r="O96" s="43"/>
+      <c r="P96" s="44"/>
+      <c r="Q96" s="10"/>
+    </row>
+    <row r="97" spans="1:17" ht="15.75">
+      <c r="A97" s="10"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D97" s="73"/>
+      <c r="E97" s="73"/>
+      <c r="F97" s="73"/>
+      <c r="G97" s="74"/>
+      <c r="H97" s="45"/>
+      <c r="I97" s="46"/>
+      <c r="J97" s="46"/>
+      <c r="K97" s="46"/>
+      <c r="L97" s="46"/>
+      <c r="M97" s="47"/>
+      <c r="N97" s="42"/>
+      <c r="O97" s="43"/>
+      <c r="P97" s="44"/>
+      <c r="Q97" s="10"/>
+    </row>
+    <row r="98" spans="1:17" ht="15.75">
+      <c r="A98" s="10"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D98" s="46"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="46"/>
+      <c r="G98" s="47"/>
+      <c r="H98" s="45"/>
+      <c r="I98" s="46"/>
+      <c r="J98" s="46"/>
+      <c r="K98" s="46"/>
+      <c r="L98" s="46"/>
+      <c r="M98" s="47"/>
+      <c r="N98" s="42"/>
+      <c r="O98" s="43"/>
+      <c r="P98" s="44"/>
+      <c r="Q98" s="10"/>
+    </row>
+    <row r="99" spans="1:17" ht="15.75">
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="45"/>
+      <c r="I99" s="46"/>
+      <c r="J99" s="46"/>
+      <c r="K99" s="46"/>
+      <c r="L99" s="46"/>
+      <c r="M99" s="47"/>
+      <c r="N99" s="42"/>
+      <c r="O99" s="43"/>
+      <c r="P99" s="44"/>
+      <c r="Q99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75">
+      <c r="A100" s="10"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="45" t="s">
+        <v>356</v>
+      </c>
+      <c r="D100" s="46"/>
+      <c r="E100" s="46"/>
+      <c r="F100" s="46"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="45"/>
+      <c r="I100" s="46"/>
+      <c r="J100" s="46"/>
+      <c r="K100" s="46"/>
+      <c r="L100" s="46"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="42"/>
+      <c r="O100" s="43"/>
+      <c r="P100" s="44"/>
+      <c r="Q100" s="10"/>
+    </row>
+    <row r="101" spans="1:17" ht="15.75">
+      <c r="A101" s="10"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D101" s="73"/>
+      <c r="E101" s="73"/>
+      <c r="F101" s="73"/>
+      <c r="G101" s="74"/>
+      <c r="H101" s="45"/>
+      <c r="I101" s="46"/>
+      <c r="J101" s="46"/>
+      <c r="K101" s="46"/>
+      <c r="L101" s="46"/>
+      <c r="M101" s="47"/>
+      <c r="N101" s="42"/>
+      <c r="O101" s="43"/>
+      <c r="P101" s="44"/>
+      <c r="Q101" s="10"/>
+    </row>
+    <row r="102" spans="1:17" ht="15.75">
+      <c r="A102" s="10"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D102" s="46"/>
+      <c r="E102" s="46"/>
+      <c r="F102" s="46"/>
+      <c r="G102" s="47"/>
+      <c r="H102" s="45"/>
+      <c r="I102" s="46"/>
+      <c r="J102" s="46"/>
+      <c r="K102" s="46"/>
+      <c r="L102" s="46"/>
+      <c r="M102" s="47"/>
+      <c r="N102" s="42"/>
+      <c r="O102" s="43"/>
+      <c r="P102" s="44"/>
+      <c r="Q102" s="10"/>
+    </row>
+    <row r="103" spans="1:17" ht="15.75">
+      <c r="A103" s="10"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" s="75"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="75"/>
+      <c r="G103" s="75"/>
+      <c r="H103" s="45"/>
+      <c r="I103" s="46"/>
+      <c r="J103" s="46"/>
+      <c r="K103" s="46"/>
+      <c r="L103" s="46"/>
+      <c r="M103" s="47"/>
+      <c r="N103" s="42"/>
+      <c r="O103" s="43"/>
+      <c r="P103" s="44"/>
+      <c r="Q103" s="10"/>
+    </row>
+    <row r="104" spans="1:17" ht="15.75">
+      <c r="A104" s="10"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="D104" s="46"/>
+      <c r="E104" s="46"/>
+      <c r="F104" s="46"/>
+      <c r="G104" s="47"/>
+      <c r="H104" s="45"/>
+      <c r="I104" s="46"/>
+      <c r="J104" s="46"/>
+      <c r="K104" s="46"/>
+      <c r="L104" s="46"/>
+      <c r="M104" s="47"/>
+      <c r="N104" s="42"/>
+      <c r="O104" s="43"/>
+      <c r="P104" s="44"/>
+      <c r="Q104" s="10"/>
+    </row>
+    <row r="105" spans="1:17" ht="15.75">
+      <c r="A105" s="10"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D105" s="73"/>
+      <c r="E105" s="73"/>
+      <c r="F105" s="73"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="45"/>
+      <c r="I105" s="46"/>
+      <c r="J105" s="46"/>
+      <c r="K105" s="46"/>
+      <c r="L105" s="46"/>
+      <c r="M105" s="47"/>
+      <c r="N105" s="42"/>
+      <c r="O105" s="43"/>
+      <c r="P105" s="44"/>
+      <c r="Q105" s="10"/>
+    </row>
+    <row r="106" spans="1:17" ht="15.75">
+      <c r="A106" s="10"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D106" s="46"/>
+      <c r="E106" s="46"/>
+      <c r="F106" s="46"/>
+      <c r="G106" s="47"/>
+      <c r="H106" s="45"/>
+      <c r="I106" s="46"/>
+      <c r="J106" s="46"/>
+      <c r="K106" s="46"/>
+      <c r="L106" s="46"/>
+      <c r="M106" s="47"/>
+      <c r="N106" s="42"/>
+      <c r="O106" s="43"/>
+      <c r="P106" s="44"/>
+      <c r="Q106" s="10"/>
+    </row>
+    <row r="107" spans="1:17" ht="15.75">
+      <c r="A107" s="10"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D107" s="75"/>
+      <c r="E107" s="75"/>
+      <c r="F107" s="75"/>
+      <c r="G107" s="75"/>
+      <c r="H107" s="45"/>
+      <c r="I107" s="46"/>
+      <c r="J107" s="46"/>
+      <c r="K107" s="46"/>
+      <c r="L107" s="46"/>
+      <c r="M107" s="47"/>
+      <c r="N107" s="42"/>
+      <c r="O107" s="43"/>
+      <c r="P107" s="44"/>
+      <c r="Q107" s="10"/>
+    </row>
+    <row r="108" spans="1:17" ht="15.75">
+      <c r="A108" s="10"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="D108" s="46"/>
+      <c r="E108" s="46"/>
+      <c r="F108" s="46"/>
+      <c r="G108" s="47"/>
+      <c r="H108" s="45"/>
+      <c r="I108" s="46"/>
+      <c r="J108" s="46"/>
+      <c r="K108" s="46"/>
+      <c r="L108" s="46"/>
+      <c r="M108" s="47"/>
+      <c r="N108" s="42"/>
+      <c r="O108" s="43"/>
+      <c r="P108" s="44"/>
+      <c r="Q108" s="10"/>
+    </row>
+    <row r="109" spans="1:17" ht="15.75">
+      <c r="A109" s="10"/>
+      <c r="B109" s="10"/>
+      <c r="C109" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D109" s="73"/>
+      <c r="E109" s="73"/>
+      <c r="F109" s="73"/>
+      <c r="G109" s="74"/>
+      <c r="H109" s="45"/>
+      <c r="I109" s="46"/>
+      <c r="J109" s="46"/>
+      <c r="K109" s="46"/>
+      <c r="L109" s="46"/>
+      <c r="M109" s="47"/>
+      <c r="N109" s="42"/>
+      <c r="O109" s="43"/>
+      <c r="P109" s="44"/>
+      <c r="Q109" s="10"/>
+    </row>
+    <row r="110" spans="1:17" ht="15.75">
+      <c r="A110" s="10"/>
+      <c r="B110" s="10"/>
+      <c r="C110" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D110" s="46"/>
+      <c r="E110" s="46"/>
+      <c r="F110" s="46"/>
+      <c r="G110" s="47"/>
+      <c r="H110" s="45"/>
+      <c r="I110" s="46"/>
+      <c r="J110" s="46"/>
+      <c r="K110" s="46"/>
+      <c r="L110" s="46"/>
+      <c r="M110" s="47"/>
+      <c r="N110" s="42"/>
+      <c r="O110" s="43"/>
+      <c r="P110" s="44"/>
+      <c r="Q110" s="10"/>
+    </row>
+    <row r="111" spans="1:17" ht="15.75">
+      <c r="A111" s="10"/>
+      <c r="B111" s="10"/>
+      <c r="C111" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D111" s="75"/>
+      <c r="E111" s="75"/>
+      <c r="F111" s="75"/>
+      <c r="G111" s="75"/>
+      <c r="H111" s="45"/>
+      <c r="I111" s="46"/>
+      <c r="J111" s="46"/>
+      <c r="K111" s="46"/>
+      <c r="L111" s="46"/>
+      <c r="M111" s="47"/>
+      <c r="N111" s="42"/>
+      <c r="O111" s="43"/>
+      <c r="P111" s="44"/>
+      <c r="Q111" s="10"/>
+    </row>
+    <row r="112" spans="1:17" ht="15.75">
+      <c r="A112" s="10"/>
+      <c r="B112" s="10"/>
+      <c r="C112" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="D112" s="46"/>
+      <c r="E112" s="46"/>
+      <c r="F112" s="46"/>
+      <c r="G112" s="47"/>
+      <c r="H112" s="45"/>
+      <c r="I112" s="46"/>
+      <c r="J112" s="46"/>
+      <c r="K112" s="46"/>
+      <c r="L112" s="46"/>
+      <c r="M112" s="47"/>
+      <c r="N112" s="42"/>
+      <c r="O112" s="43"/>
+      <c r="P112" s="44"/>
+      <c r="Q112" s="10"/>
+    </row>
+    <row r="113" spans="1:17" ht="15.75">
+      <c r="A113" s="10"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D113" s="73"/>
+      <c r="E113" s="73"/>
+      <c r="F113" s="73"/>
+      <c r="G113" s="74"/>
+      <c r="H113" s="45"/>
+      <c r="I113" s="46"/>
+      <c r="J113" s="46"/>
+      <c r="K113" s="46"/>
+      <c r="L113" s="46"/>
+      <c r="M113" s="47"/>
+      <c r="N113" s="42"/>
+      <c r="O113" s="43"/>
+      <c r="P113" s="44"/>
+      <c r="Q113" s="10"/>
+    </row>
+    <row r="114" spans="1:17" ht="15.75">
+      <c r="A114" s="10"/>
+      <c r="B114" s="10"/>
+      <c r="C114" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D114" s="46"/>
+      <c r="E114" s="46"/>
+      <c r="F114" s="46"/>
+      <c r="G114" s="47"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="46"/>
+      <c r="J114" s="46"/>
+      <c r="K114" s="46"/>
+      <c r="L114" s="46"/>
+      <c r="M114" s="47"/>
+      <c r="N114" s="42"/>
+      <c r="O114" s="43"/>
+      <c r="P114" s="44"/>
+      <c r="Q114" s="10"/>
+    </row>
+    <row r="115" spans="1:17" ht="15.75">
+      <c r="A115" s="10"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D115" s="75"/>
+      <c r="E115" s="75"/>
+      <c r="F115" s="75"/>
+      <c r="G115" s="75"/>
+      <c r="H115" s="45"/>
+      <c r="I115" s="46"/>
+      <c r="J115" s="46"/>
+      <c r="K115" s="46"/>
+      <c r="L115" s="46"/>
+      <c r="M115" s="47"/>
+      <c r="N115" s="42"/>
+      <c r="O115" s="43"/>
+      <c r="P115" s="44"/>
+      <c r="Q115" s="10"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75">
+      <c r="A116" s="10"/>
+      <c r="B116" s="10"/>
+      <c r="C116" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="D116" s="46"/>
+      <c r="E116" s="46"/>
+      <c r="F116" s="46"/>
+      <c r="G116" s="47"/>
+      <c r="H116" s="45"/>
+      <c r="I116" s="46"/>
+      <c r="J116" s="46"/>
+      <c r="K116" s="46"/>
+      <c r="L116" s="46"/>
+      <c r="M116" s="47"/>
+      <c r="N116" s="42"/>
+      <c r="O116" s="43"/>
+      <c r="P116" s="44"/>
+      <c r="Q116" s="10"/>
+    </row>
+    <row r="117" spans="1:17" ht="15.75">
+      <c r="A117" s="10"/>
+      <c r="B117" s="10"/>
+      <c r="C117" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D117" s="73"/>
+      <c r="E117" s="73"/>
+      <c r="F117" s="73"/>
+      <c r="G117" s="74"/>
+      <c r="H117" s="45"/>
+      <c r="I117" s="46"/>
+      <c r="J117" s="46"/>
+      <c r="K117" s="46"/>
+      <c r="L117" s="46"/>
+      <c r="M117" s="47"/>
+      <c r="N117" s="42"/>
+      <c r="O117" s="43"/>
+      <c r="P117" s="44"/>
+      <c r="Q117" s="10"/>
+    </row>
+    <row r="118" spans="1:17" ht="15.75">
+      <c r="A118" s="10"/>
+      <c r="B118" s="10"/>
+      <c r="C118" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D118" s="46"/>
+      <c r="E118" s="46"/>
+      <c r="F118" s="46"/>
+      <c r="G118" s="47"/>
+      <c r="H118" s="45"/>
+      <c r="I118" s="46"/>
+      <c r="J118" s="46"/>
+      <c r="K118" s="46"/>
+      <c r="L118" s="46"/>
+      <c r="M118" s="47"/>
+      <c r="N118" s="42"/>
+      <c r="O118" s="43"/>
+      <c r="P118" s="44"/>
+      <c r="Q118" s="10"/>
+    </row>
+    <row r="119" spans="1:17" ht="15.75">
+      <c r="A119" s="10"/>
+      <c r="B119" s="10"/>
+      <c r="C119" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D119" s="75"/>
+      <c r="E119" s="75"/>
+      <c r="F119" s="75"/>
+      <c r="G119" s="75"/>
+      <c r="H119" s="45"/>
+      <c r="I119" s="46"/>
+      <c r="J119" s="46"/>
+      <c r="K119" s="46"/>
+      <c r="L119" s="46"/>
+      <c r="M119" s="47"/>
+      <c r="N119" s="42"/>
+      <c r="O119" s="43"/>
+      <c r="P119" s="44"/>
+      <c r="Q119" s="10"/>
+    </row>
+    <row r="120" spans="1:17" ht="15.75">
+      <c r="A120" s="10"/>
+      <c r="B120" s="10"/>
+      <c r="C120" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="D120" s="46"/>
+      <c r="E120" s="46"/>
+      <c r="F120" s="46"/>
+      <c r="G120" s="47"/>
+      <c r="H120" s="45"/>
+      <c r="I120" s="46"/>
+      <c r="J120" s="46"/>
+      <c r="K120" s="46"/>
+      <c r="L120" s="46"/>
+      <c r="M120" s="47"/>
+      <c r="N120" s="42"/>
+      <c r="O120" s="43"/>
+      <c r="P120" s="44"/>
+      <c r="Q120" s="10"/>
+    </row>
+    <row r="121" spans="1:17" ht="15.75">
+      <c r="A121" s="10"/>
+      <c r="B121" s="10"/>
+      <c r="C121" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D121" s="73"/>
+      <c r="E121" s="73"/>
+      <c r="F121" s="73"/>
+      <c r="G121" s="74"/>
+      <c r="H121" s="45"/>
+      <c r="I121" s="46"/>
+      <c r="J121" s="46"/>
+      <c r="K121" s="46"/>
+      <c r="L121" s="46"/>
+      <c r="M121" s="47"/>
+      <c r="N121" s="42"/>
+      <c r="O121" s="43"/>
+      <c r="P121" s="44"/>
+      <c r="Q121" s="10"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75">
+      <c r="A122" s="10"/>
+      <c r="B122" s="10"/>
+      <c r="C122" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D122" s="46"/>
+      <c r="E122" s="46"/>
+      <c r="F122" s="46"/>
+      <c r="G122" s="47"/>
+      <c r="H122" s="45"/>
+      <c r="I122" s="46"/>
+      <c r="J122" s="46"/>
+      <c r="K122" s="46"/>
+      <c r="L122" s="46"/>
+      <c r="M122" s="47"/>
+      <c r="N122" s="42"/>
+      <c r="O122" s="43"/>
+      <c r="P122" s="44"/>
+      <c r="Q122" s="10"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75">
+      <c r="A123" s="10"/>
+      <c r="B123" s="10"/>
+      <c r="C123" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D123" s="75"/>
+      <c r="E123" s="75"/>
+      <c r="F123" s="75"/>
+      <c r="G123" s="75"/>
+      <c r="H123" s="45"/>
+      <c r="I123" s="46"/>
+      <c r="J123" s="46"/>
+      <c r="K123" s="46"/>
+      <c r="L123" s="46"/>
+      <c r="M123" s="47"/>
+      <c r="N123" s="42"/>
+      <c r="O123" s="43"/>
+      <c r="P123" s="44"/>
+      <c r="Q123" s="10"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75">
+      <c r="A124" s="10"/>
+      <c r="B124" s="10"/>
+      <c r="C124" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="D124" s="46"/>
+      <c r="E124" s="46"/>
+      <c r="F124" s="46"/>
+      <c r="G124" s="47"/>
+      <c r="H124" s="45"/>
+      <c r="I124" s="46"/>
+      <c r="J124" s="46"/>
+      <c r="K124" s="46"/>
+      <c r="L124" s="46"/>
+      <c r="M124" s="47"/>
+      <c r="N124" s="42"/>
+      <c r="O124" s="43"/>
+      <c r="P124" s="44"/>
+      <c r="Q124" s="10"/>
+    </row>
+    <row r="125" spans="1:17" ht="15.75">
+      <c r="A125" s="10"/>
+      <c r="B125" s="10"/>
+      <c r="C125" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D125" s="73"/>
+      <c r="E125" s="73"/>
+      <c r="F125" s="73"/>
+      <c r="G125" s="74"/>
+      <c r="H125" s="45"/>
+      <c r="I125" s="46"/>
+      <c r="J125" s="46"/>
+      <c r="K125" s="46"/>
+      <c r="L125" s="46"/>
+      <c r="M125" s="47"/>
+      <c r="N125" s="42"/>
+      <c r="O125" s="43"/>
+      <c r="P125" s="44"/>
+      <c r="Q125" s="10"/>
+    </row>
+    <row r="126" spans="1:17" ht="15.75">
+      <c r="A126" s="10"/>
+      <c r="B126" s="10"/>
+      <c r="C126" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D126" s="46"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="46"/>
+      <c r="G126" s="47"/>
+      <c r="H126" s="45"/>
+      <c r="I126" s="46"/>
+      <c r="J126" s="46"/>
+      <c r="K126" s="46"/>
+      <c r="L126" s="46"/>
+      <c r="M126" s="47"/>
+      <c r="N126" s="42"/>
+      <c r="O126" s="43"/>
+      <c r="P126" s="44"/>
+      <c r="Q126" s="10"/>
+    </row>
+    <row r="127" spans="1:17" ht="15.75">
+      <c r="A127" s="10"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D127" s="75"/>
+      <c r="E127" s="75"/>
+      <c r="F127" s="75"/>
+      <c r="G127" s="75"/>
+      <c r="H127" s="45"/>
+      <c r="I127" s="46"/>
+      <c r="J127" s="46"/>
+      <c r="K127" s="46"/>
+      <c r="L127" s="46"/>
+      <c r="M127" s="47"/>
+      <c r="N127" s="42"/>
+      <c r="O127" s="43"/>
+      <c r="P127" s="44"/>
+      <c r="Q127" s="10"/>
+    </row>
+    <row r="128" spans="1:17" ht="15.75">
+      <c r="A128" s="10"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="D128" s="46"/>
+      <c r="E128" s="46"/>
+      <c r="F128" s="46"/>
+      <c r="G128" s="47"/>
+      <c r="H128" s="45"/>
+      <c r="I128" s="46"/>
+      <c r="J128" s="46"/>
+      <c r="K128" s="46"/>
+      <c r="L128" s="46"/>
+      <c r="M128" s="47"/>
+      <c r="N128" s="42"/>
+      <c r="O128" s="43"/>
+      <c r="P128" s="44"/>
+      <c r="Q128" s="10"/>
+    </row>
+    <row r="129" spans="1:17" ht="15.75">
+      <c r="A129" s="10"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D129" s="73"/>
+      <c r="E129" s="73"/>
+      <c r="F129" s="73"/>
+      <c r="G129" s="74"/>
+      <c r="H129" s="45"/>
+      <c r="I129" s="46"/>
+      <c r="J129" s="46"/>
+      <c r="K129" s="46"/>
+      <c r="L129" s="46"/>
+      <c r="M129" s="47"/>
+      <c r="N129" s="42"/>
+      <c r="O129" s="43"/>
+      <c r="P129" s="44"/>
+      <c r="Q129" s="10"/>
+    </row>
+    <row r="130" spans="1:17" ht="15.75">
+      <c r="A130" s="10"/>
+      <c r="B130" s="10"/>
+      <c r="C130" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D130" s="46"/>
+      <c r="E130" s="46"/>
+      <c r="F130" s="46"/>
+      <c r="G130" s="47"/>
+      <c r="H130" s="45"/>
+      <c r="I130" s="46"/>
+      <c r="J130" s="46"/>
+      <c r="K130" s="46"/>
+      <c r="L130" s="46"/>
+      <c r="M130" s="47"/>
+      <c r="N130" s="42"/>
+      <c r="O130" s="43"/>
+      <c r="P130" s="44"/>
+      <c r="Q130" s="10"/>
+    </row>
+    <row r="131" spans="1:17" ht="15.75">
+      <c r="A131" s="10"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D131" s="75"/>
+      <c r="E131" s="75"/>
+      <c r="F131" s="75"/>
+      <c r="G131" s="75"/>
+      <c r="H131" s="45"/>
+      <c r="I131" s="46"/>
+      <c r="J131" s="46"/>
+      <c r="K131" s="46"/>
+      <c r="L131" s="46"/>
+      <c r="M131" s="47"/>
+      <c r="N131" s="42"/>
+      <c r="O131" s="43"/>
+      <c r="P131" s="44"/>
+      <c r="Q131" s="10"/>
+    </row>
+    <row r="132" spans="1:17" ht="15.75">
+      <c r="A132" s="10"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="D132" s="46"/>
+      <c r="E132" s="46"/>
+      <c r="F132" s="46"/>
+      <c r="G132" s="47"/>
+      <c r="H132" s="45"/>
+      <c r="I132" s="46"/>
+      <c r="J132" s="46"/>
+      <c r="K132" s="46"/>
+      <c r="L132" s="46"/>
+      <c r="M132" s="47"/>
+      <c r="N132" s="42"/>
+      <c r="O132" s="43"/>
+      <c r="P132" s="44"/>
+      <c r="Q132" s="10"/>
+    </row>
+    <row r="133" spans="1:17" ht="15.75">
+      <c r="A133" s="10"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D133" s="73"/>
+      <c r="E133" s="73"/>
+      <c r="F133" s="73"/>
+      <c r="G133" s="74"/>
+      <c r="H133" s="45"/>
+      <c r="I133" s="46"/>
+      <c r="J133" s="46"/>
+      <c r="K133" s="46"/>
+      <c r="L133" s="46"/>
+      <c r="M133" s="47"/>
+      <c r="N133" s="42"/>
+      <c r="O133" s="43"/>
+      <c r="P133" s="44"/>
+      <c r="Q133" s="10"/>
+    </row>
+    <row r="134" spans="1:17" ht="15.75">
+      <c r="A134" s="10"/>
+      <c r="B134" s="10"/>
+      <c r="C134" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D134" s="46"/>
+      <c r="E134" s="46"/>
+      <c r="F134" s="46"/>
+      <c r="G134" s="47"/>
+      <c r="H134" s="45"/>
+      <c r="I134" s="46"/>
+      <c r="J134" s="46"/>
+      <c r="K134" s="46"/>
+      <c r="L134" s="46"/>
+      <c r="M134" s="47"/>
+      <c r="N134" s="42"/>
+      <c r="O134" s="43"/>
+      <c r="P134" s="44"/>
+      <c r="Q134" s="10"/>
+    </row>
+    <row r="135" spans="1:17" ht="15.75">
+      <c r="A135" s="10"/>
+      <c r="B135" s="10"/>
+      <c r="C135" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D135" s="75"/>
+      <c r="E135" s="75"/>
+      <c r="F135" s="75"/>
+      <c r="G135" s="75"/>
+      <c r="H135" s="45"/>
+      <c r="I135" s="46"/>
+      <c r="J135" s="46"/>
+      <c r="K135" s="46"/>
+      <c r="L135" s="46"/>
+      <c r="M135" s="47"/>
+      <c r="N135" s="42"/>
+      <c r="O135" s="43"/>
+      <c r="P135" s="44"/>
+      <c r="Q135" s="10"/>
+    </row>
+    <row r="136" spans="1:17" ht="15.75">
+      <c r="A136" s="10"/>
+      <c r="B136" s="10"/>
+      <c r="C136" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="D136" s="46"/>
+      <c r="E136" s="46"/>
+      <c r="F136" s="46"/>
+      <c r="G136" s="47"/>
+      <c r="H136" s="45"/>
+      <c r="I136" s="46"/>
+      <c r="J136" s="46"/>
+      <c r="K136" s="46"/>
+      <c r="L136" s="46"/>
+      <c r="M136" s="47"/>
+      <c r="N136" s="42"/>
+      <c r="O136" s="43"/>
+      <c r="P136" s="44"/>
+      <c r="Q136" s="10"/>
+    </row>
+    <row r="137" spans="1:17" ht="15.75">
+      <c r="A137" s="10"/>
+      <c r="B137" s="10"/>
+      <c r="C137" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D137" s="73"/>
+      <c r="E137" s="73"/>
+      <c r="F137" s="73"/>
+      <c r="G137" s="74"/>
+      <c r="H137" s="45"/>
+      <c r="I137" s="46"/>
+      <c r="J137" s="46"/>
+      <c r="K137" s="46"/>
+      <c r="L137" s="46"/>
+      <c r="M137" s="47"/>
+      <c r="N137" s="42"/>
+      <c r="O137" s="43"/>
+      <c r="P137" s="44"/>
+      <c r="Q137" s="10"/>
+    </row>
+    <row r="138" spans="1:17" ht="15.75">
+      <c r="A138" s="10"/>
+      <c r="B138" s="10"/>
+      <c r="C138" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D138" s="46"/>
+      <c r="E138" s="46"/>
+      <c r="F138" s="46"/>
+      <c r="G138" s="47"/>
+      <c r="H138" s="45"/>
+      <c r="I138" s="46"/>
+      <c r="J138" s="46"/>
+      <c r="K138" s="46"/>
+      <c r="L138" s="46"/>
+      <c r="M138" s="47"/>
+      <c r="N138" s="42"/>
+      <c r="O138" s="43"/>
+      <c r="P138" s="44"/>
+      <c r="Q138" s="10"/>
+    </row>
+    <row r="139" spans="1:17" ht="15.75">
+      <c r="A139" s="10"/>
+      <c r="B139" s="10"/>
+      <c r="C139" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D139" s="75"/>
+      <c r="E139" s="75"/>
+      <c r="F139" s="75"/>
+      <c r="G139" s="75"/>
+      <c r="H139" s="45"/>
+      <c r="I139" s="46"/>
+      <c r="J139" s="46"/>
+      <c r="K139" s="46"/>
+      <c r="L139" s="46"/>
+      <c r="M139" s="47"/>
+      <c r="N139" s="42"/>
+      <c r="O139" s="43"/>
+      <c r="P139" s="44"/>
+      <c r="Q139" s="10"/>
+    </row>
+    <row r="140" spans="1:17" ht="15.75">
+      <c r="A140" s="10"/>
+      <c r="B140" s="10"/>
+      <c r="C140" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="D140" s="46"/>
+      <c r="E140" s="46"/>
+      <c r="F140" s="46"/>
+      <c r="G140" s="47"/>
+      <c r="H140" s="45"/>
+      <c r="I140" s="46"/>
+      <c r="J140" s="46"/>
+      <c r="K140" s="46"/>
+      <c r="L140" s="46"/>
+      <c r="M140" s="47"/>
+      <c r="N140" s="42"/>
+      <c r="O140" s="43"/>
+      <c r="P140" s="44"/>
+      <c r="Q140" s="10"/>
+    </row>
+    <row r="141" spans="1:17" ht="15.75">
+      <c r="A141" s="10"/>
+      <c r="B141" s="10"/>
+      <c r="C141" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D141" s="73"/>
+      <c r="E141" s="73"/>
+      <c r="F141" s="73"/>
+      <c r="G141" s="74"/>
+      <c r="H141" s="45"/>
+      <c r="I141" s="46"/>
+      <c r="J141" s="46"/>
+      <c r="K141" s="46"/>
+      <c r="L141" s="46"/>
+      <c r="M141" s="47"/>
+      <c r="N141" s="42"/>
+      <c r="O141" s="43"/>
+      <c r="P141" s="44"/>
+      <c r="Q141" s="10"/>
+    </row>
+    <row r="142" spans="1:17" ht="15.75">
+      <c r="A142" s="10"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D142" s="46"/>
+      <c r="E142" s="46"/>
+      <c r="F142" s="46"/>
+      <c r="G142" s="47"/>
+      <c r="H142" s="45"/>
+      <c r="I142" s="46"/>
+      <c r="J142" s="46"/>
+      <c r="K142" s="46"/>
+      <c r="L142" s="46"/>
+      <c r="M142" s="47"/>
+      <c r="N142" s="42"/>
+      <c r="O142" s="43"/>
+      <c r="P142" s="44"/>
+      <c r="Q142" s="10"/>
+    </row>
+    <row r="143" spans="1:17" ht="15.75">
+      <c r="A143" s="10"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D143" s="75"/>
+      <c r="E143" s="75"/>
+      <c r="F143" s="75"/>
+      <c r="G143" s="75"/>
+      <c r="H143" s="45"/>
+      <c r="I143" s="46"/>
+      <c r="J143" s="46"/>
+      <c r="K143" s="46"/>
+      <c r="L143" s="46"/>
+      <c r="M143" s="47"/>
+      <c r="N143" s="42"/>
+      <c r="O143" s="43"/>
+      <c r="P143" s="44"/>
+      <c r="Q143" s="10"/>
+    </row>
+    <row r="144" spans="1:17" ht="15.75">
+      <c r="A144" s="10"/>
+      <c r="B144" s="10"/>
+      <c r="C144" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="D144" s="46"/>
+      <c r="E144" s="46"/>
+      <c r="F144" s="46"/>
+      <c r="G144" s="47"/>
+      <c r="H144" s="45"/>
+      <c r="I144" s="46"/>
+      <c r="J144" s="46"/>
+      <c r="K144" s="46"/>
+      <c r="L144" s="46"/>
+      <c r="M144" s="47"/>
+      <c r="N144" s="42"/>
+      <c r="O144" s="43"/>
+      <c r="P144" s="44"/>
+      <c r="Q144" s="10"/>
+    </row>
+    <row r="145" spans="1:17" ht="15.75">
+      <c r="A145" s="10"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D145" s="73"/>
+      <c r="E145" s="73"/>
+      <c r="F145" s="73"/>
+      <c r="G145" s="74"/>
+      <c r="H145" s="45"/>
+      <c r="I145" s="46"/>
+      <c r="J145" s="46"/>
+      <c r="K145" s="46"/>
+      <c r="L145" s="46"/>
+      <c r="M145" s="47"/>
+      <c r="N145" s="42"/>
+      <c r="O145" s="43"/>
+      <c r="P145" s="44"/>
+      <c r="Q145" s="10"/>
+    </row>
+    <row r="146" spans="1:17" ht="15.75">
+      <c r="A146" s="10"/>
+      <c r="B146" s="10"/>
+      <c r="C146" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D146" s="46"/>
+      <c r="E146" s="46"/>
+      <c r="F146" s="46"/>
+      <c r="G146" s="47"/>
+      <c r="H146" s="45"/>
+      <c r="I146" s="46"/>
+      <c r="J146" s="46"/>
+      <c r="K146" s="46"/>
+      <c r="L146" s="46"/>
+      <c r="M146" s="47"/>
+      <c r="N146" s="42"/>
+      <c r="O146" s="43"/>
+      <c r="P146" s="44"/>
+      <c r="Q146" s="10"/>
+    </row>
+    <row r="147" spans="1:17" ht="15.75">
+      <c r="A147" s="10"/>
+      <c r="B147" s="10"/>
+      <c r="C147" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D147" s="75"/>
+      <c r="E147" s="75"/>
+      <c r="F147" s="75"/>
+      <c r="G147" s="75"/>
+      <c r="H147" s="45"/>
+      <c r="I147" s="46"/>
+      <c r="J147" s="46"/>
+      <c r="K147" s="46"/>
+      <c r="L147" s="46"/>
+      <c r="M147" s="47"/>
+      <c r="N147" s="42"/>
+      <c r="O147" s="43"/>
+      <c r="P147" s="44"/>
+      <c r="Q147" s="10"/>
+    </row>
+    <row r="148" spans="1:17" ht="15.75">
+      <c r="A148" s="10"/>
+      <c r="B148" s="10"/>
+      <c r="C148" s="45" t="s">
+        <v>368</v>
+      </c>
+      <c r="D148" s="46"/>
+      <c r="E148" s="46"/>
+      <c r="F148" s="46"/>
+      <c r="G148" s="47"/>
+      <c r="H148" s="45"/>
+      <c r="I148" s="46"/>
+      <c r="J148" s="46"/>
+      <c r="K148" s="46"/>
+      <c r="L148" s="46"/>
+      <c r="M148" s="47"/>
+      <c r="N148" s="42"/>
+      <c r="O148" s="43"/>
+      <c r="P148" s="44"/>
+      <c r="Q148" s="10"/>
+    </row>
+    <row r="149" spans="1:17" ht="15.75">
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D149" s="73"/>
+      <c r="E149" s="73"/>
+      <c r="F149" s="73"/>
+      <c r="G149" s="74"/>
+      <c r="H149" s="45"/>
+      <c r="I149" s="46"/>
+      <c r="J149" s="46"/>
+      <c r="K149" s="46"/>
+      <c r="L149" s="46"/>
+      <c r="M149" s="47"/>
+      <c r="N149" s="42"/>
+      <c r="O149" s="43"/>
+      <c r="P149" s="44"/>
+      <c r="Q149" s="10"/>
+    </row>
+    <row r="150" spans="1:17" ht="15.75">
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D150" s="46"/>
+      <c r="E150" s="46"/>
+      <c r="F150" s="46"/>
+      <c r="G150" s="47"/>
+      <c r="H150" s="45"/>
+      <c r="I150" s="46"/>
+      <c r="J150" s="46"/>
+      <c r="K150" s="46"/>
+      <c r="L150" s="46"/>
+      <c r="M150" s="47"/>
+      <c r="N150" s="42"/>
+      <c r="O150" s="43"/>
+      <c r="P150" s="44"/>
+      <c r="Q150" s="10"/>
+    </row>
+    <row r="151" spans="1:17" ht="15.75">
+      <c r="A151" s="10"/>
+      <c r="B151" s="10"/>
+      <c r="C151" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D151" s="75"/>
+      <c r="E151" s="75"/>
+      <c r="F151" s="75"/>
+      <c r="G151" s="75"/>
+      <c r="H151" s="45"/>
+      <c r="I151" s="46"/>
+      <c r="J151" s="46"/>
+      <c r="K151" s="46"/>
+      <c r="L151" s="46"/>
+      <c r="M151" s="47"/>
+      <c r="N151" s="42"/>
+      <c r="O151" s="43"/>
+      <c r="P151" s="44"/>
+      <c r="Q151" s="10"/>
+    </row>
+    <row r="152" spans="1:17" ht="15.75">
+      <c r="A152" s="10"/>
+      <c r="B152" s="10"/>
+      <c r="C152" s="45" t="s">
+        <v>369</v>
+      </c>
+      <c r="D152" s="46"/>
+      <c r="E152" s="46"/>
+      <c r="F152" s="46"/>
+      <c r="G152" s="47"/>
+      <c r="H152" s="45"/>
+      <c r="I152" s="46"/>
+      <c r="J152" s="46"/>
+      <c r="K152" s="46"/>
+      <c r="L152" s="46"/>
+      <c r="M152" s="47"/>
+      <c r="N152" s="42"/>
+      <c r="O152" s="43"/>
+      <c r="P152" s="44"/>
+      <c r="Q152" s="10"/>
+    </row>
+    <row r="153" spans="1:17" ht="15.75">
+      <c r="A153" s="10"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D153" s="73"/>
+      <c r="E153" s="73"/>
+      <c r="F153" s="73"/>
+      <c r="G153" s="74"/>
+      <c r="H153" s="45"/>
+      <c r="I153" s="46"/>
+      <c r="J153" s="46"/>
+      <c r="K153" s="46"/>
+      <c r="L153" s="46"/>
+      <c r="M153" s="47"/>
+      <c r="N153" s="42"/>
+      <c r="O153" s="43"/>
+      <c r="P153" s="44"/>
+      <c r="Q153" s="10"/>
+    </row>
+    <row r="154" spans="1:17" ht="15.75">
+      <c r="A154" s="10"/>
+      <c r="B154" s="10"/>
+      <c r="C154" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D154" s="46"/>
+      <c r="E154" s="46"/>
+      <c r="F154" s="46"/>
+      <c r="G154" s="47"/>
+      <c r="H154" s="45"/>
+      <c r="I154" s="46"/>
+      <c r="J154" s="46"/>
+      <c r="K154" s="46"/>
+      <c r="L154" s="46"/>
+      <c r="M154" s="47"/>
+      <c r="N154" s="42"/>
+      <c r="O154" s="43"/>
+      <c r="P154" s="44"/>
+      <c r="Q154" s="10"/>
+    </row>
+    <row r="155" spans="1:17" ht="15.75">
+      <c r="A155" s="10"/>
+      <c r="B155" s="10"/>
+      <c r="C155" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D155" s="75"/>
+      <c r="E155" s="75"/>
+      <c r="F155" s="75"/>
+      <c r="G155" s="75"/>
+      <c r="H155" s="45"/>
+      <c r="I155" s="46"/>
+      <c r="J155" s="46"/>
+      <c r="K155" s="46"/>
+      <c r="L155" s="46"/>
+      <c r="M155" s="47"/>
+      <c r="N155" s="42"/>
+      <c r="O155" s="43"/>
+      <c r="P155" s="44"/>
+      <c r="Q155" s="10"/>
+    </row>
+    <row r="156" spans="1:17" ht="15.75">
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="D156" s="46"/>
+      <c r="E156" s="46"/>
+      <c r="F156" s="46"/>
+      <c r="G156" s="47"/>
+      <c r="H156" s="45"/>
+      <c r="I156" s="46"/>
+      <c r="J156" s="46"/>
+      <c r="K156" s="46"/>
+      <c r="L156" s="46"/>
+      <c r="M156" s="47"/>
+      <c r="N156" s="42"/>
+      <c r="O156" s="43"/>
+      <c r="P156" s="44"/>
+      <c r="Q156" s="10"/>
+    </row>
+    <row r="157" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A157" s="10"/>
+      <c r="B157" s="10"/>
+      <c r="C157" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D157" s="73"/>
+      <c r="E157" s="73"/>
+      <c r="F157" s="73"/>
+      <c r="G157" s="74"/>
+      <c r="H157" s="45"/>
+      <c r="I157" s="46"/>
+      <c r="J157" s="46"/>
+      <c r="K157" s="46"/>
+      <c r="L157" s="46"/>
+      <c r="M157" s="47"/>
+      <c r="N157" s="42"/>
+      <c r="O157" s="43"/>
+      <c r="P157" s="44"/>
+      <c r="Q157" s="10"/>
+    </row>
+    <row r="158" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A158" s="10"/>
+      <c r="B158" s="10"/>
+      <c r="C158" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D158" s="46"/>
+      <c r="E158" s="46"/>
+      <c r="F158" s="46"/>
+      <c r="G158" s="47"/>
+      <c r="H158" s="45"/>
+      <c r="I158" s="46"/>
+      <c r="J158" s="46"/>
+      <c r="K158" s="46"/>
+      <c r="L158" s="46"/>
+      <c r="M158" s="47"/>
+      <c r="N158" s="42"/>
+      <c r="O158" s="43"/>
+      <c r="P158" s="44"/>
+      <c r="Q158" s="10"/>
+    </row>
+    <row r="159" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D159" s="75"/>
+      <c r="E159" s="75"/>
+      <c r="F159" s="75"/>
+      <c r="G159" s="75"/>
+      <c r="H159" s="45"/>
+      <c r="I159" s="46"/>
+      <c r="J159" s="46"/>
+      <c r="K159" s="46"/>
+      <c r="L159" s="46"/>
+      <c r="M159" s="47"/>
+      <c r="N159" s="42"/>
+      <c r="O159" s="43"/>
+      <c r="P159" s="44"/>
+      <c r="Q159" s="10"/>
+    </row>
+    <row r="160" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="45" t="s">
+        <v>371</v>
+      </c>
+      <c r="D160" s="46"/>
+      <c r="E160" s="46"/>
+      <c r="F160" s="46"/>
+      <c r="G160" s="47"/>
+      <c r="H160" s="45"/>
+      <c r="I160" s="46"/>
+      <c r="J160" s="46"/>
+      <c r="K160" s="46"/>
+      <c r="L160" s="46"/>
+      <c r="M160" s="47"/>
+      <c r="N160" s="42"/>
+      <c r="O160" s="43"/>
+      <c r="P160" s="44"/>
+      <c r="Q160" s="10"/>
+    </row>
+    <row r="161" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A161" s="10"/>
+      <c r="B161" s="10"/>
+      <c r="C161" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D161" s="73"/>
+      <c r="E161" s="73"/>
+      <c r="F161" s="73"/>
+      <c r="G161" s="74"/>
+      <c r="H161" s="45"/>
+      <c r="I161" s="46"/>
+      <c r="J161" s="46"/>
+      <c r="K161" s="46"/>
+      <c r="L161" s="46"/>
+      <c r="M161" s="47"/>
+      <c r="N161" s="42"/>
+      <c r="O161" s="43"/>
+      <c r="P161" s="44"/>
+      <c r="Q161" s="10"/>
+    </row>
+    <row r="162" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A162" s="10"/>
+      <c r="B162" s="10"/>
+      <c r="C162" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D162" s="46"/>
+      <c r="E162" s="46"/>
+      <c r="F162" s="46"/>
+      <c r="G162" s="47"/>
+      <c r="H162" s="45"/>
+      <c r="I162" s="46"/>
+      <c r="J162" s="46"/>
+      <c r="K162" s="46"/>
+      <c r="L162" s="46"/>
+      <c r="M162" s="47"/>
+      <c r="N162" s="42"/>
+      <c r="O162" s="43"/>
+      <c r="P162" s="44"/>
+      <c r="Q162" s="10"/>
+    </row>
+    <row r="163" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A163" s="10"/>
+      <c r="B163" s="10"/>
+      <c r="C163" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D163" s="75"/>
+      <c r="E163" s="75"/>
+      <c r="F163" s="75"/>
+      <c r="G163" s="75"/>
+      <c r="H163" s="45"/>
+      <c r="I163" s="46"/>
+      <c r="J163" s="46"/>
+      <c r="K163" s="46"/>
+      <c r="L163" s="46"/>
+      <c r="M163" s="47"/>
+      <c r="N163" s="42"/>
+      <c r="O163" s="43"/>
+      <c r="P163" s="44"/>
+      <c r="Q163" s="10"/>
+    </row>
+    <row r="164" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A164" s="10"/>
+      <c r="B164" s="10"/>
+      <c r="C164" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="D164" s="46"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="46"/>
+      <c r="G164" s="47"/>
+      <c r="H164" s="45"/>
+      <c r="I164" s="46"/>
+      <c r="J164" s="46"/>
+      <c r="K164" s="46"/>
+      <c r="L164" s="46"/>
+      <c r="M164" s="47"/>
+      <c r="N164" s="42"/>
+      <c r="O164" s="43"/>
+      <c r="P164" s="44"/>
+      <c r="Q164" s="10"/>
+    </row>
+    <row r="165" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A165" s="10"/>
+      <c r="B165" s="10"/>
+      <c r="C165" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D165" s="73"/>
+      <c r="E165" s="73"/>
+      <c r="F165" s="73"/>
+      <c r="G165" s="74"/>
+      <c r="H165" s="45"/>
+      <c r="I165" s="46"/>
+      <c r="J165" s="46"/>
+      <c r="K165" s="46"/>
+      <c r="L165" s="46"/>
+      <c r="M165" s="47"/>
+      <c r="N165" s="42"/>
+      <c r="O165" s="43"/>
+      <c r="P165" s="44"/>
+      <c r="Q165" s="10"/>
+    </row>
+    <row r="166" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A166" s="10"/>
+      <c r="B166" s="10"/>
+      <c r="C166" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D166" s="46"/>
+      <c r="E166" s="46"/>
+      <c r="F166" s="46"/>
+      <c r="G166" s="47"/>
+      <c r="H166" s="45"/>
+      <c r="I166" s="46"/>
+      <c r="J166" s="46"/>
+      <c r="K166" s="46"/>
+      <c r="L166" s="46"/>
+      <c r="M166" s="47"/>
+      <c r="N166" s="42"/>
+      <c r="O166" s="43"/>
+      <c r="P166" s="44"/>
+      <c r="Q166" s="10"/>
+    </row>
+    <row r="167" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A167" s="10"/>
+      <c r="B167" s="10"/>
+      <c r="C167" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D167" s="75"/>
+      <c r="E167" s="75"/>
+      <c r="F167" s="75"/>
+      <c r="G167" s="75"/>
+      <c r="H167" s="45"/>
+      <c r="I167" s="46"/>
+      <c r="J167" s="46"/>
+      <c r="K167" s="46"/>
+      <c r="L167" s="46"/>
+      <c r="M167" s="47"/>
+      <c r="N167" s="42"/>
+      <c r="O167" s="43"/>
+      <c r="P167" s="44"/>
+      <c r="Q167" s="10"/>
+    </row>
+    <row r="168" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A168" s="10"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="45" t="s">
+        <v>373</v>
+      </c>
+      <c r="D168" s="46"/>
+      <c r="E168" s="46"/>
+      <c r="F168" s="46"/>
+      <c r="G168" s="47"/>
+      <c r="H168" s="45"/>
+      <c r="I168" s="46"/>
+      <c r="J168" s="46"/>
+      <c r="K168" s="46"/>
+      <c r="L168" s="46"/>
+      <c r="M168" s="47"/>
+      <c r="N168" s="42"/>
+      <c r="O168" s="43"/>
+      <c r="P168" s="44"/>
+      <c r="Q168" s="10"/>
+    </row>
+    <row r="169" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A169" s="10"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D169" s="73"/>
+      <c r="E169" s="73"/>
+      <c r="F169" s="73"/>
+      <c r="G169" s="74"/>
+      <c r="H169" s="45"/>
+      <c r="I169" s="46"/>
+      <c r="J169" s="46"/>
+      <c r="K169" s="46"/>
+      <c r="L169" s="46"/>
+      <c r="M169" s="47"/>
+      <c r="N169" s="42"/>
+      <c r="O169" s="43"/>
+      <c r="P169" s="44"/>
+      <c r="Q169" s="10"/>
+    </row>
+    <row r="170" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A170" s="10"/>
+      <c r="B170" s="10"/>
+      <c r="C170" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D170" s="46"/>
+      <c r="E170" s="46"/>
+      <c r="F170" s="46"/>
+      <c r="G170" s="47"/>
+      <c r="H170" s="45"/>
+      <c r="I170" s="46"/>
+      <c r="J170" s="46"/>
+      <c r="K170" s="46"/>
+      <c r="L170" s="46"/>
+      <c r="M170" s="47"/>
+      <c r="N170" s="42"/>
+      <c r="O170" s="43"/>
+      <c r="P170" s="44"/>
+      <c r="Q170" s="10"/>
+    </row>
+    <row r="171" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A171" s="10"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D171" s="75"/>
+      <c r="E171" s="75"/>
+      <c r="F171" s="75"/>
+      <c r="G171" s="75"/>
+      <c r="H171" s="45"/>
+      <c r="I171" s="46"/>
+      <c r="J171" s="46"/>
+      <c r="K171" s="46"/>
+      <c r="L171" s="46"/>
+      <c r="M171" s="47"/>
+      <c r="N171" s="42"/>
+      <c r="O171" s="43"/>
+      <c r="P171" s="44"/>
+      <c r="Q171" s="10"/>
+    </row>
+    <row r="172" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A172" s="10"/>
+      <c r="B172" s="10"/>
+      <c r="C172" s="45" t="s">
+        <v>374</v>
+      </c>
+      <c r="D172" s="46"/>
+      <c r="E172" s="46"/>
+      <c r="F172" s="46"/>
+      <c r="G172" s="47"/>
+      <c r="H172" s="45"/>
+      <c r="I172" s="46"/>
+      <c r="J172" s="46"/>
+      <c r="K172" s="46"/>
+      <c r="L172" s="46"/>
+      <c r="M172" s="47"/>
+      <c r="N172" s="42"/>
+      <c r="O172" s="43"/>
+      <c r="P172" s="44"/>
+      <c r="Q172" s="10"/>
+    </row>
+    <row r="173" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A173" s="10"/>
+      <c r="B173" s="10"/>
+      <c r="C173" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D173" s="73"/>
+      <c r="E173" s="73"/>
+      <c r="F173" s="73"/>
+      <c r="G173" s="74"/>
+      <c r="H173" s="45"/>
+      <c r="I173" s="46"/>
+      <c r="J173" s="46"/>
+      <c r="K173" s="46"/>
+      <c r="L173" s="46"/>
+      <c r="M173" s="47"/>
+      <c r="N173" s="42"/>
+      <c r="O173" s="43"/>
+      <c r="P173" s="44"/>
+      <c r="Q173" s="10"/>
+    </row>
+    <row r="174" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A174" s="10"/>
+      <c r="B174" s="10"/>
+      <c r="C174" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D174" s="46"/>
+      <c r="E174" s="46"/>
+      <c r="F174" s="46"/>
+      <c r="G174" s="47"/>
+      <c r="H174" s="45"/>
+      <c r="I174" s="46"/>
+      <c r="J174" s="46"/>
+      <c r="K174" s="46"/>
+      <c r="L174" s="46"/>
+      <c r="M174" s="47"/>
+      <c r="N174" s="42"/>
+      <c r="O174" s="43"/>
+      <c r="P174" s="44"/>
+      <c r="Q174" s="10"/>
+    </row>
+    <row r="175" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A175" s="10"/>
+      <c r="B175" s="10"/>
+      <c r="C175" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D175" s="75"/>
+      <c r="E175" s="75"/>
+      <c r="F175" s="75"/>
+      <c r="G175" s="75"/>
+      <c r="H175" s="45"/>
+      <c r="I175" s="46"/>
+      <c r="J175" s="46"/>
+      <c r="K175" s="46"/>
+      <c r="L175" s="46"/>
+      <c r="M175" s="47"/>
+      <c r="N175" s="42"/>
+      <c r="O175" s="43"/>
+      <c r="P175" s="44"/>
+      <c r="Q175" s="10"/>
+    </row>
+    <row r="176" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A176" s="10"/>
+      <c r="B176" s="10"/>
+      <c r="C176" s="45" t="s">
+        <v>375</v>
+      </c>
+      <c r="D176" s="46"/>
+      <c r="E176" s="46"/>
+      <c r="F176" s="46"/>
+      <c r="G176" s="47"/>
+      <c r="H176" s="45"/>
+      <c r="I176" s="46"/>
+      <c r="J176" s="46"/>
+      <c r="K176" s="46"/>
+      <c r="L176" s="46"/>
+      <c r="M176" s="47"/>
+      <c r="N176" s="42"/>
+      <c r="O176" s="43"/>
+      <c r="P176" s="44"/>
+      <c r="Q176" s="10"/>
+    </row>
+    <row r="177" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A177" s="10"/>
+      <c r="B177" s="10"/>
+      <c r="C177" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D177" s="73"/>
+      <c r="E177" s="73"/>
+      <c r="F177" s="73"/>
+      <c r="G177" s="74"/>
+      <c r="H177" s="45"/>
+      <c r="I177" s="46"/>
+      <c r="J177" s="46"/>
+      <c r="K177" s="46"/>
+      <c r="L177" s="46"/>
+      <c r="M177" s="47"/>
+      <c r="N177" s="42"/>
+      <c r="O177" s="43"/>
+      <c r="P177" s="44"/>
+      <c r="Q177" s="10"/>
+    </row>
+    <row r="178" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A178" s="10"/>
+      <c r="B178" s="10"/>
+      <c r="C178" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D178" s="46"/>
+      <c r="E178" s="46"/>
+      <c r="F178" s="46"/>
+      <c r="G178" s="47"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="46"/>
+      <c r="J178" s="46"/>
+      <c r="K178" s="46"/>
+      <c r="L178" s="46"/>
+      <c r="M178" s="47"/>
+      <c r="N178" s="42"/>
+      <c r="O178" s="43"/>
+      <c r="P178" s="44"/>
+      <c r="Q178" s="10"/>
+    </row>
+    <row r="179" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A179" s="10"/>
+      <c r="B179" s="10"/>
+      <c r="C179" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D179" s="75"/>
+      <c r="E179" s="75"/>
+      <c r="F179" s="75"/>
+      <c r="G179" s="75"/>
+      <c r="H179" s="45"/>
+      <c r="I179" s="46"/>
+      <c r="J179" s="46"/>
+      <c r="K179" s="46"/>
+      <c r="L179" s="46"/>
+      <c r="M179" s="47"/>
+      <c r="N179" s="42"/>
+      <c r="O179" s="43"/>
+      <c r="P179" s="44"/>
+      <c r="Q179" s="10"/>
+    </row>
+    <row r="180" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A180" s="10"/>
+      <c r="B180" s="10"/>
+      <c r="C180" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="D180" s="46"/>
+      <c r="E180" s="46"/>
+      <c r="F180" s="46"/>
+      <c r="G180" s="47"/>
+      <c r="H180" s="45"/>
+      <c r="I180" s="46"/>
+      <c r="J180" s="46"/>
+      <c r="K180" s="46"/>
+      <c r="L180" s="46"/>
+      <c r="M180" s="47"/>
+      <c r="N180" s="42"/>
+      <c r="O180" s="43"/>
+      <c r="P180" s="44"/>
+      <c r="Q180" s="10"/>
+    </row>
+    <row r="181" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A181" s="10"/>
+      <c r="B181" s="10"/>
+      <c r="C181" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D181" s="73"/>
+      <c r="E181" s="73"/>
+      <c r="F181" s="73"/>
+      <c r="G181" s="74"/>
+      <c r="H181" s="45"/>
+      <c r="I181" s="46"/>
+      <c r="J181" s="46"/>
+      <c r="K181" s="46"/>
+      <c r="L181" s="46"/>
+      <c r="M181" s="47"/>
+      <c r="N181" s="42"/>
+      <c r="O181" s="43"/>
+      <c r="P181" s="44"/>
+      <c r="Q181" s="10"/>
+    </row>
+    <row r="182" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D182" s="46"/>
+      <c r="E182" s="46"/>
+      <c r="F182" s="46"/>
+      <c r="G182" s="47"/>
+      <c r="H182" s="45"/>
+      <c r="I182" s="46"/>
+      <c r="J182" s="46"/>
+      <c r="K182" s="46"/>
+      <c r="L182" s="46"/>
+      <c r="M182" s="47"/>
+      <c r="N182" s="42"/>
+      <c r="O182" s="43"/>
+      <c r="P182" s="44"/>
+      <c r="Q182" s="10"/>
+    </row>
+    <row r="183" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D183" s="75"/>
+      <c r="E183" s="75"/>
+      <c r="F183" s="75"/>
+      <c r="G183" s="75"/>
+      <c r="H183" s="45"/>
+      <c r="I183" s="46"/>
+      <c r="J183" s="46"/>
+      <c r="K183" s="46"/>
+      <c r="L183" s="46"/>
+      <c r="M183" s="47"/>
+      <c r="N183" s="42"/>
+      <c r="O183" s="43"/>
+      <c r="P183" s="44"/>
+      <c r="Q183" s="10"/>
+    </row>
+    <row r="184" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A184" s="10"/>
+      <c r="B184" s="10"/>
+      <c r="C184" s="45" t="s">
+        <v>377</v>
+      </c>
+      <c r="D184" s="46"/>
+      <c r="E184" s="46"/>
+      <c r="F184" s="46"/>
+      <c r="G184" s="47"/>
+      <c r="H184" s="45"/>
+      <c r="I184" s="46"/>
+      <c r="J184" s="46"/>
+      <c r="K184" s="46"/>
+      <c r="L184" s="46"/>
+      <c r="M184" s="47"/>
+      <c r="N184" s="42"/>
+      <c r="O184" s="43"/>
+      <c r="P184" s="44"/>
+      <c r="Q184" s="10"/>
+    </row>
+    <row r="185" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A185" s="10"/>
+      <c r="B185" s="10"/>
+      <c r="C185" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D185" s="73"/>
+      <c r="E185" s="73"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="74"/>
+      <c r="H185" s="45"/>
+      <c r="I185" s="46"/>
+      <c r="J185" s="46"/>
+      <c r="K185" s="46"/>
+      <c r="L185" s="46"/>
+      <c r="M185" s="47"/>
+      <c r="N185" s="42"/>
+      <c r="O185" s="43"/>
+      <c r="P185" s="44"/>
+      <c r="Q185" s="10"/>
+    </row>
+    <row r="186" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A186" s="10"/>
+      <c r="B186" s="10"/>
+      <c r="C186" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D186" s="46"/>
+      <c r="E186" s="46"/>
+      <c r="F186" s="46"/>
+      <c r="G186" s="47"/>
+      <c r="H186" s="45"/>
+      <c r="I186" s="46"/>
+      <c r="J186" s="46"/>
+      <c r="K186" s="46"/>
+      <c r="L186" s="46"/>
+      <c r="M186" s="47"/>
+      <c r="N186" s="42"/>
+      <c r="O186" s="43"/>
+      <c r="P186" s="44"/>
+      <c r="Q186" s="10"/>
+    </row>
+    <row r="187" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A187" s="10"/>
+      <c r="B187" s="10"/>
+      <c r="C187" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D187" s="75"/>
+      <c r="E187" s="75"/>
+      <c r="F187" s="75"/>
+      <c r="G187" s="75"/>
+      <c r="H187" s="45"/>
+      <c r="I187" s="46"/>
+      <c r="J187" s="46"/>
+      <c r="K187" s="46"/>
+      <c r="L187" s="46"/>
+      <c r="M187" s="47"/>
+      <c r="N187" s="42"/>
+      <c r="O187" s="43"/>
+      <c r="P187" s="44"/>
+      <c r="Q187" s="10"/>
+    </row>
+    <row r="188" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A188" s="10"/>
+      <c r="B188" s="10"/>
+      <c r="C188" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="D188" s="46"/>
+      <c r="E188" s="46"/>
+      <c r="F188" s="46"/>
+      <c r="G188" s="47"/>
+      <c r="H188" s="45"/>
+      <c r="I188" s="46"/>
+      <c r="J188" s="46"/>
+      <c r="K188" s="46"/>
+      <c r="L188" s="46"/>
+      <c r="M188" s="47"/>
+      <c r="N188" s="42"/>
+      <c r="O188" s="43"/>
+      <c r="P188" s="44"/>
+      <c r="Q188" s="10"/>
+    </row>
+    <row r="189" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A189" s="10"/>
+      <c r="B189" s="10"/>
+      <c r="C189" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D189" s="73"/>
+      <c r="E189" s="73"/>
+      <c r="F189" s="73"/>
+      <c r="G189" s="74"/>
+      <c r="H189" s="45"/>
+      <c r="I189" s="46"/>
+      <c r="J189" s="46"/>
+      <c r="K189" s="46"/>
+      <c r="L189" s="46"/>
+      <c r="M189" s="47"/>
+      <c r="N189" s="42"/>
+      <c r="O189" s="43"/>
+      <c r="P189" s="44"/>
+      <c r="Q189" s="10"/>
+    </row>
+    <row r="190" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A190" s="10"/>
+      <c r="B190" s="10"/>
+      <c r="C190" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D190" s="46"/>
+      <c r="E190" s="46"/>
+      <c r="F190" s="46"/>
+      <c r="G190" s="47"/>
+      <c r="H190" s="45"/>
+      <c r="I190" s="46"/>
+      <c r="J190" s="46"/>
+      <c r="K190" s="46"/>
+      <c r="L190" s="46"/>
+      <c r="M190" s="47"/>
+      <c r="N190" s="42"/>
+      <c r="O190" s="43"/>
+      <c r="P190" s="44"/>
+      <c r="Q190" s="10"/>
+    </row>
+    <row r="191" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A191" s="10"/>
+      <c r="B191" s="10"/>
+      <c r="C191" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D191" s="75"/>
+      <c r="E191" s="75"/>
+      <c r="F191" s="75"/>
+      <c r="G191" s="75"/>
+      <c r="H191" s="45"/>
+      <c r="I191" s="46"/>
+      <c r="J191" s="46"/>
+      <c r="K191" s="46"/>
+      <c r="L191" s="46"/>
+      <c r="M191" s="47"/>
+      <c r="N191" s="42"/>
+      <c r="O191" s="43"/>
+      <c r="P191" s="44"/>
+      <c r="Q191" s="10"/>
+    </row>
+    <row r="192" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A192" s="10"/>
+      <c r="B192" s="10"/>
+      <c r="C192" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="D192" s="46"/>
+      <c r="E192" s="46"/>
+      <c r="F192" s="46"/>
+      <c r="G192" s="47"/>
+      <c r="H192" s="45"/>
+      <c r="I192" s="46"/>
+      <c r="J192" s="46"/>
+      <c r="K192" s="46"/>
+      <c r="L192" s="46"/>
+      <c r="M192" s="47"/>
+      <c r="N192" s="42"/>
+      <c r="O192" s="43"/>
+      <c r="P192" s="44"/>
+      <c r="Q192" s="10"/>
+    </row>
+    <row r="193" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A193" s="10"/>
+      <c r="B193" s="10"/>
+      <c r="C193" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D193" s="73"/>
+      <c r="E193" s="73"/>
+      <c r="F193" s="73"/>
+      <c r="G193" s="74"/>
+      <c r="H193" s="45"/>
+      <c r="I193" s="46"/>
+      <c r="J193" s="46"/>
+      <c r="K193" s="46"/>
+      <c r="L193" s="46"/>
+      <c r="M193" s="47"/>
+      <c r="N193" s="42"/>
+      <c r="O193" s="43"/>
+      <c r="P193" s="44"/>
+      <c r="Q193" s="10"/>
+    </row>
+    <row r="194" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A194" s="10"/>
+      <c r="B194" s="10"/>
+      <c r="C194" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D194" s="46"/>
+      <c r="E194" s="46"/>
+      <c r="F194" s="46"/>
+      <c r="G194" s="47"/>
+      <c r="H194" s="45"/>
+      <c r="I194" s="46"/>
+      <c r="J194" s="46"/>
+      <c r="K194" s="46"/>
+      <c r="L194" s="46"/>
+      <c r="M194" s="47"/>
+      <c r="N194" s="42"/>
+      <c r="O194" s="43"/>
+      <c r="P194" s="44"/>
+      <c r="Q194" s="10"/>
+    </row>
+    <row r="195" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A195" s="10"/>
+      <c r="B195" s="10"/>
+      <c r="C195" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D195" s="75"/>
+      <c r="E195" s="75"/>
+      <c r="F195" s="75"/>
+      <c r="G195" s="75"/>
+      <c r="H195" s="45"/>
+      <c r="I195" s="46"/>
+      <c r="J195" s="46"/>
+      <c r="K195" s="46"/>
+      <c r="L195" s="46"/>
+      <c r="M195" s="47"/>
+      <c r="N195" s="42"/>
+      <c r="O195" s="43"/>
+      <c r="P195" s="44"/>
+      <c r="Q195" s="10"/>
+    </row>
+    <row r="196" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A196" s="10"/>
+      <c r="B196" s="10"/>
+      <c r="C196" s="45" t="s">
+        <v>380</v>
+      </c>
+      <c r="D196" s="46"/>
+      <c r="E196" s="46"/>
+      <c r="F196" s="46"/>
+      <c r="G196" s="47"/>
+      <c r="H196" s="45"/>
+      <c r="I196" s="46"/>
+      <c r="J196" s="46"/>
+      <c r="K196" s="46"/>
+      <c r="L196" s="46"/>
+      <c r="M196" s="47"/>
+      <c r="N196" s="42"/>
+      <c r="O196" s="43"/>
+      <c r="P196" s="44"/>
+      <c r="Q196" s="10"/>
+    </row>
+    <row r="197" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A197" s="10"/>
+      <c r="B197" s="10"/>
+      <c r="C197" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D197" s="73"/>
+      <c r="E197" s="73"/>
+      <c r="F197" s="73"/>
+      <c r="G197" s="74"/>
+      <c r="H197" s="45"/>
+      <c r="I197" s="46"/>
+      <c r="J197" s="46"/>
+      <c r="K197" s="46"/>
+      <c r="L197" s="46"/>
+      <c r="M197" s="47"/>
+      <c r="N197" s="42"/>
+      <c r="O197" s="43"/>
+      <c r="P197" s="44"/>
+      <c r="Q197" s="10"/>
+    </row>
+    <row r="198" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A198" s="10"/>
+      <c r="B198" s="10"/>
+      <c r="C198" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D198" s="46"/>
+      <c r="E198" s="46"/>
+      <c r="F198" s="46"/>
+      <c r="G198" s="47"/>
+      <c r="H198" s="45"/>
+      <c r="I198" s="46"/>
+      <c r="J198" s="46"/>
+      <c r="K198" s="46"/>
+      <c r="L198" s="46"/>
+      <c r="M198" s="47"/>
+      <c r="N198" s="42"/>
+      <c r="O198" s="43"/>
+      <c r="P198" s="44"/>
+      <c r="Q198" s="10"/>
+    </row>
+    <row r="199" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A199" s="10"/>
+      <c r="B199" s="10"/>
+      <c r="C199" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D199" s="75"/>
+      <c r="E199" s="75"/>
+      <c r="F199" s="75"/>
+      <c r="G199" s="75"/>
+      <c r="H199" s="45"/>
+      <c r="I199" s="46"/>
+      <c r="J199" s="46"/>
+      <c r="K199" s="46"/>
+      <c r="L199" s="46"/>
+      <c r="M199" s="47"/>
+      <c r="N199" s="42"/>
+      <c r="O199" s="43"/>
+      <c r="P199" s="44"/>
+      <c r="Q199" s="10"/>
+    </row>
+    <row r="200" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A200" s="10"/>
+      <c r="B200" s="10"/>
+      <c r="C200" s="45" t="s">
+        <v>381</v>
+      </c>
+      <c r="D200" s="46"/>
+      <c r="E200" s="46"/>
+      <c r="F200" s="46"/>
+      <c r="G200" s="47"/>
+      <c r="H200" s="45"/>
+      <c r="I200" s="46"/>
+      <c r="J200" s="46"/>
+      <c r="K200" s="46"/>
+      <c r="L200" s="46"/>
+      <c r="M200" s="47"/>
+      <c r="N200" s="42"/>
+      <c r="O200" s="43"/>
+      <c r="P200" s="44"/>
+      <c r="Q200" s="10"/>
+    </row>
+    <row r="201" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A201" s="10"/>
+      <c r="B201" s="10"/>
+      <c r="C201" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D201" s="73"/>
+      <c r="E201" s="73"/>
+      <c r="F201" s="73"/>
+      <c r="G201" s="74"/>
+      <c r="H201" s="45"/>
+      <c r="I201" s="46"/>
+      <c r="J201" s="46"/>
+      <c r="K201" s="46"/>
+      <c r="L201" s="46"/>
+      <c r="M201" s="47"/>
+      <c r="N201" s="42"/>
+      <c r="O201" s="43"/>
+      <c r="P201" s="44"/>
+      <c r="Q201" s="10"/>
+    </row>
+    <row r="202" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A202" s="10"/>
+      <c r="B202" s="10"/>
+      <c r="C202" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D202" s="46"/>
+      <c r="E202" s="46"/>
+      <c r="F202" s="46"/>
+      <c r="G202" s="47"/>
+      <c r="H202" s="45"/>
+      <c r="I202" s="46"/>
+      <c r="J202" s="46"/>
+      <c r="K202" s="46"/>
+      <c r="L202" s="46"/>
+      <c r="M202" s="47"/>
+      <c r="N202" s="42"/>
+      <c r="O202" s="43"/>
+      <c r="P202" s="44"/>
+      <c r="Q202" s="10"/>
+    </row>
+    <row r="203" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A203" s="10"/>
+      <c r="B203" s="10"/>
+      <c r="C203" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D203" s="75"/>
+      <c r="E203" s="75"/>
+      <c r="F203" s="75"/>
+      <c r="G203" s="75"/>
+      <c r="H203" s="45"/>
+      <c r="I203" s="46"/>
+      <c r="J203" s="46"/>
+      <c r="K203" s="46"/>
+      <c r="L203" s="46"/>
+      <c r="M203" s="47"/>
+      <c r="N203" s="42"/>
+      <c r="O203" s="43"/>
+      <c r="P203" s="44"/>
+      <c r="Q203" s="10"/>
+    </row>
+    <row r="204" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A204" s="10"/>
+      <c r="B204" s="10"/>
+      <c r="C204" s="45" t="s">
+        <v>382</v>
+      </c>
+      <c r="D204" s="46"/>
+      <c r="E204" s="46"/>
+      <c r="F204" s="46"/>
+      <c r="G204" s="47"/>
+      <c r="H204" s="45"/>
+      <c r="I204" s="46"/>
+      <c r="J204" s="46"/>
+      <c r="K204" s="46"/>
+      <c r="L204" s="46"/>
+      <c r="M204" s="47"/>
+      <c r="N204" s="42"/>
+      <c r="O204" s="43"/>
+      <c r="P204" s="44"/>
+      <c r="Q204" s="10"/>
+    </row>
+    <row r="205" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A205" s="10"/>
+      <c r="B205" s="10"/>
+      <c r="C205" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D205" s="73"/>
+      <c r="E205" s="73"/>
+      <c r="F205" s="73"/>
+      <c r="G205" s="74"/>
+      <c r="H205" s="45"/>
+      <c r="I205" s="46"/>
+      <c r="J205" s="46"/>
+      <c r="K205" s="46"/>
+      <c r="L205" s="46"/>
+      <c r="M205" s="47"/>
+      <c r="N205" s="42"/>
+      <c r="O205" s="43"/>
+      <c r="P205" s="44"/>
+      <c r="Q205" s="10"/>
+    </row>
+    <row r="206" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A206" s="10"/>
+      <c r="B206" s="10"/>
+      <c r="C206" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D206" s="46"/>
+      <c r="E206" s="46"/>
+      <c r="F206" s="46"/>
+      <c r="G206" s="47"/>
+      <c r="H206" s="45"/>
+      <c r="I206" s="46"/>
+      <c r="J206" s="46"/>
+      <c r="K206" s="46"/>
+      <c r="L206" s="46"/>
+      <c r="M206" s="47"/>
+      <c r="N206" s="42"/>
+      <c r="O206" s="43"/>
+      <c r="P206" s="44"/>
+      <c r="Q206" s="10"/>
+    </row>
+    <row r="207" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A207" s="10"/>
+      <c r="B207" s="10"/>
+      <c r="C207" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D207" s="75"/>
+      <c r="E207" s="75"/>
+      <c r="F207" s="75"/>
+      <c r="G207" s="75"/>
+      <c r="H207" s="45"/>
+      <c r="I207" s="46"/>
+      <c r="J207" s="46"/>
+      <c r="K207" s="46"/>
+      <c r="L207" s="46"/>
+      <c r="M207" s="47"/>
+      <c r="N207" s="42"/>
+      <c r="O207" s="43"/>
+      <c r="P207" s="44"/>
+      <c r="Q207" s="10"/>
+    </row>
+    <row r="208" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A208" s="10"/>
+      <c r="B208" s="10"/>
+      <c r="C208" s="45" t="s">
+        <v>383</v>
+      </c>
+      <c r="D208" s="46"/>
+      <c r="E208" s="46"/>
+      <c r="F208" s="46"/>
+      <c r="G208" s="47"/>
+      <c r="H208" s="45"/>
+      <c r="I208" s="46"/>
+      <c r="J208" s="46"/>
+      <c r="K208" s="46"/>
+      <c r="L208" s="46"/>
+      <c r="M208" s="47"/>
+      <c r="N208" s="42"/>
+      <c r="O208" s="43"/>
+      <c r="P208" s="44"/>
+      <c r="Q208" s="10"/>
+    </row>
+    <row r="209" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A209" s="10"/>
+      <c r="B209" s="10"/>
+      <c r="C209" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D209" s="73"/>
+      <c r="E209" s="73"/>
+      <c r="F209" s="73"/>
+      <c r="G209" s="74"/>
+      <c r="H209" s="45"/>
+      <c r="I209" s="46"/>
+      <c r="J209" s="46"/>
+      <c r="K209" s="46"/>
+      <c r="L209" s="46"/>
+      <c r="M209" s="47"/>
+      <c r="N209" s="42"/>
+      <c r="O209" s="43"/>
+      <c r="P209" s="44"/>
+      <c r="Q209" s="10"/>
+    </row>
+    <row r="210" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A210" s="10"/>
+      <c r="B210" s="10"/>
+      <c r="C210" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D210" s="46"/>
+      <c r="E210" s="46"/>
+      <c r="F210" s="46"/>
+      <c r="G210" s="47"/>
+      <c r="H210" s="45"/>
+      <c r="I210" s="46"/>
+      <c r="J210" s="46"/>
+      <c r="K210" s="46"/>
+      <c r="L210" s="46"/>
+      <c r="M210" s="47"/>
+      <c r="N210" s="42"/>
+      <c r="O210" s="43"/>
+      <c r="P210" s="44"/>
+      <c r="Q210" s="10"/>
+    </row>
+    <row r="211" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A211" s="10"/>
+      <c r="B211" s="10"/>
+      <c r="C211" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D211" s="75"/>
+      <c r="E211" s="75"/>
+      <c r="F211" s="75"/>
+      <c r="G211" s="75"/>
+      <c r="H211" s="45"/>
+      <c r="I211" s="46"/>
+      <c r="J211" s="46"/>
+      <c r="K211" s="46"/>
+      <c r="L211" s="46"/>
+      <c r="M211" s="47"/>
+      <c r="N211" s="42"/>
+      <c r="O211" s="43"/>
+      <c r="P211" s="44"/>
+      <c r="Q211" s="10"/>
+    </row>
+    <row r="212" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A212" s="10"/>
+      <c r="B212" s="10"/>
+      <c r="C212" s="45" t="s">
+        <v>384</v>
+      </c>
+      <c r="D212" s="46"/>
+      <c r="E212" s="46"/>
+      <c r="F212" s="46"/>
+      <c r="G212" s="47"/>
+      <c r="H212" s="45"/>
+      <c r="I212" s="46"/>
+      <c r="J212" s="46"/>
+      <c r="K212" s="46"/>
+      <c r="L212" s="46"/>
+      <c r="M212" s="47"/>
+      <c r="N212" s="42"/>
+      <c r="O212" s="43"/>
+      <c r="P212" s="44"/>
+      <c r="Q212" s="10"/>
+    </row>
+    <row r="213" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A213" s="10"/>
+      <c r="B213" s="10"/>
+      <c r="C213" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D213" s="73"/>
+      <c r="E213" s="73"/>
+      <c r="F213" s="73"/>
+      <c r="G213" s="74"/>
+      <c r="H213" s="45"/>
+      <c r="I213" s="46"/>
+      <c r="J213" s="46"/>
+      <c r="K213" s="46"/>
+      <c r="L213" s="46"/>
+      <c r="M213" s="47"/>
+      <c r="N213" s="42"/>
+      <c r="O213" s="43"/>
+      <c r="P213" s="44"/>
+      <c r="Q213" s="10"/>
+    </row>
+    <row r="214" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A214" s="10"/>
+      <c r="B214" s="10"/>
+      <c r="C214" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D214" s="46"/>
+      <c r="E214" s="46"/>
+      <c r="F214" s="46"/>
+      <c r="G214" s="47"/>
+      <c r="H214" s="45"/>
+      <c r="I214" s="46"/>
+      <c r="J214" s="46"/>
+      <c r="K214" s="46"/>
+      <c r="L214" s="46"/>
+      <c r="M214" s="47"/>
+      <c r="N214" s="42"/>
+      <c r="O214" s="43"/>
+      <c r="P214" s="44"/>
+      <c r="Q214" s="10"/>
+    </row>
+    <row r="215" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A215" s="10"/>
+      <c r="B215" s="10"/>
+      <c r="C215" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D215" s="75"/>
+      <c r="E215" s="75"/>
+      <c r="F215" s="75"/>
+      <c r="G215" s="75"/>
+      <c r="H215" s="45"/>
+      <c r="I215" s="46"/>
+      <c r="J215" s="46"/>
+      <c r="K215" s="46"/>
+      <c r="L215" s="46"/>
+      <c r="M215" s="47"/>
+      <c r="N215" s="42"/>
+      <c r="O215" s="43"/>
+      <c r="P215" s="44"/>
+      <c r="Q215" s="10"/>
+    </row>
+    <row r="216" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A216" s="10"/>
+      <c r="B216" s="10"/>
+      <c r="C216" s="45" t="s">
+        <v>385</v>
+      </c>
+      <c r="D216" s="46"/>
+      <c r="E216" s="46"/>
+      <c r="F216" s="46"/>
+      <c r="G216" s="47"/>
+      <c r="H216" s="45"/>
+      <c r="I216" s="46"/>
+      <c r="J216" s="46"/>
+      <c r="K216" s="46"/>
+      <c r="L216" s="46"/>
+      <c r="M216" s="47"/>
+      <c r="N216" s="42"/>
+      <c r="O216" s="43"/>
+      <c r="P216" s="44"/>
+      <c r="Q216" s="10"/>
+    </row>
+    <row r="217" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A217" s="10"/>
+      <c r="B217" s="10"/>
+      <c r="C217" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D217" s="73"/>
+      <c r="E217" s="73"/>
+      <c r="F217" s="73"/>
+      <c r="G217" s="74"/>
+      <c r="H217" s="45"/>
+      <c r="I217" s="46"/>
+      <c r="J217" s="46"/>
+      <c r="K217" s="46"/>
+      <c r="L217" s="46"/>
+      <c r="M217" s="47"/>
+      <c r="N217" s="42"/>
+      <c r="O217" s="43"/>
+      <c r="P217" s="44"/>
+      <c r="Q217" s="10"/>
+    </row>
+    <row r="218" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A218" s="10"/>
+      <c r="B218" s="10"/>
+      <c r="C218" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D218" s="46"/>
+      <c r="E218" s="46"/>
+      <c r="F218" s="46"/>
+      <c r="G218" s="47"/>
+      <c r="H218" s="45"/>
+      <c r="I218" s="46"/>
+      <c r="J218" s="46"/>
+      <c r="K218" s="46"/>
+      <c r="L218" s="46"/>
+      <c r="M218" s="47"/>
+      <c r="N218" s="42"/>
+      <c r="O218" s="43"/>
+      <c r="P218" s="44"/>
+      <c r="Q218" s="10"/>
+    </row>
+    <row r="219" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A219" s="10"/>
+      <c r="B219" s="10"/>
+      <c r="C219" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D219" s="75"/>
+      <c r="E219" s="75"/>
+      <c r="F219" s="75"/>
+      <c r="G219" s="75"/>
+      <c r="H219" s="45"/>
+      <c r="I219" s="46"/>
+      <c r="J219" s="46"/>
+      <c r="K219" s="46"/>
+      <c r="L219" s="46"/>
+      <c r="M219" s="47"/>
+      <c r="N219" s="42"/>
+      <c r="O219" s="43"/>
+      <c r="P219" s="44"/>
+      <c r="Q219" s="10"/>
+    </row>
+    <row r="220" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A220" s="10"/>
+      <c r="B220" s="10"/>
+      <c r="C220" s="45" t="s">
+        <v>386</v>
+      </c>
+      <c r="D220" s="46"/>
+      <c r="E220" s="46"/>
+      <c r="F220" s="46"/>
+      <c r="G220" s="47"/>
+      <c r="H220" s="45"/>
+      <c r="I220" s="46"/>
+      <c r="J220" s="46"/>
+      <c r="K220" s="46"/>
+      <c r="L220" s="46"/>
+      <c r="M220" s="47"/>
+      <c r="N220" s="42"/>
+      <c r="O220" s="43"/>
+      <c r="P220" s="44"/>
+      <c r="Q220" s="10"/>
+    </row>
+    <row r="221" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A221" s="10"/>
+      <c r="B221" s="10"/>
+      <c r="C221" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D221" s="73"/>
+      <c r="E221" s="73"/>
+      <c r="F221" s="73"/>
+      <c r="G221" s="74"/>
+      <c r="H221" s="45"/>
+      <c r="I221" s="46"/>
+      <c r="J221" s="46"/>
+      <c r="K221" s="46"/>
+      <c r="L221" s="46"/>
+      <c r="M221" s="47"/>
+      <c r="N221" s="42"/>
+      <c r="O221" s="43"/>
+      <c r="P221" s="44"/>
+      <c r="Q221" s="10"/>
+    </row>
+    <row r="222" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A222" s="10"/>
+      <c r="B222" s="10"/>
+      <c r="C222" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D222" s="46"/>
+      <c r="E222" s="46"/>
+      <c r="F222" s="46"/>
+      <c r="G222" s="47"/>
+      <c r="H222" s="45"/>
+      <c r="I222" s="46"/>
+      <c r="J222" s="46"/>
+      <c r="K222" s="46"/>
+      <c r="L222" s="46"/>
+      <c r="M222" s="47"/>
+      <c r="N222" s="42"/>
+      <c r="O222" s="43"/>
+      <c r="P222" s="44"/>
+      <c r="Q222" s="10"/>
+    </row>
+    <row r="223" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A223" s="10"/>
+      <c r="B223" s="10"/>
+      <c r="C223" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D223" s="75"/>
+      <c r="E223" s="75"/>
+      <c r="F223" s="75"/>
+      <c r="G223" s="75"/>
+      <c r="H223" s="45"/>
+      <c r="I223" s="46"/>
+      <c r="J223" s="46"/>
+      <c r="K223" s="46"/>
+      <c r="L223" s="46"/>
+      <c r="M223" s="47"/>
+      <c r="N223" s="42"/>
+      <c r="O223" s="43"/>
+      <c r="P223" s="44"/>
+      <c r="Q223" s="10"/>
+    </row>
+    <row r="224" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A224" s="10"/>
+      <c r="B224" s="10"/>
+      <c r="C224" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="D224" s="46"/>
+      <c r="E224" s="46"/>
+      <c r="F224" s="46"/>
+      <c r="G224" s="47"/>
+      <c r="H224" s="45"/>
+      <c r="I224" s="46"/>
+      <c r="J224" s="46"/>
+      <c r="K224" s="46"/>
+      <c r="L224" s="46"/>
+      <c r="M224" s="47"/>
+      <c r="N224" s="42"/>
+      <c r="O224" s="43"/>
+      <c r="P224" s="44"/>
+      <c r="Q224" s="10"/>
+    </row>
+    <row r="225" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A225" s="10"/>
+      <c r="B225" s="10"/>
+      <c r="C225" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D225" s="73"/>
+      <c r="E225" s="73"/>
+      <c r="F225" s="73"/>
+      <c r="G225" s="74"/>
+      <c r="H225" s="45"/>
+      <c r="I225" s="46"/>
+      <c r="J225" s="46"/>
+      <c r="K225" s="46"/>
+      <c r="L225" s="46"/>
+      <c r="M225" s="47"/>
+      <c r="N225" s="42"/>
+      <c r="O225" s="43"/>
+      <c r="P225" s="44"/>
+      <c r="Q225" s="10"/>
+    </row>
+    <row r="226" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A226" s="10"/>
+      <c r="B226" s="10"/>
+      <c r="C226" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D226" s="46"/>
+      <c r="E226" s="46"/>
+      <c r="F226" s="46"/>
+      <c r="G226" s="47"/>
+      <c r="H226" s="45"/>
+      <c r="I226" s="46"/>
+      <c r="J226" s="46"/>
+      <c r="K226" s="46"/>
+      <c r="L226" s="46"/>
+      <c r="M226" s="47"/>
+      <c r="N226" s="42"/>
+      <c r="O226" s="43"/>
+      <c r="P226" s="44"/>
+      <c r="Q226" s="10"/>
+    </row>
+    <row r="227" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A227" s="10"/>
+      <c r="B227" s="10"/>
+      <c r="C227" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="D227" s="75"/>
+      <c r="E227" s="75"/>
+      <c r="F227" s="75"/>
+      <c r="G227" s="75"/>
+      <c r="H227" s="45"/>
+      <c r="I227" s="46"/>
+      <c r="J227" s="46"/>
+      <c r="K227" s="46"/>
+      <c r="L227" s="46"/>
+      <c r="M227" s="47"/>
+      <c r="N227" s="42"/>
+      <c r="O227" s="43"/>
+      <c r="P227" s="44"/>
+      <c r="Q227" s="10"/>
+    </row>
+    <row r="228" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A228" s="10"/>
+      <c r="B228" s="10"/>
+      <c r="C228" s="45" t="s">
+        <v>388</v>
+      </c>
+      <c r="D228" s="46"/>
+      <c r="E228" s="46"/>
+      <c r="F228" s="46"/>
+      <c r="G228" s="47"/>
+      <c r="H228" s="45"/>
+      <c r="I228" s="46"/>
+      <c r="J228" s="46"/>
+      <c r="K228" s="46"/>
+      <c r="L228" s="46"/>
+      <c r="M228" s="47"/>
+      <c r="N228" s="42"/>
+      <c r="O228" s="43"/>
+      <c r="P228" s="44"/>
+      <c r="Q228" s="10"/>
+    </row>
+    <row r="229" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A229" s="10"/>
+      <c r="B229" s="10"/>
+      <c r="C229" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D229" s="73"/>
+      <c r="E229" s="73"/>
+      <c r="F229" s="73"/>
+      <c r="G229" s="74"/>
+      <c r="H229" s="45"/>
+      <c r="I229" s="46"/>
+      <c r="J229" s="46"/>
+      <c r="K229" s="46"/>
+      <c r="L229" s="46"/>
+      <c r="M229" s="47"/>
+      <c r="N229" s="42"/>
+      <c r="O229" s="43"/>
+      <c r="P229" s="44"/>
+      <c r="Q229" s="10"/>
+    </row>
+    <row r="230" spans="1:17" ht="11.25" customHeight="1">
+      <c r="A230" s="10"/>
+      <c r="B230" s="10"/>
+      <c r="C230" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="D230" s="46"/>
+      <c r="E230" s="46"/>
+      <c r="F230" s="46"/>
+      <c r="G230" s="47"/>
+      <c r="H230" s="45"/>
+      <c r="I230" s="46"/>
+      <c r="J230" s="46"/>
+      <c r="K230" s="46"/>
+      <c r="L230" s="46"/>
+      <c r="M230" s="47"/>
+      <c r="N230" s="42"/>
+      <c r="O230" s="43"/>
+      <c r="P230" s="44"/>
+      <c r="Q230" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="224">
+  <mergeCells count="740">
+    <mergeCell ref="C230:G230"/>
+    <mergeCell ref="H230:M230"/>
+    <mergeCell ref="N230:P230"/>
+    <mergeCell ref="C227:G227"/>
+    <mergeCell ref="H227:M227"/>
+    <mergeCell ref="N227:P227"/>
+    <mergeCell ref="C228:G228"/>
+    <mergeCell ref="H228:M228"/>
+    <mergeCell ref="N228:P228"/>
+    <mergeCell ref="C229:G229"/>
+    <mergeCell ref="H229:M229"/>
+    <mergeCell ref="N229:P229"/>
+    <mergeCell ref="C224:G224"/>
+    <mergeCell ref="H224:M224"/>
+    <mergeCell ref="N224:P224"/>
+    <mergeCell ref="C225:G225"/>
+    <mergeCell ref="H225:M225"/>
+    <mergeCell ref="N225:P225"/>
+    <mergeCell ref="C226:G226"/>
+    <mergeCell ref="H226:M226"/>
+    <mergeCell ref="N226:P226"/>
+    <mergeCell ref="C221:G221"/>
+    <mergeCell ref="H221:M221"/>
+    <mergeCell ref="N221:P221"/>
+    <mergeCell ref="C222:G222"/>
+    <mergeCell ref="H222:M222"/>
+    <mergeCell ref="N222:P222"/>
+    <mergeCell ref="C223:G223"/>
+    <mergeCell ref="H223:M223"/>
+    <mergeCell ref="N223:P223"/>
+    <mergeCell ref="C218:G218"/>
+    <mergeCell ref="H218:M218"/>
+    <mergeCell ref="N218:P218"/>
+    <mergeCell ref="C219:G219"/>
+    <mergeCell ref="H219:M219"/>
+    <mergeCell ref="N219:P219"/>
+    <mergeCell ref="C220:G220"/>
+    <mergeCell ref="H220:M220"/>
+    <mergeCell ref="N220:P220"/>
+    <mergeCell ref="C215:G215"/>
+    <mergeCell ref="H215:M215"/>
+    <mergeCell ref="N215:P215"/>
+    <mergeCell ref="C216:G216"/>
+    <mergeCell ref="H216:M216"/>
+    <mergeCell ref="N216:P216"/>
+    <mergeCell ref="C217:G217"/>
+    <mergeCell ref="H217:M217"/>
+    <mergeCell ref="N217:P217"/>
+    <mergeCell ref="C212:G212"/>
+    <mergeCell ref="H212:M212"/>
+    <mergeCell ref="N212:P212"/>
+    <mergeCell ref="C213:G213"/>
+    <mergeCell ref="H213:M213"/>
+    <mergeCell ref="N213:P213"/>
+    <mergeCell ref="C214:G214"/>
+    <mergeCell ref="H214:M214"/>
+    <mergeCell ref="N214:P214"/>
+    <mergeCell ref="C209:G209"/>
+    <mergeCell ref="H209:M209"/>
+    <mergeCell ref="N209:P209"/>
+    <mergeCell ref="C210:G210"/>
+    <mergeCell ref="H210:M210"/>
+    <mergeCell ref="N210:P210"/>
+    <mergeCell ref="C211:G211"/>
+    <mergeCell ref="H211:M211"/>
+    <mergeCell ref="N211:P211"/>
+    <mergeCell ref="C206:G206"/>
+    <mergeCell ref="H206:M206"/>
+    <mergeCell ref="N206:P206"/>
+    <mergeCell ref="C207:G207"/>
+    <mergeCell ref="H207:M207"/>
+    <mergeCell ref="N207:P207"/>
+    <mergeCell ref="C208:G208"/>
+    <mergeCell ref="H208:M208"/>
+    <mergeCell ref="N208:P208"/>
+    <mergeCell ref="C203:G203"/>
+    <mergeCell ref="H203:M203"/>
+    <mergeCell ref="N203:P203"/>
+    <mergeCell ref="C204:G204"/>
+    <mergeCell ref="H204:M204"/>
+    <mergeCell ref="N204:P204"/>
+    <mergeCell ref="C205:G205"/>
+    <mergeCell ref="H205:M205"/>
+    <mergeCell ref="N205:P205"/>
+    <mergeCell ref="C200:G200"/>
+    <mergeCell ref="H200:M200"/>
+    <mergeCell ref="N200:P200"/>
+    <mergeCell ref="C201:G201"/>
+    <mergeCell ref="H201:M201"/>
+    <mergeCell ref="N201:P201"/>
+    <mergeCell ref="C202:G202"/>
+    <mergeCell ref="H202:M202"/>
+    <mergeCell ref="N202:P202"/>
+    <mergeCell ref="C197:G197"/>
+    <mergeCell ref="H197:M197"/>
+    <mergeCell ref="N197:P197"/>
+    <mergeCell ref="C198:G198"/>
+    <mergeCell ref="H198:M198"/>
+    <mergeCell ref="N198:P198"/>
+    <mergeCell ref="C199:G199"/>
+    <mergeCell ref="H199:M199"/>
+    <mergeCell ref="N199:P199"/>
+    <mergeCell ref="C194:G194"/>
+    <mergeCell ref="H194:M194"/>
+    <mergeCell ref="N194:P194"/>
+    <mergeCell ref="C195:G195"/>
+    <mergeCell ref="H195:M195"/>
+    <mergeCell ref="N195:P195"/>
+    <mergeCell ref="C196:G196"/>
+    <mergeCell ref="H196:M196"/>
+    <mergeCell ref="N196:P196"/>
+    <mergeCell ref="C191:G191"/>
+    <mergeCell ref="H191:M191"/>
+    <mergeCell ref="N191:P191"/>
+    <mergeCell ref="C192:G192"/>
+    <mergeCell ref="H192:M192"/>
+    <mergeCell ref="N192:P192"/>
+    <mergeCell ref="C193:G193"/>
+    <mergeCell ref="H193:M193"/>
+    <mergeCell ref="N193:P193"/>
+    <mergeCell ref="C188:G188"/>
+    <mergeCell ref="H188:M188"/>
+    <mergeCell ref="N188:P188"/>
+    <mergeCell ref="C189:G189"/>
+    <mergeCell ref="H189:M189"/>
+    <mergeCell ref="N189:P189"/>
+    <mergeCell ref="C190:G190"/>
+    <mergeCell ref="H190:M190"/>
+    <mergeCell ref="N190:P190"/>
+    <mergeCell ref="C185:G185"/>
+    <mergeCell ref="H185:M185"/>
+    <mergeCell ref="N185:P185"/>
+    <mergeCell ref="C186:G186"/>
+    <mergeCell ref="H186:M186"/>
+    <mergeCell ref="N186:P186"/>
+    <mergeCell ref="C187:G187"/>
+    <mergeCell ref="H187:M187"/>
+    <mergeCell ref="N187:P187"/>
+    <mergeCell ref="C182:G182"/>
+    <mergeCell ref="H182:M182"/>
+    <mergeCell ref="N182:P182"/>
+    <mergeCell ref="C183:G183"/>
+    <mergeCell ref="H183:M183"/>
+    <mergeCell ref="N183:P183"/>
+    <mergeCell ref="C184:G184"/>
+    <mergeCell ref="H184:M184"/>
+    <mergeCell ref="N184:P184"/>
+    <mergeCell ref="C179:G179"/>
+    <mergeCell ref="H179:M179"/>
+    <mergeCell ref="N179:P179"/>
+    <mergeCell ref="C180:G180"/>
+    <mergeCell ref="H180:M180"/>
+    <mergeCell ref="N180:P180"/>
+    <mergeCell ref="C181:G181"/>
+    <mergeCell ref="H181:M181"/>
+    <mergeCell ref="N181:P181"/>
+    <mergeCell ref="C176:G176"/>
+    <mergeCell ref="H176:M176"/>
+    <mergeCell ref="N176:P176"/>
+    <mergeCell ref="C177:G177"/>
+    <mergeCell ref="H177:M177"/>
+    <mergeCell ref="N177:P177"/>
+    <mergeCell ref="C178:G178"/>
+    <mergeCell ref="H178:M178"/>
+    <mergeCell ref="N178:P178"/>
+    <mergeCell ref="C173:G173"/>
+    <mergeCell ref="H173:M173"/>
+    <mergeCell ref="N173:P173"/>
+    <mergeCell ref="C174:G174"/>
+    <mergeCell ref="H174:M174"/>
+    <mergeCell ref="N174:P174"/>
+    <mergeCell ref="C175:G175"/>
+    <mergeCell ref="H175:M175"/>
+    <mergeCell ref="N175:P175"/>
+    <mergeCell ref="C170:G170"/>
+    <mergeCell ref="H170:M170"/>
+    <mergeCell ref="N170:P170"/>
+    <mergeCell ref="C171:G171"/>
+    <mergeCell ref="H171:M171"/>
+    <mergeCell ref="N171:P171"/>
+    <mergeCell ref="C172:G172"/>
+    <mergeCell ref="H172:M172"/>
+    <mergeCell ref="N172:P172"/>
+    <mergeCell ref="C167:G167"/>
+    <mergeCell ref="H167:M167"/>
+    <mergeCell ref="N167:P167"/>
+    <mergeCell ref="C168:G168"/>
+    <mergeCell ref="H168:M168"/>
+    <mergeCell ref="N168:P168"/>
+    <mergeCell ref="C169:G169"/>
+    <mergeCell ref="H169:M169"/>
+    <mergeCell ref="N169:P169"/>
+    <mergeCell ref="C164:G164"/>
+    <mergeCell ref="H164:M164"/>
+    <mergeCell ref="N164:P164"/>
+    <mergeCell ref="C165:G165"/>
+    <mergeCell ref="H165:M165"/>
+    <mergeCell ref="N165:P165"/>
+    <mergeCell ref="C166:G166"/>
+    <mergeCell ref="H166:M166"/>
+    <mergeCell ref="N166:P166"/>
+    <mergeCell ref="C161:G161"/>
+    <mergeCell ref="H161:M161"/>
+    <mergeCell ref="N161:P161"/>
+    <mergeCell ref="C162:G162"/>
+    <mergeCell ref="H162:M162"/>
+    <mergeCell ref="N162:P162"/>
+    <mergeCell ref="C163:G163"/>
+    <mergeCell ref="H163:M163"/>
+    <mergeCell ref="N163:P163"/>
+    <mergeCell ref="C158:G158"/>
+    <mergeCell ref="H158:M158"/>
+    <mergeCell ref="N158:P158"/>
+    <mergeCell ref="C159:G159"/>
+    <mergeCell ref="H159:M159"/>
+    <mergeCell ref="N159:P159"/>
+    <mergeCell ref="C160:G160"/>
+    <mergeCell ref="H160:M160"/>
+    <mergeCell ref="N160:P160"/>
+    <mergeCell ref="C155:G155"/>
+    <mergeCell ref="H155:M155"/>
+    <mergeCell ref="N155:P155"/>
+    <mergeCell ref="C156:G156"/>
+    <mergeCell ref="H156:M156"/>
+    <mergeCell ref="N156:P156"/>
+    <mergeCell ref="C157:G157"/>
+    <mergeCell ref="H157:M157"/>
+    <mergeCell ref="N157:P157"/>
+    <mergeCell ref="C152:G152"/>
+    <mergeCell ref="H152:M152"/>
+    <mergeCell ref="N152:P152"/>
+    <mergeCell ref="C153:G153"/>
+    <mergeCell ref="H153:M153"/>
+    <mergeCell ref="N153:P153"/>
+    <mergeCell ref="C154:G154"/>
+    <mergeCell ref="H154:M154"/>
+    <mergeCell ref="N154:P154"/>
+    <mergeCell ref="C149:G149"/>
+    <mergeCell ref="H149:M149"/>
+    <mergeCell ref="N149:P149"/>
+    <mergeCell ref="C150:G150"/>
+    <mergeCell ref="H150:M150"/>
+    <mergeCell ref="N150:P150"/>
+    <mergeCell ref="C151:G151"/>
+    <mergeCell ref="H151:M151"/>
+    <mergeCell ref="N151:P151"/>
+    <mergeCell ref="C146:G146"/>
+    <mergeCell ref="H146:M146"/>
+    <mergeCell ref="N146:P146"/>
+    <mergeCell ref="C147:G147"/>
+    <mergeCell ref="H147:M147"/>
+    <mergeCell ref="N147:P147"/>
+    <mergeCell ref="C148:G148"/>
+    <mergeCell ref="H148:M148"/>
+    <mergeCell ref="N148:P148"/>
+    <mergeCell ref="C143:G143"/>
+    <mergeCell ref="H143:M143"/>
+    <mergeCell ref="N143:P143"/>
+    <mergeCell ref="C144:G144"/>
+    <mergeCell ref="H144:M144"/>
+    <mergeCell ref="N144:P144"/>
+    <mergeCell ref="C145:G145"/>
+    <mergeCell ref="H145:M145"/>
+    <mergeCell ref="N145:P145"/>
+    <mergeCell ref="C140:G140"/>
+    <mergeCell ref="H140:M140"/>
+    <mergeCell ref="N140:P140"/>
+    <mergeCell ref="C141:G141"/>
+    <mergeCell ref="H141:M141"/>
+    <mergeCell ref="N141:P141"/>
+    <mergeCell ref="C142:G142"/>
+    <mergeCell ref="H142:M142"/>
+    <mergeCell ref="N142:P142"/>
+    <mergeCell ref="C137:G137"/>
+    <mergeCell ref="H137:M137"/>
+    <mergeCell ref="N137:P137"/>
+    <mergeCell ref="C138:G138"/>
+    <mergeCell ref="H138:M138"/>
+    <mergeCell ref="N138:P138"/>
+    <mergeCell ref="C139:G139"/>
+    <mergeCell ref="H139:M139"/>
+    <mergeCell ref="N139:P139"/>
+    <mergeCell ref="C134:G134"/>
+    <mergeCell ref="H134:M134"/>
+    <mergeCell ref="N134:P134"/>
+    <mergeCell ref="C135:G135"/>
+    <mergeCell ref="H135:M135"/>
+    <mergeCell ref="N135:P135"/>
+    <mergeCell ref="C136:G136"/>
+    <mergeCell ref="H136:M136"/>
+    <mergeCell ref="N136:P136"/>
+    <mergeCell ref="C131:G131"/>
+    <mergeCell ref="H131:M131"/>
+    <mergeCell ref="N131:P131"/>
+    <mergeCell ref="C132:G132"/>
+    <mergeCell ref="H132:M132"/>
+    <mergeCell ref="N132:P132"/>
+    <mergeCell ref="C133:G133"/>
+    <mergeCell ref="H133:M133"/>
+    <mergeCell ref="N133:P133"/>
+    <mergeCell ref="C128:G128"/>
+    <mergeCell ref="H128:M128"/>
+    <mergeCell ref="N128:P128"/>
+    <mergeCell ref="C129:G129"/>
+    <mergeCell ref="H129:M129"/>
+    <mergeCell ref="N129:P129"/>
+    <mergeCell ref="C130:G130"/>
+    <mergeCell ref="H130:M130"/>
+    <mergeCell ref="N130:P130"/>
+    <mergeCell ref="C125:G125"/>
+    <mergeCell ref="H125:M125"/>
+    <mergeCell ref="N125:P125"/>
+    <mergeCell ref="C126:G126"/>
+    <mergeCell ref="H126:M126"/>
+    <mergeCell ref="N126:P126"/>
+    <mergeCell ref="C127:G127"/>
+    <mergeCell ref="H127:M127"/>
+    <mergeCell ref="N127:P127"/>
+    <mergeCell ref="C122:G122"/>
+    <mergeCell ref="H122:M122"/>
+    <mergeCell ref="N122:P122"/>
+    <mergeCell ref="C123:G123"/>
+    <mergeCell ref="H123:M123"/>
+    <mergeCell ref="N123:P123"/>
+    <mergeCell ref="C124:G124"/>
+    <mergeCell ref="H124:M124"/>
+    <mergeCell ref="N124:P124"/>
+    <mergeCell ref="C119:G119"/>
+    <mergeCell ref="H119:M119"/>
+    <mergeCell ref="N119:P119"/>
+    <mergeCell ref="C120:G120"/>
+    <mergeCell ref="H120:M120"/>
+    <mergeCell ref="N120:P120"/>
+    <mergeCell ref="C121:G121"/>
+    <mergeCell ref="H121:M121"/>
+    <mergeCell ref="N121:P121"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="H116:M116"/>
+    <mergeCell ref="N116:P116"/>
+    <mergeCell ref="C117:G117"/>
+    <mergeCell ref="H117:M117"/>
+    <mergeCell ref="N117:P117"/>
+    <mergeCell ref="C118:G118"/>
+    <mergeCell ref="H118:M118"/>
+    <mergeCell ref="N118:P118"/>
+    <mergeCell ref="C113:G113"/>
+    <mergeCell ref="H113:M113"/>
+    <mergeCell ref="N113:P113"/>
+    <mergeCell ref="C114:G114"/>
+    <mergeCell ref="H114:M114"/>
+    <mergeCell ref="N114:P114"/>
+    <mergeCell ref="C115:G115"/>
+    <mergeCell ref="H115:M115"/>
+    <mergeCell ref="N115:P115"/>
+    <mergeCell ref="C110:G110"/>
+    <mergeCell ref="H110:M110"/>
+    <mergeCell ref="N110:P110"/>
+    <mergeCell ref="C111:G111"/>
+    <mergeCell ref="H111:M111"/>
+    <mergeCell ref="N111:P111"/>
+    <mergeCell ref="C112:G112"/>
+    <mergeCell ref="H112:M112"/>
+    <mergeCell ref="N112:P112"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="H107:M107"/>
+    <mergeCell ref="N107:P107"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="H108:M108"/>
+    <mergeCell ref="N108:P108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="H109:M109"/>
+    <mergeCell ref="N109:P109"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="H104:M104"/>
+    <mergeCell ref="N104:P104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="H105:M105"/>
+    <mergeCell ref="N105:P105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="H106:M106"/>
+    <mergeCell ref="N106:P106"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="H101:M101"/>
+    <mergeCell ref="N101:P101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="H102:M102"/>
+    <mergeCell ref="N102:P102"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="H103:M103"/>
+    <mergeCell ref="N103:P103"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="H98:M98"/>
+    <mergeCell ref="N98:P98"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="H99:M99"/>
+    <mergeCell ref="N99:P99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="H100:M100"/>
+    <mergeCell ref="N100:P100"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="H95:M95"/>
+    <mergeCell ref="N95:P95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="H96:M96"/>
+    <mergeCell ref="N96:P96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="H97:M97"/>
+    <mergeCell ref="N97:P97"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="H92:M92"/>
+    <mergeCell ref="N92:P92"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="H93:M93"/>
+    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:M94"/>
+    <mergeCell ref="N94:P94"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="H89:M89"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="H90:M90"/>
+    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="H91:M91"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="H86:M86"/>
+    <mergeCell ref="N86:P86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="H87:M87"/>
+    <mergeCell ref="N87:P87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="H88:M88"/>
+    <mergeCell ref="N88:P88"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="H83:M83"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="H84:M84"/>
+    <mergeCell ref="N84:P84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="H85:M85"/>
+    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="H80:M80"/>
+    <mergeCell ref="N80:P80"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="H81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="H82:M82"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="H77:M77"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="H78:M78"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="H79:M79"/>
+    <mergeCell ref="N79:P79"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="H74:M74"/>
+    <mergeCell ref="N74:P74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="H75:M75"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="H76:M76"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="H71:M71"/>
+    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:M72"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="H73:M73"/>
+    <mergeCell ref="N73:P73"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="H68:M68"/>
+    <mergeCell ref="N68:P68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="H69:M69"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="H70:M70"/>
+    <mergeCell ref="N70:P70"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="H65:M65"/>
+    <mergeCell ref="N65:P65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="H66:M66"/>
+    <mergeCell ref="N66:P66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:M67"/>
+    <mergeCell ref="N67:P67"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H62:M62"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="H63:M63"/>
+    <mergeCell ref="N63:P63"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="H64:M64"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H59:M59"/>
+    <mergeCell ref="N59:P59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="H60:M60"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="H61:M61"/>
+    <mergeCell ref="N61:P61"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="H58:M58"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H56:M56"/>
+    <mergeCell ref="H57:M57"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="H54:M54"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="H55:M55"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="H53:M53"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="R56:S56"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="R58:S58"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N34:P34"/>
     <mergeCell ref="N53:P53"/>
     <mergeCell ref="N54:P54"/>
     <mergeCell ref="N55:P55"/>
@@ -4131,206 +9377,6 @@
     <mergeCell ref="N38:P38"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="R56:S56"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="H55:M55"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="H53:M53"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="H58:M58"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H56:M56"/>
-    <mergeCell ref="H57:M57"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="H54:M54"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R31:S31"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -4358,12 +9404,12 @@
         <v>13</v>
       </c>
       <c r="B1" s="79"/>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65" t="s">
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="48" t="s">
         <v>47</v>
       </c>
       <c r="G1" s="66"/>
@@ -4372,31 +9418,31 @@
       <c r="J1" s="66"/>
       <c r="K1" s="66"/>
       <c r="L1" s="66"/>
-      <c r="M1" s="67"/>
+      <c r="M1" s="49"/>
       <c r="N1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="65" t="s">
+      <c r="O1" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="67"/>
+      <c r="P1" s="49"/>
       <c r="Q1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="65" t="s">
+      <c r="R1" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="67"/>
+      <c r="S1" s="49"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="65" t="s">
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="48" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="66"/>
@@ -4405,21 +9451,21 @@
       <c r="J2" s="66"/>
       <c r="K2" s="66"/>
       <c r="L2" s="66"/>
-      <c r="M2" s="67"/>
+      <c r="M2" s="49"/>
       <c r="N2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="77">
+      <c r="O2" s="50">
         <v>44771</v>
       </c>
-      <c r="P2" s="78"/>
+      <c r="P2" s="51"/>
       <c r="Q2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="75" t="s">
+      <c r="R2" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="76"/>
+      <c r="S2" s="71"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="5"/>
@@ -4449,51 +9495,51 @@
       <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="54" t="s">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="54" t="s">
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="55"/>
-      <c r="P4" s="56"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="55"/>
       <c r="Q4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="54" t="s">
+      <c r="R4" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="56"/>
+      <c r="S4" s="55"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="74"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="58"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="68"/>
       <c r="S5" s="69"/>
@@ -4505,1025 +9551,1084 @@
       <c r="B6" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50" t="s">
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67" t="s">
         <v>275</v>
       </c>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="51" t="s">
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="52"/>
-      <c r="P6" s="53"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="61"/>
       <c r="Q6" s="11">
         <v>44771</v>
       </c>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="53"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="61"/>
       <c r="Q7" s="10"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="53"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="60"/>
+      <c r="P8" s="61"/>
       <c r="Q8" s="11"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="52"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="53"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="59"/>
+      <c r="O9" s="60"/>
+      <c r="P9" s="61"/>
       <c r="Q9" s="10"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="53"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="61"/>
       <c r="Q10" s="11"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="53"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="60"/>
+      <c r="P11" s="61"/>
       <c r="Q11" s="11"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="53"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="59"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="61"/>
       <c r="Q12" s="10"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="53"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="61"/>
       <c r="Q13" s="10"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50" t="s">
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67" t="s">
         <v>277</v>
       </c>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="51" t="s">
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="O14" s="52"/>
-      <c r="P14" s="53"/>
+      <c r="O14" s="60"/>
+      <c r="P14" s="61"/>
       <c r="Q14" s="11">
         <v>44771</v>
       </c>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="53"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="60"/>
+      <c r="P15" s="61"/>
       <c r="Q15" s="11"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
+      <c r="R15" s="52"/>
+      <c r="S15" s="52"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="10">
         <v>2</v>
       </c>
       <c r="B16" s="10"/>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="53"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="61"/>
       <c r="Q16" s="11">
         <v>44771</v>
       </c>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
+      <c r="R16" s="52"/>
+      <c r="S16" s="52"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="53"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="61"/>
       <c r="Q17" s="10"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="52"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="67" t="s">
         <v>283</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="53"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="61"/>
       <c r="Q18" s="11"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
+      <c r="R18" s="52"/>
+      <c r="S18" s="52"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="53"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="61"/>
       <c r="Q19" s="10"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="52"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50" t="s">
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67" t="s">
         <v>286</v>
       </c>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="51" t="s">
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="59" t="s">
         <v>285</v>
       </c>
-      <c r="O20" s="52"/>
-      <c r="P20" s="53"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="61"/>
       <c r="Q20" s="11">
         <v>44771</v>
       </c>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="52"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="53"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="61"/>
       <c r="Q21" s="11"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="10"/>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="53"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="61"/>
       <c r="Q22" s="11"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="52"/>
-      <c r="P23" s="53"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="61"/>
       <c r="Q23" s="10"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="52"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="53"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="60"/>
+      <c r="P24" s="61"/>
       <c r="Q24" s="11"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="52"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="52"/>
-      <c r="P25" s="53"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="61"/>
       <c r="Q25" s="10"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
+      <c r="R25" s="52"/>
+      <c r="S25" s="52"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50" t="s">
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67" t="s">
         <v>279</v>
       </c>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="51" t="s">
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="52"/>
-      <c r="P26" s="53"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="61"/>
       <c r="Q26" s="11">
         <v>44771</v>
       </c>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="52"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="53"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="61"/>
       <c r="Q27" s="10"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="10">
         <v>4</v>
       </c>
       <c r="B28" s="10"/>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="53"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="61"/>
       <c r="Q28" s="11"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="52"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="53"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="60"/>
+      <c r="P29" s="61"/>
       <c r="Q29" s="10"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="67" t="s">
         <v>287</v>
       </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="53"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="61"/>
       <c r="Q30" s="11"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="53"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="61"/>
       <c r="Q31" s="10"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="52"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50" t="s">
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="51" t="s">
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="67"/>
+      <c r="L32" s="67"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="59" t="s">
         <v>289</v>
       </c>
-      <c r="O32" s="52"/>
-      <c r="P32" s="53"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="61"/>
       <c r="Q32" s="11">
         <v>44771</v>
       </c>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="51"/>
-      <c r="O33" s="52"/>
-      <c r="P33" s="53"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="67"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="67"/>
+      <c r="M33" s="67"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="60"/>
+      <c r="P33" s="61"/>
       <c r="Q33" s="10"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="52"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="10" t="s">
         <v>282</v>
       </c>
       <c r="B34" s="10"/>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="53"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="67"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="59"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="61"/>
       <c r="Q34" s="11"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
+      <c r="R34" s="52"/>
+      <c r="S34" s="52"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="51"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="53"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="60"/>
+      <c r="P35" s="61"/>
       <c r="Q35" s="10"/>
-      <c r="R35" s="45"/>
-      <c r="S35" s="45"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="53"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="59"/>
+      <c r="O36" s="60"/>
+      <c r="P36" s="61"/>
       <c r="Q36" s="11"/>
-      <c r="R36" s="45"/>
-      <c r="S36" s="45"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="53"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="59"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="61"/>
       <c r="Q37" s="10"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50" t="s">
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="51" t="s">
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="67"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="O38" s="52"/>
-      <c r="P38" s="53"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="61"/>
       <c r="Q38" s="11">
         <v>44771</v>
       </c>
-      <c r="R38" s="45"/>
-      <c r="S38" s="45"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="51" t="s">
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="67"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="O39" s="52"/>
-      <c r="P39" s="53"/>
+      <c r="O39" s="60"/>
+      <c r="P39" s="61"/>
       <c r="Q39" s="10"/>
-      <c r="R39" s="45"/>
-      <c r="S39" s="45"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="53"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="59"/>
+      <c r="O40" s="60"/>
+      <c r="P40" s="61"/>
       <c r="Q40" s="11"/>
-      <c r="R40" s="45"/>
-      <c r="S40" s="45"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="10">
         <v>6</v>
       </c>
       <c r="B41" s="10"/>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="52"/>
-      <c r="P41" s="53"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="61"/>
       <c r="Q41" s="11"/>
-      <c r="R41" s="45"/>
-      <c r="S41" s="45"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="52"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="50"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="52"/>
-      <c r="P42" s="53"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="67"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="59"/>
+      <c r="O42" s="60"/>
+      <c r="P42" s="61"/>
       <c r="Q42" s="10"/>
-      <c r="R42" s="45"/>
-      <c r="S42" s="45"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="51"/>
-      <c r="O43" s="52"/>
-      <c r="P43" s="53"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
+      <c r="I43" s="67"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="67"/>
+      <c r="M43" s="67"/>
+      <c r="N43" s="59"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="61"/>
       <c r="Q43" s="11"/>
-      <c r="R43" s="45"/>
-      <c r="S43" s="45"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="51"/>
-      <c r="O44" s="52"/>
-      <c r="P44" s="53"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="67"/>
+      <c r="I44" s="67"/>
+      <c r="J44" s="67"/>
+      <c r="K44" s="67"/>
+      <c r="L44" s="67"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="59"/>
+      <c r="O44" s="60"/>
+      <c r="P44" s="61"/>
       <c r="Q44" s="10"/>
-      <c r="R44" s="45"/>
-      <c r="S44" s="45"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="50" t="s">
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="51" t="s">
+      <c r="I45" s="67"/>
+      <c r="J45" s="67"/>
+      <c r="K45" s="67"/>
+      <c r="L45" s="67"/>
+      <c r="M45" s="67"/>
+      <c r="N45" s="59" t="s">
         <v>281</v>
       </c>
-      <c r="O45" s="52"/>
-      <c r="P45" s="53"/>
+      <c r="O45" s="60"/>
+      <c r="P45" s="61"/>
       <c r="Q45" s="11">
         <v>44771</v>
       </c>
-      <c r="R45" s="45"/>
-      <c r="S45" s="45"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="50"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="50"/>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="51"/>
-      <c r="O46" s="52"/>
-      <c r="P46" s="53"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="59"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="61"/>
       <c r="Q46" s="10"/>
-      <c r="R46" s="45"/>
-      <c r="S46" s="45"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="181">
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="H22:M22"/>
     <mergeCell ref="N22:P22"/>
@@ -5548,114 +10653,55 @@
     <mergeCell ref="H17:M17"/>
     <mergeCell ref="N17:P17"/>
     <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/document/編集機能_結合テスト仕様書.xlsx
+++ b/document/編集機能_結合テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FB29E7-8F26-4AC5-B8BB-5AB04F9CAFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EF1944-7E09-474C-B38B-0DF86B48DB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="888" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="888" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様書兼報告書" sheetId="166" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="396">
   <si>
     <t>作成者</t>
   </si>
@@ -2261,25 +2261,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>タブB上のタスク編集画面で、タスク名を変更する</t>
-    <rPh sb="3" eb="4">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>タスク名：総合テスト</t>
     <rPh sb="5" eb="7">
       <t>ソウゴウ</t>
@@ -2468,6 +2449,106 @@
     </rPh>
     <rPh sb="35" eb="37">
       <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タブB上で以下のタスクのラジオボタンを押下する</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タブB上で削除ボタンを押下する</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タブB上のタスク編集画面で、以下のタスク名に変更する</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タブA上のタスク編集画面で、以下のタスク名に変更する</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>サラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タブA上のタスク編集画面で、編集実行ボタンを押下する</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タスク編集失敗画面が表示されている
+・表示されているタスク名が「総合テスト」になっている</t>
+    <rPh sb="5" eb="7">
+      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3385,7 +3466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S230"/>
+  <dimension ref="A1:S247"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.875" style="4" customWidth="1"/>
@@ -5934,7 +6015,7 @@
       <c r="P109" s="44"/>
       <c r="Q109" s="10"/>
     </row>
-    <row r="110" spans="1:17" ht="104.25" customHeight="1">
+    <row r="110" spans="1:17" ht="96" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
       <c r="C110" s="67" t="s">
@@ -5997,7 +6078,7 @@
       <c r="P112" s="44"/>
       <c r="Q112" s="10"/>
     </row>
-    <row r="113" spans="1:17" ht="82.5" customHeight="1">
+    <row r="113" spans="1:17" ht="77.25" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="72" t="s">
@@ -6021,13 +6102,13 @@
     <row r="114" spans="1:17" ht="30" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
-      <c r="C114" s="46" t="s">
-        <v>375</v>
-      </c>
-      <c r="D114" s="47"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="47"/>
-      <c r="G114" s="48"/>
+      <c r="C114" s="75" t="s">
+        <v>390</v>
+      </c>
+      <c r="D114" s="75"/>
+      <c r="E114" s="75"/>
+      <c r="F114" s="75"/>
+      <c r="G114" s="75"/>
       <c r="H114" s="46"/>
       <c r="I114" s="47"/>
       <c r="J114" s="47"/>
@@ -6039,7 +6120,7 @@
       <c r="P114" s="44"/>
       <c r="Q114" s="10"/>
     </row>
-    <row r="115" spans="1:17" ht="102.75" customHeight="1">
+    <row r="115" spans="1:17" ht="96" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="67" t="s">
@@ -6063,13 +6144,13 @@
     <row r="116" spans="1:17" ht="30" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
-      <c r="C116" s="46" t="s">
-        <v>373</v>
-      </c>
-      <c r="D116" s="47"/>
-      <c r="E116" s="47"/>
-      <c r="F116" s="47"/>
-      <c r="G116" s="48"/>
+      <c r="C116" s="75" t="s">
+        <v>391</v>
+      </c>
+      <c r="D116" s="75"/>
+      <c r="E116" s="75"/>
+      <c r="F116" s="75"/>
+      <c r="G116" s="75"/>
       <c r="H116" s="46"/>
       <c r="I116" s="47"/>
       <c r="J116" s="47"/>
@@ -6085,7 +6166,7 @@
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="72" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="D117" s="73"/>
       <c r="E117" s="73"/>
@@ -6105,13 +6186,13 @@
     <row r="118" spans="1:17" ht="30" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
-      <c r="C118" s="46" t="s">
-        <v>369</v>
-      </c>
-      <c r="D118" s="47"/>
-      <c r="E118" s="47"/>
-      <c r="F118" s="47"/>
-      <c r="G118" s="48"/>
+      <c r="C118" s="75" t="s">
+        <v>378</v>
+      </c>
+      <c r="D118" s="75"/>
+      <c r="E118" s="75"/>
+      <c r="F118" s="75"/>
+      <c r="G118" s="75"/>
       <c r="H118" s="46"/>
       <c r="I118" s="47"/>
       <c r="J118" s="47"/>
@@ -6123,23 +6204,27 @@
       <c r="P118" s="44"/>
       <c r="Q118" s="10"/>
     </row>
-    <row r="119" spans="1:17" ht="30" customHeight="1">
+    <row r="119" spans="1:17" ht="55.5" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
-      <c r="C119" s="75" t="s">
-        <v>362</v>
-      </c>
-      <c r="D119" s="75"/>
-      <c r="E119" s="75"/>
-      <c r="F119" s="75"/>
-      <c r="G119" s="75"/>
-      <c r="H119" s="46"/>
+      <c r="C119" s="67" t="s">
+        <v>394</v>
+      </c>
+      <c r="D119" s="67"/>
+      <c r="E119" s="67"/>
+      <c r="F119" s="67"/>
+      <c r="G119" s="67"/>
+      <c r="H119" s="46" t="s">
+        <v>349</v>
+      </c>
       <c r="I119" s="47"/>
       <c r="J119" s="47"/>
       <c r="K119" s="47"/>
       <c r="L119" s="47"/>
       <c r="M119" s="48"/>
-      <c r="N119" s="42"/>
+      <c r="N119" s="45" t="s">
+        <v>395</v>
+      </c>
       <c r="O119" s="43"/>
       <c r="P119" s="44"/>
       <c r="Q119" s="10"/>
@@ -6147,13 +6232,11 @@
     <row r="120" spans="1:17" ht="30" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
-      <c r="C120" s="72" t="s">
-        <v>377</v>
-      </c>
-      <c r="D120" s="73"/>
-      <c r="E120" s="73"/>
-      <c r="F120" s="73"/>
-      <c r="G120" s="74"/>
+      <c r="C120" s="75"/>
+      <c r="D120" s="75"/>
+      <c r="E120" s="75"/>
+      <c r="F120" s="75"/>
+      <c r="G120" s="75"/>
       <c r="H120" s="46"/>
       <c r="I120" s="47"/>
       <c r="J120" s="47"/>
@@ -6168,13 +6251,11 @@
     <row r="121" spans="1:17" ht="30" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
-      <c r="C121" s="72" t="s">
-        <v>378</v>
-      </c>
-      <c r="D121" s="73"/>
-      <c r="E121" s="73"/>
-      <c r="F121" s="73"/>
-      <c r="G121" s="74"/>
+      <c r="C121" s="75"/>
+      <c r="D121" s="75"/>
+      <c r="E121" s="75"/>
+      <c r="F121" s="75"/>
+      <c r="G121" s="75"/>
       <c r="H121" s="46"/>
       <c r="I121" s="47"/>
       <c r="J121" s="47"/>
@@ -6189,13 +6270,11 @@
     <row r="122" spans="1:17" ht="30" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
-      <c r="C122" s="46" t="s">
-        <v>379</v>
-      </c>
-      <c r="D122" s="47"/>
-      <c r="E122" s="47"/>
-      <c r="F122" s="47"/>
-      <c r="G122" s="48"/>
+      <c r="C122" s="75"/>
+      <c r="D122" s="75"/>
+      <c r="E122" s="75"/>
+      <c r="F122" s="75"/>
+      <c r="G122" s="75"/>
       <c r="H122" s="46"/>
       <c r="I122" s="47"/>
       <c r="J122" s="47"/>
@@ -6207,48 +6286,34 @@
       <c r="P122" s="44"/>
       <c r="Q122" s="10"/>
     </row>
-    <row r="123" spans="1:17" ht="60.75" customHeight="1">
+    <row r="123" spans="1:17" ht="30" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="81" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="67" t="s">
-        <v>380</v>
-      </c>
-      <c r="D123" s="67"/>
-      <c r="E123" s="67"/>
-      <c r="F123" s="67"/>
-      <c r="G123" s="67"/>
-      <c r="H123" s="72" t="s">
-        <v>374</v>
-      </c>
-      <c r="I123" s="73"/>
-      <c r="J123" s="73"/>
-      <c r="K123" s="73"/>
-      <c r="L123" s="73"/>
-      <c r="M123" s="74"/>
-      <c r="N123" s="45" t="s">
-        <v>363</v>
-      </c>
-      <c r="O123" s="53"/>
-      <c r="P123" s="54"/>
+      <c r="B123" s="10"/>
+      <c r="C123" s="75"/>
+      <c r="D123" s="75"/>
+      <c r="E123" s="75"/>
+      <c r="F123" s="75"/>
+      <c r="G123" s="75"/>
+      <c r="H123" s="46"/>
+      <c r="I123" s="47"/>
+      <c r="J123" s="47"/>
+      <c r="K123" s="47"/>
+      <c r="L123" s="47"/>
+      <c r="M123" s="48"/>
+      <c r="N123" s="42"/>
+      <c r="O123" s="43"/>
+      <c r="P123" s="44"/>
       <c r="Q123" s="10"/>
     </row>
     <row r="124" spans="1:17" ht="30" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C124" s="72" t="s">
-        <v>381</v>
-      </c>
-      <c r="D124" s="73"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="73"/>
-      <c r="G124" s="74"/>
-      <c r="H124" s="46" t="s">
-        <v>382</v>
-      </c>
+      <c r="B124" s="10"/>
+      <c r="C124" s="75"/>
+      <c r="D124" s="75"/>
+      <c r="E124" s="75"/>
+      <c r="F124" s="75"/>
+      <c r="G124" s="75"/>
+      <c r="H124" s="46"/>
       <c r="I124" s="47"/>
       <c r="J124" s="47"/>
       <c r="K124" s="47"/>
@@ -6260,13 +6325,17 @@
       <c r="Q124" s="10"/>
     </row>
     <row r="125" spans="1:17" ht="30" customHeight="1">
-      <c r="A125" s="10"/>
+      <c r="A125" s="10">
+        <v>13</v>
+      </c>
       <c r="B125" s="10"/>
-      <c r="C125" s="72"/>
-      <c r="D125" s="73"/>
-      <c r="E125" s="73"/>
-      <c r="F125" s="73"/>
-      <c r="G125" s="74"/>
+      <c r="C125" s="67" t="s">
+        <v>366</v>
+      </c>
+      <c r="D125" s="67"/>
+      <c r="E125" s="67"/>
+      <c r="F125" s="67"/>
+      <c r="G125" s="67"/>
       <c r="H125" s="46"/>
       <c r="I125" s="47"/>
       <c r="J125" s="47"/>
@@ -6279,12 +6348,10 @@
       <c r="Q125" s="10"/>
     </row>
     <row r="126" spans="1:17" ht="30" customHeight="1">
-      <c r="A126" s="10">
-        <v>14</v>
-      </c>
+      <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="67" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="D126" s="67"/>
       <c r="E126" s="67"/>
@@ -6301,16 +6368,16 @@
       <c r="P126" s="44"/>
       <c r="Q126" s="10"/>
     </row>
-    <row r="127" spans="1:17" ht="30" customHeight="1">
+    <row r="127" spans="1:17" ht="104.25" customHeight="1">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="67" t="s">
-        <v>305</v>
-      </c>
-      <c r="D127" s="67"/>
-      <c r="E127" s="67"/>
-      <c r="F127" s="67"/>
-      <c r="G127" s="67"/>
+        <v>304</v>
+      </c>
+      <c r="D127" s="75"/>
+      <c r="E127" s="75"/>
+      <c r="F127" s="75"/>
+      <c r="G127" s="75"/>
       <c r="H127" s="46"/>
       <c r="I127" s="47"/>
       <c r="J127" s="47"/>
@@ -6322,11 +6389,11 @@
       <c r="P127" s="44"/>
       <c r="Q127" s="10"/>
     </row>
-    <row r="128" spans="1:17" ht="98.25" customHeight="1">
+    <row r="128" spans="1:17" ht="30" customHeight="1">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
       <c r="C128" s="67" t="s">
-        <v>304</v>
+        <v>367</v>
       </c>
       <c r="D128" s="75"/>
       <c r="E128" s="75"/>
@@ -6346,8 +6413,8 @@
     <row r="129" spans="1:17" ht="30" customHeight="1">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
-      <c r="C129" s="67" t="s">
-        <v>308</v>
+      <c r="C129" s="75" t="s">
+        <v>368</v>
       </c>
       <c r="D129" s="75"/>
       <c r="E129" s="75"/>
@@ -6364,16 +6431,16 @@
       <c r="P129" s="44"/>
       <c r="Q129" s="10"/>
     </row>
-    <row r="130" spans="1:17" ht="30" customHeight="1">
+    <row r="130" spans="1:17" ht="82.5" customHeight="1">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
-      <c r="C130" s="75" t="s">
-        <v>303</v>
-      </c>
-      <c r="D130" s="75"/>
-      <c r="E130" s="75"/>
-      <c r="F130" s="75"/>
-      <c r="G130" s="75"/>
+      <c r="C130" s="72" t="s">
+        <v>365</v>
+      </c>
+      <c r="D130" s="73"/>
+      <c r="E130" s="73"/>
+      <c r="F130" s="73"/>
+      <c r="G130" s="74"/>
       <c r="H130" s="46"/>
       <c r="I130" s="47"/>
       <c r="J130" s="47"/>
@@ -6388,13 +6455,13 @@
     <row r="131" spans="1:17" ht="30" customHeight="1">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
-      <c r="C131" s="75" t="s">
-        <v>383</v>
-      </c>
-      <c r="D131" s="75"/>
-      <c r="E131" s="75"/>
-      <c r="F131" s="75"/>
-      <c r="G131" s="75"/>
+      <c r="C131" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="D131" s="47"/>
+      <c r="E131" s="47"/>
+      <c r="F131" s="47"/>
+      <c r="G131" s="48"/>
       <c r="H131" s="46"/>
       <c r="I131" s="47"/>
       <c r="J131" s="47"/>
@@ -6406,16 +6473,16 @@
       <c r="P131" s="44"/>
       <c r="Q131" s="10"/>
     </row>
-    <row r="132" spans="1:17" ht="30" customHeight="1">
+    <row r="132" spans="1:17" ht="102.75" customHeight="1">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
-      <c r="C132" s="46" t="s">
-        <v>384</v>
-      </c>
-      <c r="D132" s="47"/>
-      <c r="E132" s="47"/>
-      <c r="F132" s="47"/>
-      <c r="G132" s="48"/>
+      <c r="C132" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="D132" s="75"/>
+      <c r="E132" s="75"/>
+      <c r="F132" s="75"/>
+      <c r="G132" s="75"/>
       <c r="H132" s="46"/>
       <c r="I132" s="47"/>
       <c r="J132" s="47"/>
@@ -6430,13 +6497,13 @@
     <row r="133" spans="1:17" ht="30" customHeight="1">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
-      <c r="C133" s="75" t="s">
-        <v>385</v>
-      </c>
-      <c r="D133" s="75"/>
-      <c r="E133" s="75"/>
-      <c r="F133" s="75"/>
-      <c r="G133" s="75"/>
+      <c r="C133" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="D133" s="47"/>
+      <c r="E133" s="47"/>
+      <c r="F133" s="47"/>
+      <c r="G133" s="48"/>
       <c r="H133" s="46"/>
       <c r="I133" s="47"/>
       <c r="J133" s="47"/>
@@ -6451,13 +6518,13 @@
     <row r="134" spans="1:17" ht="30" customHeight="1">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
-      <c r="C134" s="46" t="s">
-        <v>386</v>
-      </c>
-      <c r="D134" s="47"/>
-      <c r="E134" s="47"/>
-      <c r="F134" s="47"/>
-      <c r="G134" s="48"/>
+      <c r="C134" s="72" t="s">
+        <v>376</v>
+      </c>
+      <c r="D134" s="73"/>
+      <c r="E134" s="73"/>
+      <c r="F134" s="73"/>
+      <c r="G134" s="74"/>
       <c r="H134" s="46"/>
       <c r="I134" s="47"/>
       <c r="J134" s="47"/>
@@ -6472,13 +6539,13 @@
     <row r="135" spans="1:17" ht="30" customHeight="1">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
-      <c r="C135" s="75" t="s">
-        <v>387</v>
-      </c>
-      <c r="D135" s="75"/>
-      <c r="E135" s="75"/>
-      <c r="F135" s="75"/>
-      <c r="G135" s="75"/>
+      <c r="C135" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="D135" s="47"/>
+      <c r="E135" s="47"/>
+      <c r="F135" s="47"/>
+      <c r="G135" s="48"/>
       <c r="H135" s="46"/>
       <c r="I135" s="47"/>
       <c r="J135" s="47"/>
@@ -6493,13 +6560,13 @@
     <row r="136" spans="1:17" ht="30" customHeight="1">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
-      <c r="C136" s="46" t="s">
-        <v>388</v>
-      </c>
-      <c r="D136" s="47"/>
-      <c r="E136" s="47"/>
-      <c r="F136" s="47"/>
-      <c r="G136" s="48"/>
+      <c r="C136" s="75" t="s">
+        <v>362</v>
+      </c>
+      <c r="D136" s="75"/>
+      <c r="E136" s="75"/>
+      <c r="F136" s="75"/>
+      <c r="G136" s="75"/>
       <c r="H136" s="46"/>
       <c r="I136" s="47"/>
       <c r="J136" s="47"/>
@@ -6511,39 +6578,37 @@
       <c r="P136" s="44"/>
       <c r="Q136" s="10"/>
     </row>
-    <row r="137" spans="1:17" ht="52.5" customHeight="1">
+    <row r="137" spans="1:17" ht="30" customHeight="1">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
       <c r="C137" s="72" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="D137" s="73"/>
       <c r="E137" s="73"/>
       <c r="F137" s="73"/>
       <c r="G137" s="74"/>
-      <c r="H137" s="72" t="s">
-        <v>389</v>
-      </c>
-      <c r="I137" s="73"/>
-      <c r="J137" s="73"/>
-      <c r="K137" s="73"/>
-      <c r="L137" s="73"/>
-      <c r="M137" s="74"/>
-      <c r="N137" s="45" t="s">
-        <v>390</v>
-      </c>
-      <c r="O137" s="53"/>
-      <c r="P137" s="54"/>
+      <c r="H137" s="46"/>
+      <c r="I137" s="47"/>
+      <c r="J137" s="47"/>
+      <c r="K137" s="47"/>
+      <c r="L137" s="47"/>
+      <c r="M137" s="48"/>
+      <c r="N137" s="42"/>
+      <c r="O137" s="43"/>
+      <c r="P137" s="44"/>
       <c r="Q137" s="10"/>
     </row>
     <row r="138" spans="1:17" ht="30" customHeight="1">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
-      <c r="C138" s="46"/>
-      <c r="D138" s="47"/>
-      <c r="E138" s="47"/>
-      <c r="F138" s="47"/>
-      <c r="G138" s="48"/>
+      <c r="C138" s="72" t="s">
+        <v>392</v>
+      </c>
+      <c r="D138" s="73"/>
+      <c r="E138" s="73"/>
+      <c r="F138" s="73"/>
+      <c r="G138" s="74"/>
       <c r="H138" s="46"/>
       <c r="I138" s="47"/>
       <c r="J138" s="47"/>
@@ -6558,11 +6623,13 @@
     <row r="139" spans="1:17" ht="30" customHeight="1">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
-      <c r="C139" s="75"/>
-      <c r="D139" s="75"/>
-      <c r="E139" s="75"/>
-      <c r="F139" s="75"/>
-      <c r="G139" s="75"/>
+      <c r="C139" s="46" t="s">
+        <v>378</v>
+      </c>
+      <c r="D139" s="47"/>
+      <c r="E139" s="47"/>
+      <c r="F139" s="47"/>
+      <c r="G139" s="48"/>
       <c r="H139" s="46"/>
       <c r="I139" s="47"/>
       <c r="J139" s="47"/>
@@ -6574,34 +6641,48 @@
       <c r="P139" s="44"/>
       <c r="Q139" s="10"/>
     </row>
-    <row r="140" spans="1:17" ht="30" customHeight="1">
+    <row r="140" spans="1:17" ht="60.75" customHeight="1">
       <c r="A140" s="10"/>
-      <c r="B140" s="10"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="47"/>
-      <c r="E140" s="47"/>
-      <c r="F140" s="47"/>
-      <c r="G140" s="48"/>
-      <c r="H140" s="46"/>
-      <c r="I140" s="47"/>
-      <c r="J140" s="47"/>
-      <c r="K140" s="47"/>
-      <c r="L140" s="47"/>
-      <c r="M140" s="48"/>
-      <c r="N140" s="42"/>
-      <c r="O140" s="43"/>
-      <c r="P140" s="44"/>
+      <c r="B140" s="81" t="s">
+        <v>364</v>
+      </c>
+      <c r="C140" s="67" t="s">
+        <v>379</v>
+      </c>
+      <c r="D140" s="67"/>
+      <c r="E140" s="67"/>
+      <c r="F140" s="67"/>
+      <c r="G140" s="67"/>
+      <c r="H140" s="72" t="s">
+        <v>374</v>
+      </c>
+      <c r="I140" s="73"/>
+      <c r="J140" s="73"/>
+      <c r="K140" s="73"/>
+      <c r="L140" s="73"/>
+      <c r="M140" s="74"/>
+      <c r="N140" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="O140" s="53"/>
+      <c r="P140" s="54"/>
       <c r="Q140" s="10"/>
     </row>
     <row r="141" spans="1:17" ht="30" customHeight="1">
       <c r="A141" s="10"/>
-      <c r="B141" s="10"/>
-      <c r="C141" s="72"/>
+      <c r="B141" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C141" s="72" t="s">
+        <v>380</v>
+      </c>
       <c r="D141" s="73"/>
       <c r="E141" s="73"/>
       <c r="F141" s="73"/>
       <c r="G141" s="74"/>
-      <c r="H141" s="46"/>
+      <c r="H141" s="46" t="s">
+        <v>381</v>
+      </c>
       <c r="I141" s="47"/>
       <c r="J141" s="47"/>
       <c r="K141" s="47"/>
@@ -6615,11 +6696,11 @@
     <row r="142" spans="1:17" ht="30" customHeight="1">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
-      <c r="C142" s="46"/>
-      <c r="D142" s="47"/>
-      <c r="E142" s="47"/>
-      <c r="F142" s="47"/>
-      <c r="G142" s="48"/>
+      <c r="C142" s="72"/>
+      <c r="D142" s="73"/>
+      <c r="E142" s="73"/>
+      <c r="F142" s="73"/>
+      <c r="G142" s="74"/>
       <c r="H142" s="46"/>
       <c r="I142" s="47"/>
       <c r="J142" s="47"/>
@@ -6632,13 +6713,17 @@
       <c r="Q142" s="10"/>
     </row>
     <row r="143" spans="1:17" ht="30" customHeight="1">
-      <c r="A143" s="10"/>
+      <c r="A143" s="10">
+        <v>14</v>
+      </c>
       <c r="B143" s="10"/>
-      <c r="C143" s="75"/>
-      <c r="D143" s="75"/>
-      <c r="E143" s="75"/>
-      <c r="F143" s="75"/>
-      <c r="G143" s="75"/>
+      <c r="C143" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="D143" s="67"/>
+      <c r="E143" s="67"/>
+      <c r="F143" s="67"/>
+      <c r="G143" s="67"/>
       <c r="H143" s="46"/>
       <c r="I143" s="47"/>
       <c r="J143" s="47"/>
@@ -6653,11 +6738,13 @@
     <row r="144" spans="1:17" ht="30" customHeight="1">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
-      <c r="C144" s="46"/>
-      <c r="D144" s="47"/>
-      <c r="E144" s="47"/>
-      <c r="F144" s="47"/>
-      <c r="G144" s="48"/>
+      <c r="C144" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="D144" s="67"/>
+      <c r="E144" s="67"/>
+      <c r="F144" s="67"/>
+      <c r="G144" s="67"/>
       <c r="H144" s="46"/>
       <c r="I144" s="47"/>
       <c r="J144" s="47"/>
@@ -6669,14 +6756,16 @@
       <c r="P144" s="44"/>
       <c r="Q144" s="10"/>
     </row>
-    <row r="145" spans="1:17" ht="30" customHeight="1">
+    <row r="145" spans="1:17" ht="98.25" customHeight="1">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
-      <c r="C145" s="72"/>
-      <c r="D145" s="73"/>
-      <c r="E145" s="73"/>
-      <c r="F145" s="73"/>
-      <c r="G145" s="74"/>
+      <c r="C145" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="D145" s="75"/>
+      <c r="E145" s="75"/>
+      <c r="F145" s="75"/>
+      <c r="G145" s="75"/>
       <c r="H145" s="46"/>
       <c r="I145" s="47"/>
       <c r="J145" s="47"/>
@@ -6691,11 +6780,13 @@
     <row r="146" spans="1:17" ht="30" customHeight="1">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
-      <c r="C146" s="46"/>
-      <c r="D146" s="47"/>
-      <c r="E146" s="47"/>
-      <c r="F146" s="47"/>
-      <c r="G146" s="48"/>
+      <c r="C146" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="D146" s="75"/>
+      <c r="E146" s="75"/>
+      <c r="F146" s="75"/>
+      <c r="G146" s="75"/>
       <c r="H146" s="46"/>
       <c r="I146" s="47"/>
       <c r="J146" s="47"/>
@@ -6710,7 +6801,9 @@
     <row r="147" spans="1:17" ht="30" customHeight="1">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
-      <c r="C147" s="75"/>
+      <c r="C147" s="75" t="s">
+        <v>303</v>
+      </c>
       <c r="D147" s="75"/>
       <c r="E147" s="75"/>
       <c r="F147" s="75"/>
@@ -6729,11 +6822,13 @@
     <row r="148" spans="1:17" ht="30" customHeight="1">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
-      <c r="C148" s="46"/>
-      <c r="D148" s="47"/>
-      <c r="E148" s="47"/>
-      <c r="F148" s="47"/>
-      <c r="G148" s="48"/>
+      <c r="C148" s="75" t="s">
+        <v>382</v>
+      </c>
+      <c r="D148" s="75"/>
+      <c r="E148" s="75"/>
+      <c r="F148" s="75"/>
+      <c r="G148" s="75"/>
       <c r="H148" s="46"/>
       <c r="I148" s="47"/>
       <c r="J148" s="47"/>
@@ -6748,11 +6843,13 @@
     <row r="149" spans="1:17" ht="30" customHeight="1">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
-      <c r="C149" s="72"/>
-      <c r="D149" s="73"/>
-      <c r="E149" s="73"/>
-      <c r="F149" s="73"/>
-      <c r="G149" s="74"/>
+      <c r="C149" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="D149" s="47"/>
+      <c r="E149" s="47"/>
+      <c r="F149" s="47"/>
+      <c r="G149" s="48"/>
       <c r="H149" s="46"/>
       <c r="I149" s="47"/>
       <c r="J149" s="47"/>
@@ -6767,11 +6864,13 @@
     <row r="150" spans="1:17" ht="30" customHeight="1">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
-      <c r="C150" s="46"/>
-      <c r="D150" s="47"/>
-      <c r="E150" s="47"/>
-      <c r="F150" s="47"/>
-      <c r="G150" s="48"/>
+      <c r="C150" s="75" t="s">
+        <v>384</v>
+      </c>
+      <c r="D150" s="75"/>
+      <c r="E150" s="75"/>
+      <c r="F150" s="75"/>
+      <c r="G150" s="75"/>
       <c r="H150" s="46"/>
       <c r="I150" s="47"/>
       <c r="J150" s="47"/>
@@ -6786,11 +6885,13 @@
     <row r="151" spans="1:17" ht="30" customHeight="1">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
-      <c r="C151" s="75"/>
-      <c r="D151" s="75"/>
-      <c r="E151" s="75"/>
-      <c r="F151" s="75"/>
-      <c r="G151" s="75"/>
+      <c r="C151" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="D151" s="47"/>
+      <c r="E151" s="47"/>
+      <c r="F151" s="47"/>
+      <c r="G151" s="48"/>
       <c r="H151" s="46"/>
       <c r="I151" s="47"/>
       <c r="J151" s="47"/>
@@ -6805,11 +6906,13 @@
     <row r="152" spans="1:17" ht="30" customHeight="1">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
-      <c r="C152" s="46"/>
-      <c r="D152" s="47"/>
-      <c r="E152" s="47"/>
-      <c r="F152" s="47"/>
-      <c r="G152" s="48"/>
+      <c r="C152" s="75" t="s">
+        <v>386</v>
+      </c>
+      <c r="D152" s="75"/>
+      <c r="E152" s="75"/>
+      <c r="F152" s="75"/>
+      <c r="G152" s="75"/>
       <c r="H152" s="46"/>
       <c r="I152" s="47"/>
       <c r="J152" s="47"/>
@@ -6824,11 +6927,13 @@
     <row r="153" spans="1:17" ht="30" customHeight="1">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
-      <c r="C153" s="72"/>
-      <c r="D153" s="73"/>
-      <c r="E153" s="73"/>
-      <c r="F153" s="73"/>
-      <c r="G153" s="74"/>
+      <c r="C153" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="D153" s="47"/>
+      <c r="E153" s="47"/>
+      <c r="F153" s="47"/>
+      <c r="G153" s="48"/>
       <c r="H153" s="46"/>
       <c r="I153" s="47"/>
       <c r="J153" s="47"/>
@@ -6840,33 +6945,41 @@
       <c r="P153" s="44"/>
       <c r="Q153" s="10"/>
     </row>
-    <row r="154" spans="1:17" ht="30" customHeight="1">
+    <row r="154" spans="1:17" ht="52.5" customHeight="1">
       <c r="A154" s="10"/>
-      <c r="B154" s="10"/>
-      <c r="C154" s="46"/>
-      <c r="D154" s="47"/>
-      <c r="E154" s="47"/>
-      <c r="F154" s="47"/>
-      <c r="G154" s="48"/>
-      <c r="H154" s="46"/>
-      <c r="I154" s="47"/>
-      <c r="J154" s="47"/>
-      <c r="K154" s="47"/>
-      <c r="L154" s="47"/>
-      <c r="M154" s="48"/>
-      <c r="N154" s="42"/>
-      <c r="O154" s="43"/>
-      <c r="P154" s="44"/>
+      <c r="B154" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C154" s="72" t="s">
+        <v>327</v>
+      </c>
+      <c r="D154" s="73"/>
+      <c r="E154" s="73"/>
+      <c r="F154" s="73"/>
+      <c r="G154" s="74"/>
+      <c r="H154" s="72" t="s">
+        <v>388</v>
+      </c>
+      <c r="I154" s="73"/>
+      <c r="J154" s="73"/>
+      <c r="K154" s="73"/>
+      <c r="L154" s="73"/>
+      <c r="M154" s="74"/>
+      <c r="N154" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="O154" s="53"/>
+      <c r="P154" s="54"/>
       <c r="Q154" s="10"/>
     </row>
     <row r="155" spans="1:17" ht="30" customHeight="1">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
-      <c r="C155" s="75"/>
-      <c r="D155" s="75"/>
-      <c r="E155" s="75"/>
-      <c r="F155" s="75"/>
-      <c r="G155" s="75"/>
+      <c r="C155" s="46"/>
+      <c r="D155" s="47"/>
+      <c r="E155" s="47"/>
+      <c r="F155" s="47"/>
+      <c r="G155" s="48"/>
       <c r="H155" s="46"/>
       <c r="I155" s="47"/>
       <c r="J155" s="47"/>
@@ -6881,11 +6994,11 @@
     <row r="156" spans="1:17" ht="30" customHeight="1">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
-      <c r="C156" s="46"/>
-      <c r="D156" s="47"/>
-      <c r="E156" s="47"/>
-      <c r="F156" s="47"/>
-      <c r="G156" s="48"/>
+      <c r="C156" s="75"/>
+      <c r="D156" s="75"/>
+      <c r="E156" s="75"/>
+      <c r="F156" s="75"/>
+      <c r="G156" s="75"/>
       <c r="H156" s="46"/>
       <c r="I156" s="47"/>
       <c r="J156" s="47"/>
@@ -6900,11 +7013,11 @@
     <row r="157" spans="1:17" ht="30" customHeight="1">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
-      <c r="C157" s="72"/>
-      <c r="D157" s="73"/>
-      <c r="E157" s="73"/>
-      <c r="F157" s="73"/>
-      <c r="G157" s="74"/>
+      <c r="C157" s="46"/>
+      <c r="D157" s="47"/>
+      <c r="E157" s="47"/>
+      <c r="F157" s="47"/>
+      <c r="G157" s="48"/>
       <c r="H157" s="46"/>
       <c r="I157" s="47"/>
       <c r="J157" s="47"/>
@@ -6919,11 +7032,11 @@
     <row r="158" spans="1:17" ht="30" customHeight="1">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
-      <c r="C158" s="46"/>
-      <c r="D158" s="47"/>
-      <c r="E158" s="47"/>
-      <c r="F158" s="47"/>
-      <c r="G158" s="48"/>
+      <c r="C158" s="72"/>
+      <c r="D158" s="73"/>
+      <c r="E158" s="73"/>
+      <c r="F158" s="73"/>
+      <c r="G158" s="74"/>
       <c r="H158" s="46"/>
       <c r="I158" s="47"/>
       <c r="J158" s="47"/>
@@ -6938,11 +7051,11 @@
     <row r="159" spans="1:17" ht="30" customHeight="1">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
-      <c r="C159" s="75"/>
-      <c r="D159" s="75"/>
-      <c r="E159" s="75"/>
-      <c r="F159" s="75"/>
-      <c r="G159" s="75"/>
+      <c r="C159" s="46"/>
+      <c r="D159" s="47"/>
+      <c r="E159" s="47"/>
+      <c r="F159" s="47"/>
+      <c r="G159" s="48"/>
       <c r="H159" s="46"/>
       <c r="I159" s="47"/>
       <c r="J159" s="47"/>
@@ -6957,11 +7070,11 @@
     <row r="160" spans="1:17" ht="30" customHeight="1">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
-      <c r="C160" s="46"/>
-      <c r="D160" s="47"/>
-      <c r="E160" s="47"/>
-      <c r="F160" s="47"/>
-      <c r="G160" s="48"/>
+      <c r="C160" s="75"/>
+      <c r="D160" s="75"/>
+      <c r="E160" s="75"/>
+      <c r="F160" s="75"/>
+      <c r="G160" s="75"/>
       <c r="H160" s="46"/>
       <c r="I160" s="47"/>
       <c r="J160" s="47"/>
@@ -6976,11 +7089,11 @@
     <row r="161" spans="1:17" ht="30" customHeight="1">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
-      <c r="C161" s="72"/>
-      <c r="D161" s="73"/>
-      <c r="E161" s="73"/>
-      <c r="F161" s="73"/>
-      <c r="G161" s="74"/>
+      <c r="C161" s="46"/>
+      <c r="D161" s="47"/>
+      <c r="E161" s="47"/>
+      <c r="F161" s="47"/>
+      <c r="G161" s="48"/>
       <c r="H161" s="46"/>
       <c r="I161" s="47"/>
       <c r="J161" s="47"/>
@@ -6995,11 +7108,11 @@
     <row r="162" spans="1:17" ht="30" customHeight="1">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
-      <c r="C162" s="46"/>
-      <c r="D162" s="47"/>
-      <c r="E162" s="47"/>
-      <c r="F162" s="47"/>
-      <c r="G162" s="48"/>
+      <c r="C162" s="72"/>
+      <c r="D162" s="73"/>
+      <c r="E162" s="73"/>
+      <c r="F162" s="73"/>
+      <c r="G162" s="74"/>
       <c r="H162" s="46"/>
       <c r="I162" s="47"/>
       <c r="J162" s="47"/>
@@ -7014,11 +7127,11 @@
     <row r="163" spans="1:17" ht="30" customHeight="1">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
-      <c r="C163" s="75"/>
-      <c r="D163" s="75"/>
-      <c r="E163" s="75"/>
-      <c r="F163" s="75"/>
-      <c r="G163" s="75"/>
+      <c r="C163" s="46"/>
+      <c r="D163" s="47"/>
+      <c r="E163" s="47"/>
+      <c r="F163" s="47"/>
+      <c r="G163" s="48"/>
       <c r="H163" s="46"/>
       <c r="I163" s="47"/>
       <c r="J163" s="47"/>
@@ -7033,11 +7146,11 @@
     <row r="164" spans="1:17" ht="30" customHeight="1">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
-      <c r="C164" s="46"/>
-      <c r="D164" s="47"/>
-      <c r="E164" s="47"/>
-      <c r="F164" s="47"/>
-      <c r="G164" s="48"/>
+      <c r="C164" s="75"/>
+      <c r="D164" s="75"/>
+      <c r="E164" s="75"/>
+      <c r="F164" s="75"/>
+      <c r="G164" s="75"/>
       <c r="H164" s="46"/>
       <c r="I164" s="47"/>
       <c r="J164" s="47"/>
@@ -7052,11 +7165,11 @@
     <row r="165" spans="1:17" ht="30" customHeight="1">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
-      <c r="C165" s="72"/>
-      <c r="D165" s="73"/>
-      <c r="E165" s="73"/>
-      <c r="F165" s="73"/>
-      <c r="G165" s="74"/>
+      <c r="C165" s="46"/>
+      <c r="D165" s="47"/>
+      <c r="E165" s="47"/>
+      <c r="F165" s="47"/>
+      <c r="G165" s="48"/>
       <c r="H165" s="46"/>
       <c r="I165" s="47"/>
       <c r="J165" s="47"/>
@@ -7071,11 +7184,11 @@
     <row r="166" spans="1:17" ht="30" customHeight="1">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
-      <c r="C166" s="46"/>
-      <c r="D166" s="47"/>
-      <c r="E166" s="47"/>
-      <c r="F166" s="47"/>
-      <c r="G166" s="48"/>
+      <c r="C166" s="72"/>
+      <c r="D166" s="73"/>
+      <c r="E166" s="73"/>
+      <c r="F166" s="73"/>
+      <c r="G166" s="74"/>
       <c r="H166" s="46"/>
       <c r="I166" s="47"/>
       <c r="J166" s="47"/>
@@ -7090,11 +7203,11 @@
     <row r="167" spans="1:17" ht="30" customHeight="1">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
-      <c r="C167" s="75"/>
-      <c r="D167" s="75"/>
-      <c r="E167" s="75"/>
-      <c r="F167" s="75"/>
-      <c r="G167" s="75"/>
+      <c r="C167" s="46"/>
+      <c r="D167" s="47"/>
+      <c r="E167" s="47"/>
+      <c r="F167" s="47"/>
+      <c r="G167" s="48"/>
       <c r="H167" s="46"/>
       <c r="I167" s="47"/>
       <c r="J167" s="47"/>
@@ -7109,11 +7222,11 @@
     <row r="168" spans="1:17" ht="30" customHeight="1">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
-      <c r="C168" s="46"/>
-      <c r="D168" s="47"/>
-      <c r="E168" s="47"/>
-      <c r="F168" s="47"/>
-      <c r="G168" s="48"/>
+      <c r="C168" s="75"/>
+      <c r="D168" s="75"/>
+      <c r="E168" s="75"/>
+      <c r="F168" s="75"/>
+      <c r="G168" s="75"/>
       <c r="H168" s="46"/>
       <c r="I168" s="47"/>
       <c r="J168" s="47"/>
@@ -7128,11 +7241,11 @@
     <row r="169" spans="1:17" ht="30" customHeight="1">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
-      <c r="C169" s="72"/>
-      <c r="D169" s="73"/>
-      <c r="E169" s="73"/>
-      <c r="F169" s="73"/>
-      <c r="G169" s="74"/>
+      <c r="C169" s="46"/>
+      <c r="D169" s="47"/>
+      <c r="E169" s="47"/>
+      <c r="F169" s="47"/>
+      <c r="G169" s="48"/>
       <c r="H169" s="46"/>
       <c r="I169" s="47"/>
       <c r="J169" s="47"/>
@@ -7147,11 +7260,11 @@
     <row r="170" spans="1:17" ht="30" customHeight="1">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
-      <c r="C170" s="46"/>
-      <c r="D170" s="47"/>
-      <c r="E170" s="47"/>
-      <c r="F170" s="47"/>
-      <c r="G170" s="48"/>
+      <c r="C170" s="72"/>
+      <c r="D170" s="73"/>
+      <c r="E170" s="73"/>
+      <c r="F170" s="73"/>
+      <c r="G170" s="74"/>
       <c r="H170" s="46"/>
       <c r="I170" s="47"/>
       <c r="J170" s="47"/>
@@ -7166,11 +7279,11 @@
     <row r="171" spans="1:17" ht="30" customHeight="1">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
-      <c r="C171" s="75"/>
-      <c r="D171" s="75"/>
-      <c r="E171" s="75"/>
-      <c r="F171" s="75"/>
-      <c r="G171" s="75"/>
+      <c r="C171" s="46"/>
+      <c r="D171" s="47"/>
+      <c r="E171" s="47"/>
+      <c r="F171" s="47"/>
+      <c r="G171" s="48"/>
       <c r="H171" s="46"/>
       <c r="I171" s="47"/>
       <c r="J171" s="47"/>
@@ -7185,11 +7298,11 @@
     <row r="172" spans="1:17" ht="30" customHeight="1">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
-      <c r="C172" s="46"/>
-      <c r="D172" s="47"/>
-      <c r="E172" s="47"/>
-      <c r="F172" s="47"/>
-      <c r="G172" s="48"/>
+      <c r="C172" s="75"/>
+      <c r="D172" s="75"/>
+      <c r="E172" s="75"/>
+      <c r="F172" s="75"/>
+      <c r="G172" s="75"/>
       <c r="H172" s="46"/>
       <c r="I172" s="47"/>
       <c r="J172" s="47"/>
@@ -7204,11 +7317,11 @@
     <row r="173" spans="1:17" ht="30" customHeight="1">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
-      <c r="C173" s="72"/>
-      <c r="D173" s="73"/>
-      <c r="E173" s="73"/>
-      <c r="F173" s="73"/>
-      <c r="G173" s="74"/>
+      <c r="C173" s="46"/>
+      <c r="D173" s="47"/>
+      <c r="E173" s="47"/>
+      <c r="F173" s="47"/>
+      <c r="G173" s="48"/>
       <c r="H173" s="46"/>
       <c r="I173" s="47"/>
       <c r="J173" s="47"/>
@@ -7223,11 +7336,11 @@
     <row r="174" spans="1:17" ht="30" customHeight="1">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
-      <c r="C174" s="46"/>
-      <c r="D174" s="47"/>
-      <c r="E174" s="47"/>
-      <c r="F174" s="47"/>
-      <c r="G174" s="48"/>
+      <c r="C174" s="72"/>
+      <c r="D174" s="73"/>
+      <c r="E174" s="73"/>
+      <c r="F174" s="73"/>
+      <c r="G174" s="74"/>
       <c r="H174" s="46"/>
       <c r="I174" s="47"/>
       <c r="J174" s="47"/>
@@ -7242,11 +7355,11 @@
     <row r="175" spans="1:17" ht="30" customHeight="1">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
-      <c r="C175" s="75"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="75"/>
-      <c r="F175" s="75"/>
-      <c r="G175" s="75"/>
+      <c r="C175" s="46"/>
+      <c r="D175" s="47"/>
+      <c r="E175" s="47"/>
+      <c r="F175" s="47"/>
+      <c r="G175" s="48"/>
       <c r="H175" s="46"/>
       <c r="I175" s="47"/>
       <c r="J175" s="47"/>
@@ -7261,11 +7374,11 @@
     <row r="176" spans="1:17" ht="30" customHeight="1">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
-      <c r="C176" s="46"/>
-      <c r="D176" s="47"/>
-      <c r="E176" s="47"/>
-      <c r="F176" s="47"/>
-      <c r="G176" s="48"/>
+      <c r="C176" s="75"/>
+      <c r="D176" s="75"/>
+      <c r="E176" s="75"/>
+      <c r="F176" s="75"/>
+      <c r="G176" s="75"/>
       <c r="H176" s="46"/>
       <c r="I176" s="47"/>
       <c r="J176" s="47"/>
@@ -7280,11 +7393,11 @@
     <row r="177" spans="1:17" ht="30" customHeight="1">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
-      <c r="C177" s="72"/>
-      <c r="D177" s="73"/>
-      <c r="E177" s="73"/>
-      <c r="F177" s="73"/>
-      <c r="G177" s="74"/>
+      <c r="C177" s="46"/>
+      <c r="D177" s="47"/>
+      <c r="E177" s="47"/>
+      <c r="F177" s="47"/>
+      <c r="G177" s="48"/>
       <c r="H177" s="46"/>
       <c r="I177" s="47"/>
       <c r="J177" s="47"/>
@@ -7299,11 +7412,11 @@
     <row r="178" spans="1:17" ht="30" customHeight="1">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
-      <c r="C178" s="46"/>
-      <c r="D178" s="47"/>
-      <c r="E178" s="47"/>
-      <c r="F178" s="47"/>
-      <c r="G178" s="48"/>
+      <c r="C178" s="72"/>
+      <c r="D178" s="73"/>
+      <c r="E178" s="73"/>
+      <c r="F178" s="73"/>
+      <c r="G178" s="74"/>
       <c r="H178" s="46"/>
       <c r="I178" s="47"/>
       <c r="J178" s="47"/>
@@ -7318,11 +7431,11 @@
     <row r="179" spans="1:17" ht="30" customHeight="1">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
-      <c r="C179" s="75"/>
-      <c r="D179" s="75"/>
-      <c r="E179" s="75"/>
-      <c r="F179" s="75"/>
-      <c r="G179" s="75"/>
+      <c r="C179" s="46"/>
+      <c r="D179" s="47"/>
+      <c r="E179" s="47"/>
+      <c r="F179" s="47"/>
+      <c r="G179" s="48"/>
       <c r="H179" s="46"/>
       <c r="I179" s="47"/>
       <c r="J179" s="47"/>
@@ -7337,11 +7450,11 @@
     <row r="180" spans="1:17" ht="30" customHeight="1">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
-      <c r="C180" s="46"/>
-      <c r="D180" s="47"/>
-      <c r="E180" s="47"/>
-      <c r="F180" s="47"/>
-      <c r="G180" s="48"/>
+      <c r="C180" s="75"/>
+      <c r="D180" s="75"/>
+      <c r="E180" s="75"/>
+      <c r="F180" s="75"/>
+      <c r="G180" s="75"/>
       <c r="H180" s="46"/>
       <c r="I180" s="47"/>
       <c r="J180" s="47"/>
@@ -7356,11 +7469,11 @@
     <row r="181" spans="1:17" ht="30" customHeight="1">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
-      <c r="C181" s="72"/>
-      <c r="D181" s="73"/>
-      <c r="E181" s="73"/>
-      <c r="F181" s="73"/>
-      <c r="G181" s="74"/>
+      <c r="C181" s="46"/>
+      <c r="D181" s="47"/>
+      <c r="E181" s="47"/>
+      <c r="F181" s="47"/>
+      <c r="G181" s="48"/>
       <c r="H181" s="46"/>
       <c r="I181" s="47"/>
       <c r="J181" s="47"/>
@@ -7375,11 +7488,11 @@
     <row r="182" spans="1:17" ht="30" customHeight="1">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
-      <c r="C182" s="46"/>
-      <c r="D182" s="47"/>
-      <c r="E182" s="47"/>
-      <c r="F182" s="47"/>
-      <c r="G182" s="48"/>
+      <c r="C182" s="72"/>
+      <c r="D182" s="73"/>
+      <c r="E182" s="73"/>
+      <c r="F182" s="73"/>
+      <c r="G182" s="74"/>
       <c r="H182" s="46"/>
       <c r="I182" s="47"/>
       <c r="J182" s="47"/>
@@ -7394,11 +7507,11 @@
     <row r="183" spans="1:17" ht="30" customHeight="1">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
-      <c r="C183" s="75"/>
-      <c r="D183" s="75"/>
-      <c r="E183" s="75"/>
-      <c r="F183" s="75"/>
-      <c r="G183" s="75"/>
+      <c r="C183" s="46"/>
+      <c r="D183" s="47"/>
+      <c r="E183" s="47"/>
+      <c r="F183" s="47"/>
+      <c r="G183" s="48"/>
       <c r="H183" s="46"/>
       <c r="I183" s="47"/>
       <c r="J183" s="47"/>
@@ -7413,11 +7526,11 @@
     <row r="184" spans="1:17" ht="30" customHeight="1">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
-      <c r="C184" s="46"/>
-      <c r="D184" s="47"/>
-      <c r="E184" s="47"/>
-      <c r="F184" s="47"/>
-      <c r="G184" s="48"/>
+      <c r="C184" s="75"/>
+      <c r="D184" s="75"/>
+      <c r="E184" s="75"/>
+      <c r="F184" s="75"/>
+      <c r="G184" s="75"/>
       <c r="H184" s="46"/>
       <c r="I184" s="47"/>
       <c r="J184" s="47"/>
@@ -7432,11 +7545,11 @@
     <row r="185" spans="1:17" ht="30" customHeight="1">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
-      <c r="C185" s="72"/>
-      <c r="D185" s="73"/>
-      <c r="E185" s="73"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="74"/>
+      <c r="C185" s="46"/>
+      <c r="D185" s="47"/>
+      <c r="E185" s="47"/>
+      <c r="F185" s="47"/>
+      <c r="G185" s="48"/>
       <c r="H185" s="46"/>
       <c r="I185" s="47"/>
       <c r="J185" s="47"/>
@@ -7451,11 +7564,11 @@
     <row r="186" spans="1:17" ht="30" customHeight="1">
       <c r="A186" s="10"/>
       <c r="B186" s="10"/>
-      <c r="C186" s="46"/>
-      <c r="D186" s="47"/>
-      <c r="E186" s="47"/>
-      <c r="F186" s="47"/>
-      <c r="G186" s="48"/>
+      <c r="C186" s="72"/>
+      <c r="D186" s="73"/>
+      <c r="E186" s="73"/>
+      <c r="F186" s="73"/>
+      <c r="G186" s="74"/>
       <c r="H186" s="46"/>
       <c r="I186" s="47"/>
       <c r="J186" s="47"/>
@@ -7470,11 +7583,11 @@
     <row r="187" spans="1:17" ht="30" customHeight="1">
       <c r="A187" s="10"/>
       <c r="B187" s="10"/>
-      <c r="C187" s="75"/>
-      <c r="D187" s="75"/>
-      <c r="E187" s="75"/>
-      <c r="F187" s="75"/>
-      <c r="G187" s="75"/>
+      <c r="C187" s="46"/>
+      <c r="D187" s="47"/>
+      <c r="E187" s="47"/>
+      <c r="F187" s="47"/>
+      <c r="G187" s="48"/>
       <c r="H187" s="46"/>
       <c r="I187" s="47"/>
       <c r="J187" s="47"/>
@@ -7489,11 +7602,11 @@
     <row r="188" spans="1:17" ht="30" customHeight="1">
       <c r="A188" s="10"/>
       <c r="B188" s="10"/>
-      <c r="C188" s="46"/>
-      <c r="D188" s="47"/>
-      <c r="E188" s="47"/>
-      <c r="F188" s="47"/>
-      <c r="G188" s="48"/>
+      <c r="C188" s="75"/>
+      <c r="D188" s="75"/>
+      <c r="E188" s="75"/>
+      <c r="F188" s="75"/>
+      <c r="G188" s="75"/>
       <c r="H188" s="46"/>
       <c r="I188" s="47"/>
       <c r="J188" s="47"/>
@@ -7508,11 +7621,11 @@
     <row r="189" spans="1:17" ht="30" customHeight="1">
       <c r="A189" s="10"/>
       <c r="B189" s="10"/>
-      <c r="C189" s="72"/>
-      <c r="D189" s="73"/>
-      <c r="E189" s="73"/>
-      <c r="F189" s="73"/>
-      <c r="G189" s="74"/>
+      <c r="C189" s="46"/>
+      <c r="D189" s="47"/>
+      <c r="E189" s="47"/>
+      <c r="F189" s="47"/>
+      <c r="G189" s="48"/>
       <c r="H189" s="46"/>
       <c r="I189" s="47"/>
       <c r="J189" s="47"/>
@@ -7527,11 +7640,11 @@
     <row r="190" spans="1:17" ht="30" customHeight="1">
       <c r="A190" s="10"/>
       <c r="B190" s="10"/>
-      <c r="C190" s="46"/>
-      <c r="D190" s="47"/>
-      <c r="E190" s="47"/>
-      <c r="F190" s="47"/>
-      <c r="G190" s="48"/>
+      <c r="C190" s="72"/>
+      <c r="D190" s="73"/>
+      <c r="E190" s="73"/>
+      <c r="F190" s="73"/>
+      <c r="G190" s="74"/>
       <c r="H190" s="46"/>
       <c r="I190" s="47"/>
       <c r="J190" s="47"/>
@@ -7546,11 +7659,11 @@
     <row r="191" spans="1:17" ht="30" customHeight="1">
       <c r="A191" s="10"/>
       <c r="B191" s="10"/>
-      <c r="C191" s="75"/>
-      <c r="D191" s="75"/>
-      <c r="E191" s="75"/>
-      <c r="F191" s="75"/>
-      <c r="G191" s="75"/>
+      <c r="C191" s="46"/>
+      <c r="D191" s="47"/>
+      <c r="E191" s="47"/>
+      <c r="F191" s="47"/>
+      <c r="G191" s="48"/>
       <c r="H191" s="46"/>
       <c r="I191" s="47"/>
       <c r="J191" s="47"/>
@@ -7565,11 +7678,11 @@
     <row r="192" spans="1:17" ht="30" customHeight="1">
       <c r="A192" s="10"/>
       <c r="B192" s="10"/>
-      <c r="C192" s="46"/>
-      <c r="D192" s="47"/>
-      <c r="E192" s="47"/>
-      <c r="F192" s="47"/>
-      <c r="G192" s="48"/>
+      <c r="C192" s="75"/>
+      <c r="D192" s="75"/>
+      <c r="E192" s="75"/>
+      <c r="F192" s="75"/>
+      <c r="G192" s="75"/>
       <c r="H192" s="46"/>
       <c r="I192" s="47"/>
       <c r="J192" s="47"/>
@@ -7584,11 +7697,11 @@
     <row r="193" spans="1:17" ht="30" customHeight="1">
       <c r="A193" s="10"/>
       <c r="B193" s="10"/>
-      <c r="C193" s="72"/>
-      <c r="D193" s="73"/>
-      <c r="E193" s="73"/>
-      <c r="F193" s="73"/>
-      <c r="G193" s="74"/>
+      <c r="C193" s="46"/>
+      <c r="D193" s="47"/>
+      <c r="E193" s="47"/>
+      <c r="F193" s="47"/>
+      <c r="G193" s="48"/>
       <c r="H193" s="46"/>
       <c r="I193" s="47"/>
       <c r="J193" s="47"/>
@@ -7603,11 +7716,11 @@
     <row r="194" spans="1:17" ht="30" customHeight="1">
       <c r="A194" s="10"/>
       <c r="B194" s="10"/>
-      <c r="C194" s="46"/>
-      <c r="D194" s="47"/>
-      <c r="E194" s="47"/>
-      <c r="F194" s="47"/>
-      <c r="G194" s="48"/>
+      <c r="C194" s="72"/>
+      <c r="D194" s="73"/>
+      <c r="E194" s="73"/>
+      <c r="F194" s="73"/>
+      <c r="G194" s="74"/>
       <c r="H194" s="46"/>
       <c r="I194" s="47"/>
       <c r="J194" s="47"/>
@@ -7622,11 +7735,11 @@
     <row r="195" spans="1:17" ht="30" customHeight="1">
       <c r="A195" s="10"/>
       <c r="B195" s="10"/>
-      <c r="C195" s="75"/>
-      <c r="D195" s="75"/>
-      <c r="E195" s="75"/>
-      <c r="F195" s="75"/>
-      <c r="G195" s="75"/>
+      <c r="C195" s="46"/>
+      <c r="D195" s="47"/>
+      <c r="E195" s="47"/>
+      <c r="F195" s="47"/>
+      <c r="G195" s="48"/>
       <c r="H195" s="46"/>
       <c r="I195" s="47"/>
       <c r="J195" s="47"/>
@@ -7641,11 +7754,11 @@
     <row r="196" spans="1:17" ht="30" customHeight="1">
       <c r="A196" s="10"/>
       <c r="B196" s="10"/>
-      <c r="C196" s="46"/>
-      <c r="D196" s="47"/>
-      <c r="E196" s="47"/>
-      <c r="F196" s="47"/>
-      <c r="G196" s="48"/>
+      <c r="C196" s="75"/>
+      <c r="D196" s="75"/>
+      <c r="E196" s="75"/>
+      <c r="F196" s="75"/>
+      <c r="G196" s="75"/>
       <c r="H196" s="46"/>
       <c r="I196" s="47"/>
       <c r="J196" s="47"/>
@@ -7660,11 +7773,11 @@
     <row r="197" spans="1:17" ht="30" customHeight="1">
       <c r="A197" s="10"/>
       <c r="B197" s="10"/>
-      <c r="C197" s="72"/>
-      <c r="D197" s="73"/>
-      <c r="E197" s="73"/>
-      <c r="F197" s="73"/>
-      <c r="G197" s="74"/>
+      <c r="C197" s="46"/>
+      <c r="D197" s="47"/>
+      <c r="E197" s="47"/>
+      <c r="F197" s="47"/>
+      <c r="G197" s="48"/>
       <c r="H197" s="46"/>
       <c r="I197" s="47"/>
       <c r="J197" s="47"/>
@@ -7679,11 +7792,11 @@
     <row r="198" spans="1:17" ht="30" customHeight="1">
       <c r="A198" s="10"/>
       <c r="B198" s="10"/>
-      <c r="C198" s="46"/>
-      <c r="D198" s="47"/>
-      <c r="E198" s="47"/>
-      <c r="F198" s="47"/>
-      <c r="G198" s="48"/>
+      <c r="C198" s="72"/>
+      <c r="D198" s="73"/>
+      <c r="E198" s="73"/>
+      <c r="F198" s="73"/>
+      <c r="G198" s="74"/>
       <c r="H198" s="46"/>
       <c r="I198" s="47"/>
       <c r="J198" s="47"/>
@@ -7698,11 +7811,11 @@
     <row r="199" spans="1:17" ht="30" customHeight="1">
       <c r="A199" s="10"/>
       <c r="B199" s="10"/>
-      <c r="C199" s="75"/>
-      <c r="D199" s="75"/>
-      <c r="E199" s="75"/>
-      <c r="F199" s="75"/>
-      <c r="G199" s="75"/>
+      <c r="C199" s="46"/>
+      <c r="D199" s="47"/>
+      <c r="E199" s="47"/>
+      <c r="F199" s="47"/>
+      <c r="G199" s="48"/>
       <c r="H199" s="46"/>
       <c r="I199" s="47"/>
       <c r="J199" s="47"/>
@@ -7717,11 +7830,11 @@
     <row r="200" spans="1:17" ht="30" customHeight="1">
       <c r="A200" s="10"/>
       <c r="B200" s="10"/>
-      <c r="C200" s="46"/>
-      <c r="D200" s="47"/>
-      <c r="E200" s="47"/>
-      <c r="F200" s="47"/>
-      <c r="G200" s="48"/>
+      <c r="C200" s="75"/>
+      <c r="D200" s="75"/>
+      <c r="E200" s="75"/>
+      <c r="F200" s="75"/>
+      <c r="G200" s="75"/>
       <c r="H200" s="46"/>
       <c r="I200" s="47"/>
       <c r="J200" s="47"/>
@@ -7736,11 +7849,11 @@
     <row r="201" spans="1:17" ht="30" customHeight="1">
       <c r="A201" s="10"/>
       <c r="B201" s="10"/>
-      <c r="C201" s="72"/>
-      <c r="D201" s="73"/>
-      <c r="E201" s="73"/>
-      <c r="F201" s="73"/>
-      <c r="G201" s="74"/>
+      <c r="C201" s="46"/>
+      <c r="D201" s="47"/>
+      <c r="E201" s="47"/>
+      <c r="F201" s="47"/>
+      <c r="G201" s="48"/>
       <c r="H201" s="46"/>
       <c r="I201" s="47"/>
       <c r="J201" s="47"/>
@@ -7755,11 +7868,11 @@
     <row r="202" spans="1:17" ht="30" customHeight="1">
       <c r="A202" s="10"/>
       <c r="B202" s="10"/>
-      <c r="C202" s="46"/>
-      <c r="D202" s="47"/>
-      <c r="E202" s="47"/>
-      <c r="F202" s="47"/>
-      <c r="G202" s="48"/>
+      <c r="C202" s="72"/>
+      <c r="D202" s="73"/>
+      <c r="E202" s="73"/>
+      <c r="F202" s="73"/>
+      <c r="G202" s="74"/>
       <c r="H202" s="46"/>
       <c r="I202" s="47"/>
       <c r="J202" s="47"/>
@@ -7774,11 +7887,11 @@
     <row r="203" spans="1:17" ht="30" customHeight="1">
       <c r="A203" s="10"/>
       <c r="B203" s="10"/>
-      <c r="C203" s="75"/>
-      <c r="D203" s="75"/>
-      <c r="E203" s="75"/>
-      <c r="F203" s="75"/>
-      <c r="G203" s="75"/>
+      <c r="C203" s="46"/>
+      <c r="D203" s="47"/>
+      <c r="E203" s="47"/>
+      <c r="F203" s="47"/>
+      <c r="G203" s="48"/>
       <c r="H203" s="46"/>
       <c r="I203" s="47"/>
       <c r="J203" s="47"/>
@@ -7793,11 +7906,11 @@
     <row r="204" spans="1:17" ht="30" customHeight="1">
       <c r="A204" s="10"/>
       <c r="B204" s="10"/>
-      <c r="C204" s="46"/>
-      <c r="D204" s="47"/>
-      <c r="E204" s="47"/>
-      <c r="F204" s="47"/>
-      <c r="G204" s="48"/>
+      <c r="C204" s="75"/>
+      <c r="D204" s="75"/>
+      <c r="E204" s="75"/>
+      <c r="F204" s="75"/>
+      <c r="G204" s="75"/>
       <c r="H204" s="46"/>
       <c r="I204" s="47"/>
       <c r="J204" s="47"/>
@@ -7812,11 +7925,11 @@
     <row r="205" spans="1:17" ht="30" customHeight="1">
       <c r="A205" s="10"/>
       <c r="B205" s="10"/>
-      <c r="C205" s="72"/>
-      <c r="D205" s="73"/>
-      <c r="E205" s="73"/>
-      <c r="F205" s="73"/>
-      <c r="G205" s="74"/>
+      <c r="C205" s="46"/>
+      <c r="D205" s="47"/>
+      <c r="E205" s="47"/>
+      <c r="F205" s="47"/>
+      <c r="G205" s="48"/>
       <c r="H205" s="46"/>
       <c r="I205" s="47"/>
       <c r="J205" s="47"/>
@@ -7831,11 +7944,11 @@
     <row r="206" spans="1:17" ht="30" customHeight="1">
       <c r="A206" s="10"/>
       <c r="B206" s="10"/>
-      <c r="C206" s="46"/>
-      <c r="D206" s="47"/>
-      <c r="E206" s="47"/>
-      <c r="F206" s="47"/>
-      <c r="G206" s="48"/>
+      <c r="C206" s="72"/>
+      <c r="D206" s="73"/>
+      <c r="E206" s="73"/>
+      <c r="F206" s="73"/>
+      <c r="G206" s="74"/>
       <c r="H206" s="46"/>
       <c r="I206" s="47"/>
       <c r="J206" s="47"/>
@@ -7850,11 +7963,11 @@
     <row r="207" spans="1:17" ht="30" customHeight="1">
       <c r="A207" s="10"/>
       <c r="B207" s="10"/>
-      <c r="C207" s="75"/>
-      <c r="D207" s="75"/>
-      <c r="E207" s="75"/>
-      <c r="F207" s="75"/>
-      <c r="G207" s="75"/>
+      <c r="C207" s="46"/>
+      <c r="D207" s="47"/>
+      <c r="E207" s="47"/>
+      <c r="F207" s="47"/>
+      <c r="G207" s="48"/>
       <c r="H207" s="46"/>
       <c r="I207" s="47"/>
       <c r="J207" s="47"/>
@@ -7869,11 +7982,11 @@
     <row r="208" spans="1:17" ht="30" customHeight="1">
       <c r="A208" s="10"/>
       <c r="B208" s="10"/>
-      <c r="C208" s="46"/>
-      <c r="D208" s="47"/>
-      <c r="E208" s="47"/>
-      <c r="F208" s="47"/>
-      <c r="G208" s="48"/>
+      <c r="C208" s="75"/>
+      <c r="D208" s="75"/>
+      <c r="E208" s="75"/>
+      <c r="F208" s="75"/>
+      <c r="G208" s="75"/>
       <c r="H208" s="46"/>
       <c r="I208" s="47"/>
       <c r="J208" s="47"/>
@@ -7888,11 +8001,11 @@
     <row r="209" spans="1:17" ht="30" customHeight="1">
       <c r="A209" s="10"/>
       <c r="B209" s="10"/>
-      <c r="C209" s="72"/>
-      <c r="D209" s="73"/>
-      <c r="E209" s="73"/>
-      <c r="F209" s="73"/>
-      <c r="G209" s="74"/>
+      <c r="C209" s="46"/>
+      <c r="D209" s="47"/>
+      <c r="E209" s="47"/>
+      <c r="F209" s="47"/>
+      <c r="G209" s="48"/>
       <c r="H209" s="46"/>
       <c r="I209" s="47"/>
       <c r="J209" s="47"/>
@@ -7907,11 +8020,11 @@
     <row r="210" spans="1:17" ht="30" customHeight="1">
       <c r="A210" s="10"/>
       <c r="B210" s="10"/>
-      <c r="C210" s="46"/>
-      <c r="D210" s="47"/>
-      <c r="E210" s="47"/>
-      <c r="F210" s="47"/>
-      <c r="G210" s="48"/>
+      <c r="C210" s="72"/>
+      <c r="D210" s="73"/>
+      <c r="E210" s="73"/>
+      <c r="F210" s="73"/>
+      <c r="G210" s="74"/>
       <c r="H210" s="46"/>
       <c r="I210" s="47"/>
       <c r="J210" s="47"/>
@@ -7926,11 +8039,11 @@
     <row r="211" spans="1:17" ht="30" customHeight="1">
       <c r="A211" s="10"/>
       <c r="B211" s="10"/>
-      <c r="C211" s="75"/>
-      <c r="D211" s="75"/>
-      <c r="E211" s="75"/>
-      <c r="F211" s="75"/>
-      <c r="G211" s="75"/>
+      <c r="C211" s="46"/>
+      <c r="D211" s="47"/>
+      <c r="E211" s="47"/>
+      <c r="F211" s="47"/>
+      <c r="G211" s="48"/>
       <c r="H211" s="46"/>
       <c r="I211" s="47"/>
       <c r="J211" s="47"/>
@@ -7945,11 +8058,11 @@
     <row r="212" spans="1:17" ht="30" customHeight="1">
       <c r="A212" s="10"/>
       <c r="B212" s="10"/>
-      <c r="C212" s="46"/>
-      <c r="D212" s="47"/>
-      <c r="E212" s="47"/>
-      <c r="F212" s="47"/>
-      <c r="G212" s="48"/>
+      <c r="C212" s="75"/>
+      <c r="D212" s="75"/>
+      <c r="E212" s="75"/>
+      <c r="F212" s="75"/>
+      <c r="G212" s="75"/>
       <c r="H212" s="46"/>
       <c r="I212" s="47"/>
       <c r="J212" s="47"/>
@@ -7964,11 +8077,11 @@
     <row r="213" spans="1:17" ht="30" customHeight="1">
       <c r="A213" s="10"/>
       <c r="B213" s="10"/>
-      <c r="C213" s="72"/>
-      <c r="D213" s="73"/>
-      <c r="E213" s="73"/>
-      <c r="F213" s="73"/>
-      <c r="G213" s="74"/>
+      <c r="C213" s="46"/>
+      <c r="D213" s="47"/>
+      <c r="E213" s="47"/>
+      <c r="F213" s="47"/>
+      <c r="G213" s="48"/>
       <c r="H213" s="46"/>
       <c r="I213" s="47"/>
       <c r="J213" s="47"/>
@@ -7983,11 +8096,11 @@
     <row r="214" spans="1:17" ht="30" customHeight="1">
       <c r="A214" s="10"/>
       <c r="B214" s="10"/>
-      <c r="C214" s="46"/>
-      <c r="D214" s="47"/>
-      <c r="E214" s="47"/>
-      <c r="F214" s="47"/>
-      <c r="G214" s="48"/>
+      <c r="C214" s="72"/>
+      <c r="D214" s="73"/>
+      <c r="E214" s="73"/>
+      <c r="F214" s="73"/>
+      <c r="G214" s="74"/>
       <c r="H214" s="46"/>
       <c r="I214" s="47"/>
       <c r="J214" s="47"/>
@@ -8002,11 +8115,11 @@
     <row r="215" spans="1:17" ht="30" customHeight="1">
       <c r="A215" s="10"/>
       <c r="B215" s="10"/>
-      <c r="C215" s="75"/>
-      <c r="D215" s="75"/>
-      <c r="E215" s="75"/>
-      <c r="F215" s="75"/>
-      <c r="G215" s="75"/>
+      <c r="C215" s="46"/>
+      <c r="D215" s="47"/>
+      <c r="E215" s="47"/>
+      <c r="F215" s="47"/>
+      <c r="G215" s="48"/>
       <c r="H215" s="46"/>
       <c r="I215" s="47"/>
       <c r="J215" s="47"/>
@@ -8021,11 +8134,11 @@
     <row r="216" spans="1:17" ht="30" customHeight="1">
       <c r="A216" s="10"/>
       <c r="B216" s="10"/>
-      <c r="C216" s="46"/>
-      <c r="D216" s="47"/>
-      <c r="E216" s="47"/>
-      <c r="F216" s="47"/>
-      <c r="G216" s="48"/>
+      <c r="C216" s="75"/>
+      <c r="D216" s="75"/>
+      <c r="E216" s="75"/>
+      <c r="F216" s="75"/>
+      <c r="G216" s="75"/>
       <c r="H216" s="46"/>
       <c r="I216" s="47"/>
       <c r="J216" s="47"/>
@@ -8040,11 +8153,11 @@
     <row r="217" spans="1:17" ht="30" customHeight="1">
       <c r="A217" s="10"/>
       <c r="B217" s="10"/>
-      <c r="C217" s="72"/>
-      <c r="D217" s="73"/>
-      <c r="E217" s="73"/>
-      <c r="F217" s="73"/>
-      <c r="G217" s="74"/>
+      <c r="C217" s="46"/>
+      <c r="D217" s="47"/>
+      <c r="E217" s="47"/>
+      <c r="F217" s="47"/>
+      <c r="G217" s="48"/>
       <c r="H217" s="46"/>
       <c r="I217" s="47"/>
       <c r="J217" s="47"/>
@@ -8059,11 +8172,11 @@
     <row r="218" spans="1:17" ht="30" customHeight="1">
       <c r="A218" s="10"/>
       <c r="B218" s="10"/>
-      <c r="C218" s="46"/>
-      <c r="D218" s="47"/>
-      <c r="E218" s="47"/>
-      <c r="F218" s="47"/>
-      <c r="G218" s="48"/>
+      <c r="C218" s="72"/>
+      <c r="D218" s="73"/>
+      <c r="E218" s="73"/>
+      <c r="F218" s="73"/>
+      <c r="G218" s="74"/>
       <c r="H218" s="46"/>
       <c r="I218" s="47"/>
       <c r="J218" s="47"/>
@@ -8078,11 +8191,11 @@
     <row r="219" spans="1:17" ht="30" customHeight="1">
       <c r="A219" s="10"/>
       <c r="B219" s="10"/>
-      <c r="C219" s="75"/>
-      <c r="D219" s="75"/>
-      <c r="E219" s="75"/>
-      <c r="F219" s="75"/>
-      <c r="G219" s="75"/>
+      <c r="C219" s="46"/>
+      <c r="D219" s="47"/>
+      <c r="E219" s="47"/>
+      <c r="F219" s="47"/>
+      <c r="G219" s="48"/>
       <c r="H219" s="46"/>
       <c r="I219" s="47"/>
       <c r="J219" s="47"/>
@@ -8097,11 +8210,11 @@
     <row r="220" spans="1:17" ht="30" customHeight="1">
       <c r="A220" s="10"/>
       <c r="B220" s="10"/>
-      <c r="C220" s="46"/>
-      <c r="D220" s="47"/>
-      <c r="E220" s="47"/>
-      <c r="F220" s="47"/>
-      <c r="G220" s="48"/>
+      <c r="C220" s="75"/>
+      <c r="D220" s="75"/>
+      <c r="E220" s="75"/>
+      <c r="F220" s="75"/>
+      <c r="G220" s="75"/>
       <c r="H220" s="46"/>
       <c r="I220" s="47"/>
       <c r="J220" s="47"/>
@@ -8116,11 +8229,11 @@
     <row r="221" spans="1:17" ht="30" customHeight="1">
       <c r="A221" s="10"/>
       <c r="B221" s="10"/>
-      <c r="C221" s="72"/>
-      <c r="D221" s="73"/>
-      <c r="E221" s="73"/>
-      <c r="F221" s="73"/>
-      <c r="G221" s="74"/>
+      <c r="C221" s="46"/>
+      <c r="D221" s="47"/>
+      <c r="E221" s="47"/>
+      <c r="F221" s="47"/>
+      <c r="G221" s="48"/>
       <c r="H221" s="46"/>
       <c r="I221" s="47"/>
       <c r="J221" s="47"/>
@@ -8135,11 +8248,11 @@
     <row r="222" spans="1:17" ht="30" customHeight="1">
       <c r="A222" s="10"/>
       <c r="B222" s="10"/>
-      <c r="C222" s="46"/>
-      <c r="D222" s="47"/>
-      <c r="E222" s="47"/>
-      <c r="F222" s="47"/>
-      <c r="G222" s="48"/>
+      <c r="C222" s="72"/>
+      <c r="D222" s="73"/>
+      <c r="E222" s="73"/>
+      <c r="F222" s="73"/>
+      <c r="G222" s="74"/>
       <c r="H222" s="46"/>
       <c r="I222" s="47"/>
       <c r="J222" s="47"/>
@@ -8154,11 +8267,11 @@
     <row r="223" spans="1:17" ht="30" customHeight="1">
       <c r="A223" s="10"/>
       <c r="B223" s="10"/>
-      <c r="C223" s="75"/>
-      <c r="D223" s="75"/>
-      <c r="E223" s="75"/>
-      <c r="F223" s="75"/>
-      <c r="G223" s="75"/>
+      <c r="C223" s="46"/>
+      <c r="D223" s="47"/>
+      <c r="E223" s="47"/>
+      <c r="F223" s="47"/>
+      <c r="G223" s="48"/>
       <c r="H223" s="46"/>
       <c r="I223" s="47"/>
       <c r="J223" s="47"/>
@@ -8173,11 +8286,11 @@
     <row r="224" spans="1:17" ht="30" customHeight="1">
       <c r="A224" s="10"/>
       <c r="B224" s="10"/>
-      <c r="C224" s="46"/>
-      <c r="D224" s="47"/>
-      <c r="E224" s="47"/>
-      <c r="F224" s="47"/>
-      <c r="G224" s="48"/>
+      <c r="C224" s="75"/>
+      <c r="D224" s="75"/>
+      <c r="E224" s="75"/>
+      <c r="F224" s="75"/>
+      <c r="G224" s="75"/>
       <c r="H224" s="46"/>
       <c r="I224" s="47"/>
       <c r="J224" s="47"/>
@@ -8192,11 +8305,11 @@
     <row r="225" spans="1:17" ht="30" customHeight="1">
       <c r="A225" s="10"/>
       <c r="B225" s="10"/>
-      <c r="C225" s="72"/>
-      <c r="D225" s="73"/>
-      <c r="E225" s="73"/>
-      <c r="F225" s="73"/>
-      <c r="G225" s="74"/>
+      <c r="C225" s="46"/>
+      <c r="D225" s="47"/>
+      <c r="E225" s="47"/>
+      <c r="F225" s="47"/>
+      <c r="G225" s="48"/>
       <c r="H225" s="46"/>
       <c r="I225" s="47"/>
       <c r="J225" s="47"/>
@@ -8211,11 +8324,11 @@
     <row r="226" spans="1:17" ht="30" customHeight="1">
       <c r="A226" s="10"/>
       <c r="B226" s="10"/>
-      <c r="C226" s="46"/>
-      <c r="D226" s="47"/>
-      <c r="E226" s="47"/>
-      <c r="F226" s="47"/>
-      <c r="G226" s="48"/>
+      <c r="C226" s="72"/>
+      <c r="D226" s="73"/>
+      <c r="E226" s="73"/>
+      <c r="F226" s="73"/>
+      <c r="G226" s="74"/>
       <c r="H226" s="46"/>
       <c r="I226" s="47"/>
       <c r="J226" s="47"/>
@@ -8230,11 +8343,11 @@
     <row r="227" spans="1:17" ht="30" customHeight="1">
       <c r="A227" s="10"/>
       <c r="B227" s="10"/>
-      <c r="C227" s="75"/>
-      <c r="D227" s="75"/>
-      <c r="E227" s="75"/>
-      <c r="F227" s="75"/>
-      <c r="G227" s="75"/>
+      <c r="C227" s="46"/>
+      <c r="D227" s="47"/>
+      <c r="E227" s="47"/>
+      <c r="F227" s="47"/>
+      <c r="G227" s="48"/>
       <c r="H227" s="46"/>
       <c r="I227" s="47"/>
       <c r="J227" s="47"/>
@@ -8249,11 +8362,11 @@
     <row r="228" spans="1:17" ht="30" customHeight="1">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
-      <c r="C228" s="46"/>
-      <c r="D228" s="47"/>
-      <c r="E228" s="47"/>
-      <c r="F228" s="47"/>
-      <c r="G228" s="48"/>
+      <c r="C228" s="75"/>
+      <c r="D228" s="75"/>
+      <c r="E228" s="75"/>
+      <c r="F228" s="75"/>
+      <c r="G228" s="75"/>
       <c r="H228" s="46"/>
       <c r="I228" s="47"/>
       <c r="J228" s="47"/>
@@ -8268,11 +8381,11 @@
     <row r="229" spans="1:17" ht="30" customHeight="1">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
-      <c r="C229" s="72"/>
-      <c r="D229" s="73"/>
-      <c r="E229" s="73"/>
-      <c r="F229" s="73"/>
-      <c r="G229" s="74"/>
+      <c r="C229" s="46"/>
+      <c r="D229" s="47"/>
+      <c r="E229" s="47"/>
+      <c r="F229" s="47"/>
+      <c r="G229" s="48"/>
       <c r="H229" s="46"/>
       <c r="I229" s="47"/>
       <c r="J229" s="47"/>
@@ -8287,11 +8400,11 @@
     <row r="230" spans="1:17" ht="30" customHeight="1">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
-      <c r="C230" s="46"/>
-      <c r="D230" s="47"/>
-      <c r="E230" s="47"/>
-      <c r="F230" s="47"/>
-      <c r="G230" s="48"/>
+      <c r="C230" s="72"/>
+      <c r="D230" s="73"/>
+      <c r="E230" s="73"/>
+      <c r="F230" s="73"/>
+      <c r="G230" s="74"/>
       <c r="H230" s="46"/>
       <c r="I230" s="47"/>
       <c r="J230" s="47"/>
@@ -8303,326 +8416,331 @@
       <c r="P230" s="44"/>
       <c r="Q230" s="10"/>
     </row>
+    <row r="231" spans="1:17" ht="30" customHeight="1">
+      <c r="A231" s="10"/>
+      <c r="B231" s="10"/>
+      <c r="C231" s="46"/>
+      <c r="D231" s="47"/>
+      <c r="E231" s="47"/>
+      <c r="F231" s="47"/>
+      <c r="G231" s="48"/>
+      <c r="H231" s="46"/>
+      <c r="I231" s="47"/>
+      <c r="J231" s="47"/>
+      <c r="K231" s="47"/>
+      <c r="L231" s="47"/>
+      <c r="M231" s="48"/>
+      <c r="N231" s="42"/>
+      <c r="O231" s="43"/>
+      <c r="P231" s="44"/>
+      <c r="Q231" s="10"/>
+    </row>
+    <row r="232" spans="1:17" ht="30" customHeight="1">
+      <c r="A232" s="10"/>
+      <c r="B232" s="10"/>
+      <c r="C232" s="75"/>
+      <c r="D232" s="75"/>
+      <c r="E232" s="75"/>
+      <c r="F232" s="75"/>
+      <c r="G232" s="75"/>
+      <c r="H232" s="46"/>
+      <c r="I232" s="47"/>
+      <c r="J232" s="47"/>
+      <c r="K232" s="47"/>
+      <c r="L232" s="47"/>
+      <c r="M232" s="48"/>
+      <c r="N232" s="42"/>
+      <c r="O232" s="43"/>
+      <c r="P232" s="44"/>
+      <c r="Q232" s="10"/>
+    </row>
+    <row r="233" spans="1:17" ht="30" customHeight="1">
+      <c r="A233" s="10"/>
+      <c r="B233" s="10"/>
+      <c r="C233" s="46"/>
+      <c r="D233" s="47"/>
+      <c r="E233" s="47"/>
+      <c r="F233" s="47"/>
+      <c r="G233" s="48"/>
+      <c r="H233" s="46"/>
+      <c r="I233" s="47"/>
+      <c r="J233" s="47"/>
+      <c r="K233" s="47"/>
+      <c r="L233" s="47"/>
+      <c r="M233" s="48"/>
+      <c r="N233" s="42"/>
+      <c r="O233" s="43"/>
+      <c r="P233" s="44"/>
+      <c r="Q233" s="10"/>
+    </row>
+    <row r="234" spans="1:17" ht="30" customHeight="1">
+      <c r="A234" s="10"/>
+      <c r="B234" s="10"/>
+      <c r="C234" s="72"/>
+      <c r="D234" s="73"/>
+      <c r="E234" s="73"/>
+      <c r="F234" s="73"/>
+      <c r="G234" s="74"/>
+      <c r="H234" s="46"/>
+      <c r="I234" s="47"/>
+      <c r="J234" s="47"/>
+      <c r="K234" s="47"/>
+      <c r="L234" s="47"/>
+      <c r="M234" s="48"/>
+      <c r="N234" s="42"/>
+      <c r="O234" s="43"/>
+      <c r="P234" s="44"/>
+      <c r="Q234" s="10"/>
+    </row>
+    <row r="235" spans="1:17" ht="30" customHeight="1">
+      <c r="A235" s="10"/>
+      <c r="B235" s="10"/>
+      <c r="C235" s="46"/>
+      <c r="D235" s="47"/>
+      <c r="E235" s="47"/>
+      <c r="F235" s="47"/>
+      <c r="G235" s="48"/>
+      <c r="H235" s="46"/>
+      <c r="I235" s="47"/>
+      <c r="J235" s="47"/>
+      <c r="K235" s="47"/>
+      <c r="L235" s="47"/>
+      <c r="M235" s="48"/>
+      <c r="N235" s="42"/>
+      <c r="O235" s="43"/>
+      <c r="P235" s="44"/>
+      <c r="Q235" s="10"/>
+    </row>
+    <row r="236" spans="1:17" ht="30" customHeight="1">
+      <c r="A236" s="10"/>
+      <c r="B236" s="10"/>
+      <c r="C236" s="75"/>
+      <c r="D236" s="75"/>
+      <c r="E236" s="75"/>
+      <c r="F236" s="75"/>
+      <c r="G236" s="75"/>
+      <c r="H236" s="46"/>
+      <c r="I236" s="47"/>
+      <c r="J236" s="47"/>
+      <c r="K236" s="47"/>
+      <c r="L236" s="47"/>
+      <c r="M236" s="48"/>
+      <c r="N236" s="42"/>
+      <c r="O236" s="43"/>
+      <c r="P236" s="44"/>
+      <c r="Q236" s="10"/>
+    </row>
+    <row r="237" spans="1:17" ht="30" customHeight="1">
+      <c r="A237" s="10"/>
+      <c r="B237" s="10"/>
+      <c r="C237" s="46"/>
+      <c r="D237" s="47"/>
+      <c r="E237" s="47"/>
+      <c r="F237" s="47"/>
+      <c r="G237" s="48"/>
+      <c r="H237" s="46"/>
+      <c r="I237" s="47"/>
+      <c r="J237" s="47"/>
+      <c r="K237" s="47"/>
+      <c r="L237" s="47"/>
+      <c r="M237" s="48"/>
+      <c r="N237" s="42"/>
+      <c r="O237" s="43"/>
+      <c r="P237" s="44"/>
+      <c r="Q237" s="10"/>
+    </row>
+    <row r="238" spans="1:17" ht="30" customHeight="1">
+      <c r="A238" s="10"/>
+      <c r="B238" s="10"/>
+      <c r="C238" s="72"/>
+      <c r="D238" s="73"/>
+      <c r="E238" s="73"/>
+      <c r="F238" s="73"/>
+      <c r="G238" s="74"/>
+      <c r="H238" s="46"/>
+      <c r="I238" s="47"/>
+      <c r="J238" s="47"/>
+      <c r="K238" s="47"/>
+      <c r="L238" s="47"/>
+      <c r="M238" s="48"/>
+      <c r="N238" s="42"/>
+      <c r="O238" s="43"/>
+      <c r="P238" s="44"/>
+      <c r="Q238" s="10"/>
+    </row>
+    <row r="239" spans="1:17" ht="30" customHeight="1">
+      <c r="A239" s="10"/>
+      <c r="B239" s="10"/>
+      <c r="C239" s="46"/>
+      <c r="D239" s="47"/>
+      <c r="E239" s="47"/>
+      <c r="F239" s="47"/>
+      <c r="G239" s="48"/>
+      <c r="H239" s="46"/>
+      <c r="I239" s="47"/>
+      <c r="J239" s="47"/>
+      <c r="K239" s="47"/>
+      <c r="L239" s="47"/>
+      <c r="M239" s="48"/>
+      <c r="N239" s="42"/>
+      <c r="O239" s="43"/>
+      <c r="P239" s="44"/>
+      <c r="Q239" s="10"/>
+    </row>
+    <row r="240" spans="1:17" ht="30" customHeight="1">
+      <c r="A240" s="10"/>
+      <c r="B240" s="10"/>
+      <c r="C240" s="75"/>
+      <c r="D240" s="75"/>
+      <c r="E240" s="75"/>
+      <c r="F240" s="75"/>
+      <c r="G240" s="75"/>
+      <c r="H240" s="46"/>
+      <c r="I240" s="47"/>
+      <c r="J240" s="47"/>
+      <c r="K240" s="47"/>
+      <c r="L240" s="47"/>
+      <c r="M240" s="48"/>
+      <c r="N240" s="42"/>
+      <c r="O240" s="43"/>
+      <c r="P240" s="44"/>
+      <c r="Q240" s="10"/>
+    </row>
+    <row r="241" spans="1:17" ht="30" customHeight="1">
+      <c r="A241" s="10"/>
+      <c r="B241" s="10"/>
+      <c r="C241" s="46"/>
+      <c r="D241" s="47"/>
+      <c r="E241" s="47"/>
+      <c r="F241" s="47"/>
+      <c r="G241" s="48"/>
+      <c r="H241" s="46"/>
+      <c r="I241" s="47"/>
+      <c r="J241" s="47"/>
+      <c r="K241" s="47"/>
+      <c r="L241" s="47"/>
+      <c r="M241" s="48"/>
+      <c r="N241" s="42"/>
+      <c r="O241" s="43"/>
+      <c r="P241" s="44"/>
+      <c r="Q241" s="10"/>
+    </row>
+    <row r="242" spans="1:17" ht="30" customHeight="1">
+      <c r="A242" s="10"/>
+      <c r="B242" s="10"/>
+      <c r="C242" s="72"/>
+      <c r="D242" s="73"/>
+      <c r="E242" s="73"/>
+      <c r="F242" s="73"/>
+      <c r="G242" s="74"/>
+      <c r="H242" s="46"/>
+      <c r="I242" s="47"/>
+      <c r="J242" s="47"/>
+      <c r="K242" s="47"/>
+      <c r="L242" s="47"/>
+      <c r="M242" s="48"/>
+      <c r="N242" s="42"/>
+      <c r="O242" s="43"/>
+      <c r="P242" s="44"/>
+      <c r="Q242" s="10"/>
+    </row>
+    <row r="243" spans="1:17" ht="30" customHeight="1">
+      <c r="A243" s="10"/>
+      <c r="B243" s="10"/>
+      <c r="C243" s="46"/>
+      <c r="D243" s="47"/>
+      <c r="E243" s="47"/>
+      <c r="F243" s="47"/>
+      <c r="G243" s="48"/>
+      <c r="H243" s="46"/>
+      <c r="I243" s="47"/>
+      <c r="J243" s="47"/>
+      <c r="K243" s="47"/>
+      <c r="L243" s="47"/>
+      <c r="M243" s="48"/>
+      <c r="N243" s="42"/>
+      <c r="O243" s="43"/>
+      <c r="P243" s="44"/>
+      <c r="Q243" s="10"/>
+    </row>
+    <row r="244" spans="1:17" ht="30" customHeight="1">
+      <c r="A244" s="10"/>
+      <c r="B244" s="10"/>
+      <c r="C244" s="75"/>
+      <c r="D244" s="75"/>
+      <c r="E244" s="75"/>
+      <c r="F244" s="75"/>
+      <c r="G244" s="75"/>
+      <c r="H244" s="46"/>
+      <c r="I244" s="47"/>
+      <c r="J244" s="47"/>
+      <c r="K244" s="47"/>
+      <c r="L244" s="47"/>
+      <c r="M244" s="48"/>
+      <c r="N244" s="42"/>
+      <c r="O244" s="43"/>
+      <c r="P244" s="44"/>
+      <c r="Q244" s="10"/>
+    </row>
+    <row r="245" spans="1:17" ht="30" customHeight="1">
+      <c r="A245" s="10"/>
+      <c r="B245" s="10"/>
+      <c r="C245" s="46"/>
+      <c r="D245" s="47"/>
+      <c r="E245" s="47"/>
+      <c r="F245" s="47"/>
+      <c r="G245" s="48"/>
+      <c r="H245" s="46"/>
+      <c r="I245" s="47"/>
+      <c r="J245" s="47"/>
+      <c r="K245" s="47"/>
+      <c r="L245" s="47"/>
+      <c r="M245" s="48"/>
+      <c r="N245" s="42"/>
+      <c r="O245" s="43"/>
+      <c r="P245" s="44"/>
+      <c r="Q245" s="10"/>
+    </row>
+    <row r="246" spans="1:17" ht="30" customHeight="1">
+      <c r="A246" s="10"/>
+      <c r="B246" s="10"/>
+      <c r="C246" s="72"/>
+      <c r="D246" s="73"/>
+      <c r="E246" s="73"/>
+      <c r="F246" s="73"/>
+      <c r="G246" s="74"/>
+      <c r="H246" s="46"/>
+      <c r="I246" s="47"/>
+      <c r="J246" s="47"/>
+      <c r="K246" s="47"/>
+      <c r="L246" s="47"/>
+      <c r="M246" s="48"/>
+      <c r="N246" s="42"/>
+      <c r="O246" s="43"/>
+      <c r="P246" s="44"/>
+      <c r="Q246" s="10"/>
+    </row>
+    <row r="247" spans="1:17" ht="30" customHeight="1">
+      <c r="A247" s="10"/>
+      <c r="B247" s="10"/>
+      <c r="C247" s="46"/>
+      <c r="D247" s="47"/>
+      <c r="E247" s="47"/>
+      <c r="F247" s="47"/>
+      <c r="G247" s="48"/>
+      <c r="H247" s="46"/>
+      <c r="I247" s="47"/>
+      <c r="J247" s="47"/>
+      <c r="K247" s="47"/>
+      <c r="L247" s="47"/>
+      <c r="M247" s="48"/>
+      <c r="N247" s="42"/>
+      <c r="O247" s="43"/>
+      <c r="P247" s="44"/>
+      <c r="Q247" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="740">
-    <mergeCell ref="C230:G230"/>
-    <mergeCell ref="H230:M230"/>
-    <mergeCell ref="N230:P230"/>
-    <mergeCell ref="C227:G227"/>
-    <mergeCell ref="H227:M227"/>
-    <mergeCell ref="N227:P227"/>
-    <mergeCell ref="C228:G228"/>
-    <mergeCell ref="H228:M228"/>
-    <mergeCell ref="N228:P228"/>
-    <mergeCell ref="C229:G229"/>
-    <mergeCell ref="H229:M229"/>
-    <mergeCell ref="N229:P229"/>
-    <mergeCell ref="C224:G224"/>
-    <mergeCell ref="H224:M224"/>
-    <mergeCell ref="N224:P224"/>
-    <mergeCell ref="C225:G225"/>
-    <mergeCell ref="H225:M225"/>
-    <mergeCell ref="N225:P225"/>
-    <mergeCell ref="C226:G226"/>
-    <mergeCell ref="H226:M226"/>
-    <mergeCell ref="N226:P226"/>
-    <mergeCell ref="C221:G221"/>
-    <mergeCell ref="H221:M221"/>
-    <mergeCell ref="N221:P221"/>
-    <mergeCell ref="C222:G222"/>
-    <mergeCell ref="H222:M222"/>
-    <mergeCell ref="N222:P222"/>
-    <mergeCell ref="C223:G223"/>
-    <mergeCell ref="H223:M223"/>
-    <mergeCell ref="N223:P223"/>
-    <mergeCell ref="C218:G218"/>
-    <mergeCell ref="H218:M218"/>
-    <mergeCell ref="N218:P218"/>
-    <mergeCell ref="C219:G219"/>
-    <mergeCell ref="H219:M219"/>
-    <mergeCell ref="N219:P219"/>
-    <mergeCell ref="C220:G220"/>
-    <mergeCell ref="H220:M220"/>
-    <mergeCell ref="N220:P220"/>
-    <mergeCell ref="C215:G215"/>
-    <mergeCell ref="H215:M215"/>
-    <mergeCell ref="N215:P215"/>
-    <mergeCell ref="C216:G216"/>
-    <mergeCell ref="H216:M216"/>
-    <mergeCell ref="N216:P216"/>
-    <mergeCell ref="C217:G217"/>
-    <mergeCell ref="H217:M217"/>
-    <mergeCell ref="N217:P217"/>
-    <mergeCell ref="C212:G212"/>
-    <mergeCell ref="H212:M212"/>
-    <mergeCell ref="N212:P212"/>
-    <mergeCell ref="C213:G213"/>
-    <mergeCell ref="H213:M213"/>
-    <mergeCell ref="N213:P213"/>
-    <mergeCell ref="C214:G214"/>
-    <mergeCell ref="H214:M214"/>
-    <mergeCell ref="N214:P214"/>
-    <mergeCell ref="C209:G209"/>
-    <mergeCell ref="H209:M209"/>
-    <mergeCell ref="N209:P209"/>
-    <mergeCell ref="C210:G210"/>
-    <mergeCell ref="H210:M210"/>
-    <mergeCell ref="N210:P210"/>
-    <mergeCell ref="C211:G211"/>
-    <mergeCell ref="H211:M211"/>
-    <mergeCell ref="N211:P211"/>
-    <mergeCell ref="C206:G206"/>
-    <mergeCell ref="H206:M206"/>
-    <mergeCell ref="N206:P206"/>
-    <mergeCell ref="C207:G207"/>
-    <mergeCell ref="H207:M207"/>
-    <mergeCell ref="N207:P207"/>
-    <mergeCell ref="C208:G208"/>
-    <mergeCell ref="H208:M208"/>
-    <mergeCell ref="N208:P208"/>
-    <mergeCell ref="C203:G203"/>
-    <mergeCell ref="H203:M203"/>
-    <mergeCell ref="N203:P203"/>
-    <mergeCell ref="C204:G204"/>
-    <mergeCell ref="H204:M204"/>
-    <mergeCell ref="N204:P204"/>
-    <mergeCell ref="C205:G205"/>
-    <mergeCell ref="H205:M205"/>
-    <mergeCell ref="N205:P205"/>
-    <mergeCell ref="C200:G200"/>
-    <mergeCell ref="H200:M200"/>
-    <mergeCell ref="N200:P200"/>
-    <mergeCell ref="C201:G201"/>
-    <mergeCell ref="H201:M201"/>
-    <mergeCell ref="N201:P201"/>
-    <mergeCell ref="C202:G202"/>
-    <mergeCell ref="H202:M202"/>
-    <mergeCell ref="N202:P202"/>
-    <mergeCell ref="C197:G197"/>
-    <mergeCell ref="H197:M197"/>
-    <mergeCell ref="N197:P197"/>
-    <mergeCell ref="C198:G198"/>
-    <mergeCell ref="H198:M198"/>
-    <mergeCell ref="N198:P198"/>
-    <mergeCell ref="C199:G199"/>
-    <mergeCell ref="H199:M199"/>
-    <mergeCell ref="N199:P199"/>
-    <mergeCell ref="C194:G194"/>
-    <mergeCell ref="H194:M194"/>
-    <mergeCell ref="N194:P194"/>
-    <mergeCell ref="C195:G195"/>
-    <mergeCell ref="H195:M195"/>
-    <mergeCell ref="N195:P195"/>
-    <mergeCell ref="C196:G196"/>
-    <mergeCell ref="H196:M196"/>
-    <mergeCell ref="N196:P196"/>
-    <mergeCell ref="C191:G191"/>
-    <mergeCell ref="H191:M191"/>
-    <mergeCell ref="N191:P191"/>
-    <mergeCell ref="C192:G192"/>
-    <mergeCell ref="H192:M192"/>
-    <mergeCell ref="N192:P192"/>
-    <mergeCell ref="C193:G193"/>
-    <mergeCell ref="H193:M193"/>
-    <mergeCell ref="N193:P193"/>
-    <mergeCell ref="C188:G188"/>
-    <mergeCell ref="H188:M188"/>
-    <mergeCell ref="N188:P188"/>
-    <mergeCell ref="C189:G189"/>
-    <mergeCell ref="H189:M189"/>
-    <mergeCell ref="N189:P189"/>
-    <mergeCell ref="C190:G190"/>
-    <mergeCell ref="H190:M190"/>
-    <mergeCell ref="N190:P190"/>
-    <mergeCell ref="C185:G185"/>
-    <mergeCell ref="H185:M185"/>
-    <mergeCell ref="N185:P185"/>
-    <mergeCell ref="C186:G186"/>
-    <mergeCell ref="H186:M186"/>
-    <mergeCell ref="N186:P186"/>
-    <mergeCell ref="C187:G187"/>
-    <mergeCell ref="H187:M187"/>
-    <mergeCell ref="N187:P187"/>
-    <mergeCell ref="C182:G182"/>
-    <mergeCell ref="H182:M182"/>
-    <mergeCell ref="N182:P182"/>
-    <mergeCell ref="C183:G183"/>
-    <mergeCell ref="H183:M183"/>
-    <mergeCell ref="N183:P183"/>
-    <mergeCell ref="C184:G184"/>
-    <mergeCell ref="H184:M184"/>
-    <mergeCell ref="N184:P184"/>
-    <mergeCell ref="C179:G179"/>
-    <mergeCell ref="H179:M179"/>
-    <mergeCell ref="N179:P179"/>
-    <mergeCell ref="C180:G180"/>
-    <mergeCell ref="H180:M180"/>
-    <mergeCell ref="N180:P180"/>
-    <mergeCell ref="C181:G181"/>
-    <mergeCell ref="H181:M181"/>
-    <mergeCell ref="N181:P181"/>
-    <mergeCell ref="C176:G176"/>
-    <mergeCell ref="H176:M176"/>
-    <mergeCell ref="N176:P176"/>
-    <mergeCell ref="C177:G177"/>
-    <mergeCell ref="H177:M177"/>
-    <mergeCell ref="N177:P177"/>
-    <mergeCell ref="C178:G178"/>
-    <mergeCell ref="H178:M178"/>
-    <mergeCell ref="N178:P178"/>
-    <mergeCell ref="C173:G173"/>
-    <mergeCell ref="H173:M173"/>
-    <mergeCell ref="N173:P173"/>
-    <mergeCell ref="C174:G174"/>
-    <mergeCell ref="H174:M174"/>
-    <mergeCell ref="N174:P174"/>
-    <mergeCell ref="C175:G175"/>
-    <mergeCell ref="H175:M175"/>
-    <mergeCell ref="N175:P175"/>
-    <mergeCell ref="C170:G170"/>
-    <mergeCell ref="H170:M170"/>
-    <mergeCell ref="N170:P170"/>
-    <mergeCell ref="C171:G171"/>
-    <mergeCell ref="H171:M171"/>
-    <mergeCell ref="N171:P171"/>
-    <mergeCell ref="C172:G172"/>
-    <mergeCell ref="H172:M172"/>
-    <mergeCell ref="N172:P172"/>
-    <mergeCell ref="C167:G167"/>
-    <mergeCell ref="H167:M167"/>
-    <mergeCell ref="N167:P167"/>
-    <mergeCell ref="C168:G168"/>
-    <mergeCell ref="H168:M168"/>
-    <mergeCell ref="N168:P168"/>
-    <mergeCell ref="C169:G169"/>
-    <mergeCell ref="H169:M169"/>
-    <mergeCell ref="N169:P169"/>
-    <mergeCell ref="C164:G164"/>
-    <mergeCell ref="H164:M164"/>
-    <mergeCell ref="N164:P164"/>
-    <mergeCell ref="C165:G165"/>
-    <mergeCell ref="H165:M165"/>
-    <mergeCell ref="N165:P165"/>
-    <mergeCell ref="C166:G166"/>
-    <mergeCell ref="H166:M166"/>
-    <mergeCell ref="N166:P166"/>
-    <mergeCell ref="C161:G161"/>
-    <mergeCell ref="H161:M161"/>
-    <mergeCell ref="N161:P161"/>
-    <mergeCell ref="C162:G162"/>
-    <mergeCell ref="H162:M162"/>
-    <mergeCell ref="N162:P162"/>
-    <mergeCell ref="C163:G163"/>
-    <mergeCell ref="H163:M163"/>
-    <mergeCell ref="N163:P163"/>
-    <mergeCell ref="C158:G158"/>
-    <mergeCell ref="H158:M158"/>
-    <mergeCell ref="N158:P158"/>
-    <mergeCell ref="C159:G159"/>
-    <mergeCell ref="H159:M159"/>
-    <mergeCell ref="N159:P159"/>
-    <mergeCell ref="C160:G160"/>
-    <mergeCell ref="H160:M160"/>
-    <mergeCell ref="N160:P160"/>
-    <mergeCell ref="C155:G155"/>
-    <mergeCell ref="H155:M155"/>
-    <mergeCell ref="N155:P155"/>
-    <mergeCell ref="C156:G156"/>
-    <mergeCell ref="H156:M156"/>
-    <mergeCell ref="N156:P156"/>
-    <mergeCell ref="C157:G157"/>
-    <mergeCell ref="H157:M157"/>
-    <mergeCell ref="N157:P157"/>
-    <mergeCell ref="C152:G152"/>
-    <mergeCell ref="H152:M152"/>
-    <mergeCell ref="N152:P152"/>
-    <mergeCell ref="C153:G153"/>
-    <mergeCell ref="H153:M153"/>
-    <mergeCell ref="N153:P153"/>
-    <mergeCell ref="C154:G154"/>
-    <mergeCell ref="H154:M154"/>
-    <mergeCell ref="N154:P154"/>
-    <mergeCell ref="C149:G149"/>
-    <mergeCell ref="H149:M149"/>
-    <mergeCell ref="N149:P149"/>
-    <mergeCell ref="C150:G150"/>
-    <mergeCell ref="H150:M150"/>
-    <mergeCell ref="N150:P150"/>
-    <mergeCell ref="C151:G151"/>
-    <mergeCell ref="H151:M151"/>
-    <mergeCell ref="N151:P151"/>
-    <mergeCell ref="C146:G146"/>
-    <mergeCell ref="H146:M146"/>
-    <mergeCell ref="N146:P146"/>
-    <mergeCell ref="C147:G147"/>
-    <mergeCell ref="H147:M147"/>
-    <mergeCell ref="N147:P147"/>
-    <mergeCell ref="C148:G148"/>
-    <mergeCell ref="H148:M148"/>
-    <mergeCell ref="N148:P148"/>
-    <mergeCell ref="C143:G143"/>
-    <mergeCell ref="H143:M143"/>
-    <mergeCell ref="N143:P143"/>
-    <mergeCell ref="C144:G144"/>
-    <mergeCell ref="H144:M144"/>
-    <mergeCell ref="N144:P144"/>
-    <mergeCell ref="C145:G145"/>
-    <mergeCell ref="H145:M145"/>
-    <mergeCell ref="N145:P145"/>
-    <mergeCell ref="C140:G140"/>
-    <mergeCell ref="H140:M140"/>
-    <mergeCell ref="N140:P140"/>
-    <mergeCell ref="C141:G141"/>
-    <mergeCell ref="H141:M141"/>
-    <mergeCell ref="N141:P141"/>
-    <mergeCell ref="C142:G142"/>
-    <mergeCell ref="H142:M142"/>
-    <mergeCell ref="N142:P142"/>
-    <mergeCell ref="C137:G137"/>
-    <mergeCell ref="H137:M137"/>
-    <mergeCell ref="N137:P137"/>
-    <mergeCell ref="C138:G138"/>
-    <mergeCell ref="H138:M138"/>
-    <mergeCell ref="N138:P138"/>
-    <mergeCell ref="C139:G139"/>
-    <mergeCell ref="H139:M139"/>
-    <mergeCell ref="N139:P139"/>
-    <mergeCell ref="C134:G134"/>
-    <mergeCell ref="H134:M134"/>
-    <mergeCell ref="N134:P134"/>
-    <mergeCell ref="C135:G135"/>
-    <mergeCell ref="H135:M135"/>
-    <mergeCell ref="N135:P135"/>
-    <mergeCell ref="C136:G136"/>
-    <mergeCell ref="H136:M136"/>
-    <mergeCell ref="N136:P136"/>
-    <mergeCell ref="C131:G131"/>
-    <mergeCell ref="H131:M131"/>
-    <mergeCell ref="N131:P131"/>
-    <mergeCell ref="C132:G132"/>
-    <mergeCell ref="H132:M132"/>
-    <mergeCell ref="N132:P132"/>
-    <mergeCell ref="C133:G133"/>
-    <mergeCell ref="H133:M133"/>
-    <mergeCell ref="N133:P133"/>
-    <mergeCell ref="C128:G128"/>
-    <mergeCell ref="H128:M128"/>
-    <mergeCell ref="N128:P128"/>
-    <mergeCell ref="C129:G129"/>
-    <mergeCell ref="H129:M129"/>
-    <mergeCell ref="N129:P129"/>
-    <mergeCell ref="C130:G130"/>
-    <mergeCell ref="H130:M130"/>
-    <mergeCell ref="N130:P130"/>
-    <mergeCell ref="C125:G125"/>
-    <mergeCell ref="H125:M125"/>
-    <mergeCell ref="N125:P125"/>
-    <mergeCell ref="C126:G126"/>
-    <mergeCell ref="H126:M126"/>
-    <mergeCell ref="N126:P126"/>
-    <mergeCell ref="C127:G127"/>
-    <mergeCell ref="H127:M127"/>
-    <mergeCell ref="N127:P127"/>
+  <mergeCells count="791">
     <mergeCell ref="C122:G122"/>
     <mergeCell ref="H122:M122"/>
     <mergeCell ref="N122:P122"/>
@@ -8659,6 +8777,384 @@
     <mergeCell ref="C115:G115"/>
     <mergeCell ref="H115:M115"/>
     <mergeCell ref="N115:P115"/>
+    <mergeCell ref="C247:G247"/>
+    <mergeCell ref="H247:M247"/>
+    <mergeCell ref="N247:P247"/>
+    <mergeCell ref="C244:G244"/>
+    <mergeCell ref="H244:M244"/>
+    <mergeCell ref="N244:P244"/>
+    <mergeCell ref="C245:G245"/>
+    <mergeCell ref="H245:M245"/>
+    <mergeCell ref="N245:P245"/>
+    <mergeCell ref="C246:G246"/>
+    <mergeCell ref="H246:M246"/>
+    <mergeCell ref="N246:P246"/>
+    <mergeCell ref="C241:G241"/>
+    <mergeCell ref="H241:M241"/>
+    <mergeCell ref="N241:P241"/>
+    <mergeCell ref="C242:G242"/>
+    <mergeCell ref="H242:M242"/>
+    <mergeCell ref="N242:P242"/>
+    <mergeCell ref="C243:G243"/>
+    <mergeCell ref="H243:M243"/>
+    <mergeCell ref="N243:P243"/>
+    <mergeCell ref="C238:G238"/>
+    <mergeCell ref="H238:M238"/>
+    <mergeCell ref="N238:P238"/>
+    <mergeCell ref="C239:G239"/>
+    <mergeCell ref="H239:M239"/>
+    <mergeCell ref="N239:P239"/>
+    <mergeCell ref="C240:G240"/>
+    <mergeCell ref="H240:M240"/>
+    <mergeCell ref="N240:P240"/>
+    <mergeCell ref="C235:G235"/>
+    <mergeCell ref="H235:M235"/>
+    <mergeCell ref="N235:P235"/>
+    <mergeCell ref="C236:G236"/>
+    <mergeCell ref="H236:M236"/>
+    <mergeCell ref="N236:P236"/>
+    <mergeCell ref="C237:G237"/>
+    <mergeCell ref="H237:M237"/>
+    <mergeCell ref="N237:P237"/>
+    <mergeCell ref="C232:G232"/>
+    <mergeCell ref="H232:M232"/>
+    <mergeCell ref="N232:P232"/>
+    <mergeCell ref="C233:G233"/>
+    <mergeCell ref="H233:M233"/>
+    <mergeCell ref="N233:P233"/>
+    <mergeCell ref="C234:G234"/>
+    <mergeCell ref="H234:M234"/>
+    <mergeCell ref="N234:P234"/>
+    <mergeCell ref="C229:G229"/>
+    <mergeCell ref="H229:M229"/>
+    <mergeCell ref="N229:P229"/>
+    <mergeCell ref="C230:G230"/>
+    <mergeCell ref="H230:M230"/>
+    <mergeCell ref="N230:P230"/>
+    <mergeCell ref="C231:G231"/>
+    <mergeCell ref="H231:M231"/>
+    <mergeCell ref="N231:P231"/>
+    <mergeCell ref="C226:G226"/>
+    <mergeCell ref="H226:M226"/>
+    <mergeCell ref="N226:P226"/>
+    <mergeCell ref="C227:G227"/>
+    <mergeCell ref="H227:M227"/>
+    <mergeCell ref="N227:P227"/>
+    <mergeCell ref="C228:G228"/>
+    <mergeCell ref="H228:M228"/>
+    <mergeCell ref="N228:P228"/>
+    <mergeCell ref="C223:G223"/>
+    <mergeCell ref="H223:M223"/>
+    <mergeCell ref="N223:P223"/>
+    <mergeCell ref="C224:G224"/>
+    <mergeCell ref="H224:M224"/>
+    <mergeCell ref="N224:P224"/>
+    <mergeCell ref="C225:G225"/>
+    <mergeCell ref="H225:M225"/>
+    <mergeCell ref="N225:P225"/>
+    <mergeCell ref="C220:G220"/>
+    <mergeCell ref="H220:M220"/>
+    <mergeCell ref="N220:P220"/>
+    <mergeCell ref="C221:G221"/>
+    <mergeCell ref="H221:M221"/>
+    <mergeCell ref="N221:P221"/>
+    <mergeCell ref="C222:G222"/>
+    <mergeCell ref="H222:M222"/>
+    <mergeCell ref="N222:P222"/>
+    <mergeCell ref="C217:G217"/>
+    <mergeCell ref="H217:M217"/>
+    <mergeCell ref="N217:P217"/>
+    <mergeCell ref="C218:G218"/>
+    <mergeCell ref="H218:M218"/>
+    <mergeCell ref="N218:P218"/>
+    <mergeCell ref="C219:G219"/>
+    <mergeCell ref="H219:M219"/>
+    <mergeCell ref="N219:P219"/>
+    <mergeCell ref="C214:G214"/>
+    <mergeCell ref="H214:M214"/>
+    <mergeCell ref="N214:P214"/>
+    <mergeCell ref="C215:G215"/>
+    <mergeCell ref="H215:M215"/>
+    <mergeCell ref="N215:P215"/>
+    <mergeCell ref="C216:G216"/>
+    <mergeCell ref="H216:M216"/>
+    <mergeCell ref="N216:P216"/>
+    <mergeCell ref="C211:G211"/>
+    <mergeCell ref="H211:M211"/>
+    <mergeCell ref="N211:P211"/>
+    <mergeCell ref="C212:G212"/>
+    <mergeCell ref="H212:M212"/>
+    <mergeCell ref="N212:P212"/>
+    <mergeCell ref="C213:G213"/>
+    <mergeCell ref="H213:M213"/>
+    <mergeCell ref="N213:P213"/>
+    <mergeCell ref="C208:G208"/>
+    <mergeCell ref="H208:M208"/>
+    <mergeCell ref="N208:P208"/>
+    <mergeCell ref="C209:G209"/>
+    <mergeCell ref="H209:M209"/>
+    <mergeCell ref="N209:P209"/>
+    <mergeCell ref="C210:G210"/>
+    <mergeCell ref="H210:M210"/>
+    <mergeCell ref="N210:P210"/>
+    <mergeCell ref="C205:G205"/>
+    <mergeCell ref="H205:M205"/>
+    <mergeCell ref="N205:P205"/>
+    <mergeCell ref="C206:G206"/>
+    <mergeCell ref="H206:M206"/>
+    <mergeCell ref="N206:P206"/>
+    <mergeCell ref="C207:G207"/>
+    <mergeCell ref="H207:M207"/>
+    <mergeCell ref="N207:P207"/>
+    <mergeCell ref="C202:G202"/>
+    <mergeCell ref="H202:M202"/>
+    <mergeCell ref="N202:P202"/>
+    <mergeCell ref="C203:G203"/>
+    <mergeCell ref="H203:M203"/>
+    <mergeCell ref="N203:P203"/>
+    <mergeCell ref="C204:G204"/>
+    <mergeCell ref="H204:M204"/>
+    <mergeCell ref="N204:P204"/>
+    <mergeCell ref="C199:G199"/>
+    <mergeCell ref="H199:M199"/>
+    <mergeCell ref="N199:P199"/>
+    <mergeCell ref="C200:G200"/>
+    <mergeCell ref="H200:M200"/>
+    <mergeCell ref="N200:P200"/>
+    <mergeCell ref="C201:G201"/>
+    <mergeCell ref="H201:M201"/>
+    <mergeCell ref="N201:P201"/>
+    <mergeCell ref="C196:G196"/>
+    <mergeCell ref="H196:M196"/>
+    <mergeCell ref="N196:P196"/>
+    <mergeCell ref="C197:G197"/>
+    <mergeCell ref="H197:M197"/>
+    <mergeCell ref="N197:P197"/>
+    <mergeCell ref="C198:G198"/>
+    <mergeCell ref="H198:M198"/>
+    <mergeCell ref="N198:P198"/>
+    <mergeCell ref="C193:G193"/>
+    <mergeCell ref="H193:M193"/>
+    <mergeCell ref="N193:P193"/>
+    <mergeCell ref="C194:G194"/>
+    <mergeCell ref="H194:M194"/>
+    <mergeCell ref="N194:P194"/>
+    <mergeCell ref="C195:G195"/>
+    <mergeCell ref="H195:M195"/>
+    <mergeCell ref="N195:P195"/>
+    <mergeCell ref="C190:G190"/>
+    <mergeCell ref="H190:M190"/>
+    <mergeCell ref="N190:P190"/>
+    <mergeCell ref="C191:G191"/>
+    <mergeCell ref="H191:M191"/>
+    <mergeCell ref="N191:P191"/>
+    <mergeCell ref="C192:G192"/>
+    <mergeCell ref="H192:M192"/>
+    <mergeCell ref="N192:P192"/>
+    <mergeCell ref="C187:G187"/>
+    <mergeCell ref="H187:M187"/>
+    <mergeCell ref="N187:P187"/>
+    <mergeCell ref="C188:G188"/>
+    <mergeCell ref="H188:M188"/>
+    <mergeCell ref="N188:P188"/>
+    <mergeCell ref="C189:G189"/>
+    <mergeCell ref="H189:M189"/>
+    <mergeCell ref="N189:P189"/>
+    <mergeCell ref="C184:G184"/>
+    <mergeCell ref="H184:M184"/>
+    <mergeCell ref="N184:P184"/>
+    <mergeCell ref="C185:G185"/>
+    <mergeCell ref="H185:M185"/>
+    <mergeCell ref="N185:P185"/>
+    <mergeCell ref="C186:G186"/>
+    <mergeCell ref="H186:M186"/>
+    <mergeCell ref="N186:P186"/>
+    <mergeCell ref="C181:G181"/>
+    <mergeCell ref="H181:M181"/>
+    <mergeCell ref="N181:P181"/>
+    <mergeCell ref="C182:G182"/>
+    <mergeCell ref="H182:M182"/>
+    <mergeCell ref="N182:P182"/>
+    <mergeCell ref="C183:G183"/>
+    <mergeCell ref="H183:M183"/>
+    <mergeCell ref="N183:P183"/>
+    <mergeCell ref="C178:G178"/>
+    <mergeCell ref="H178:M178"/>
+    <mergeCell ref="N178:P178"/>
+    <mergeCell ref="C179:G179"/>
+    <mergeCell ref="H179:M179"/>
+    <mergeCell ref="N179:P179"/>
+    <mergeCell ref="C180:G180"/>
+    <mergeCell ref="H180:M180"/>
+    <mergeCell ref="N180:P180"/>
+    <mergeCell ref="C175:G175"/>
+    <mergeCell ref="H175:M175"/>
+    <mergeCell ref="N175:P175"/>
+    <mergeCell ref="C176:G176"/>
+    <mergeCell ref="H176:M176"/>
+    <mergeCell ref="N176:P176"/>
+    <mergeCell ref="C177:G177"/>
+    <mergeCell ref="H177:M177"/>
+    <mergeCell ref="N177:P177"/>
+    <mergeCell ref="C172:G172"/>
+    <mergeCell ref="H172:M172"/>
+    <mergeCell ref="N172:P172"/>
+    <mergeCell ref="C173:G173"/>
+    <mergeCell ref="H173:M173"/>
+    <mergeCell ref="N173:P173"/>
+    <mergeCell ref="C174:G174"/>
+    <mergeCell ref="H174:M174"/>
+    <mergeCell ref="N174:P174"/>
+    <mergeCell ref="C169:G169"/>
+    <mergeCell ref="H169:M169"/>
+    <mergeCell ref="N169:P169"/>
+    <mergeCell ref="C170:G170"/>
+    <mergeCell ref="H170:M170"/>
+    <mergeCell ref="N170:P170"/>
+    <mergeCell ref="C171:G171"/>
+    <mergeCell ref="H171:M171"/>
+    <mergeCell ref="N171:P171"/>
+    <mergeCell ref="C166:G166"/>
+    <mergeCell ref="H166:M166"/>
+    <mergeCell ref="N166:P166"/>
+    <mergeCell ref="C167:G167"/>
+    <mergeCell ref="H167:M167"/>
+    <mergeCell ref="N167:P167"/>
+    <mergeCell ref="C168:G168"/>
+    <mergeCell ref="H168:M168"/>
+    <mergeCell ref="N168:P168"/>
+    <mergeCell ref="C163:G163"/>
+    <mergeCell ref="H163:M163"/>
+    <mergeCell ref="N163:P163"/>
+    <mergeCell ref="C164:G164"/>
+    <mergeCell ref="H164:M164"/>
+    <mergeCell ref="N164:P164"/>
+    <mergeCell ref="C165:G165"/>
+    <mergeCell ref="H165:M165"/>
+    <mergeCell ref="N165:P165"/>
+    <mergeCell ref="C160:G160"/>
+    <mergeCell ref="H160:M160"/>
+    <mergeCell ref="N160:P160"/>
+    <mergeCell ref="C161:G161"/>
+    <mergeCell ref="H161:M161"/>
+    <mergeCell ref="N161:P161"/>
+    <mergeCell ref="C162:G162"/>
+    <mergeCell ref="H162:M162"/>
+    <mergeCell ref="N162:P162"/>
+    <mergeCell ref="C157:G157"/>
+    <mergeCell ref="H157:M157"/>
+    <mergeCell ref="N157:P157"/>
+    <mergeCell ref="C158:G158"/>
+    <mergeCell ref="H158:M158"/>
+    <mergeCell ref="N158:P158"/>
+    <mergeCell ref="C159:G159"/>
+    <mergeCell ref="H159:M159"/>
+    <mergeCell ref="N159:P159"/>
+    <mergeCell ref="C154:G154"/>
+    <mergeCell ref="H154:M154"/>
+    <mergeCell ref="N154:P154"/>
+    <mergeCell ref="C155:G155"/>
+    <mergeCell ref="H155:M155"/>
+    <mergeCell ref="N155:P155"/>
+    <mergeCell ref="C156:G156"/>
+    <mergeCell ref="H156:M156"/>
+    <mergeCell ref="N156:P156"/>
+    <mergeCell ref="C151:G151"/>
+    <mergeCell ref="H151:M151"/>
+    <mergeCell ref="N151:P151"/>
+    <mergeCell ref="C152:G152"/>
+    <mergeCell ref="H152:M152"/>
+    <mergeCell ref="N152:P152"/>
+    <mergeCell ref="C153:G153"/>
+    <mergeCell ref="H153:M153"/>
+    <mergeCell ref="N153:P153"/>
+    <mergeCell ref="C148:G148"/>
+    <mergeCell ref="H148:M148"/>
+    <mergeCell ref="N148:P148"/>
+    <mergeCell ref="C149:G149"/>
+    <mergeCell ref="H149:M149"/>
+    <mergeCell ref="N149:P149"/>
+    <mergeCell ref="C150:G150"/>
+    <mergeCell ref="H150:M150"/>
+    <mergeCell ref="N150:P150"/>
+    <mergeCell ref="C145:G145"/>
+    <mergeCell ref="H145:M145"/>
+    <mergeCell ref="N145:P145"/>
+    <mergeCell ref="C146:G146"/>
+    <mergeCell ref="H146:M146"/>
+    <mergeCell ref="N146:P146"/>
+    <mergeCell ref="C147:G147"/>
+    <mergeCell ref="H147:M147"/>
+    <mergeCell ref="N147:P147"/>
+    <mergeCell ref="C142:G142"/>
+    <mergeCell ref="H142:M142"/>
+    <mergeCell ref="N142:P142"/>
+    <mergeCell ref="C143:G143"/>
+    <mergeCell ref="H143:M143"/>
+    <mergeCell ref="N143:P143"/>
+    <mergeCell ref="C144:G144"/>
+    <mergeCell ref="H144:M144"/>
+    <mergeCell ref="N144:P144"/>
+    <mergeCell ref="C139:G139"/>
+    <mergeCell ref="H139:M139"/>
+    <mergeCell ref="N139:P139"/>
+    <mergeCell ref="C140:G140"/>
+    <mergeCell ref="H140:M140"/>
+    <mergeCell ref="N140:P140"/>
+    <mergeCell ref="C141:G141"/>
+    <mergeCell ref="H141:M141"/>
+    <mergeCell ref="N141:P141"/>
+    <mergeCell ref="C136:G136"/>
+    <mergeCell ref="H136:M136"/>
+    <mergeCell ref="N136:P136"/>
+    <mergeCell ref="C137:G137"/>
+    <mergeCell ref="H137:M137"/>
+    <mergeCell ref="N137:P137"/>
+    <mergeCell ref="C138:G138"/>
+    <mergeCell ref="H138:M138"/>
+    <mergeCell ref="N138:P138"/>
+    <mergeCell ref="C133:G133"/>
+    <mergeCell ref="H133:M133"/>
+    <mergeCell ref="N133:P133"/>
+    <mergeCell ref="C134:G134"/>
+    <mergeCell ref="H134:M134"/>
+    <mergeCell ref="N134:P134"/>
+    <mergeCell ref="C135:G135"/>
+    <mergeCell ref="H135:M135"/>
+    <mergeCell ref="N135:P135"/>
+    <mergeCell ref="C130:G130"/>
+    <mergeCell ref="H130:M130"/>
+    <mergeCell ref="N130:P130"/>
+    <mergeCell ref="C131:G131"/>
+    <mergeCell ref="H131:M131"/>
+    <mergeCell ref="N131:P131"/>
+    <mergeCell ref="C132:G132"/>
+    <mergeCell ref="H132:M132"/>
+    <mergeCell ref="N132:P132"/>
+    <mergeCell ref="C127:G127"/>
+    <mergeCell ref="H127:M127"/>
+    <mergeCell ref="N127:P127"/>
+    <mergeCell ref="C128:G128"/>
+    <mergeCell ref="H128:M128"/>
+    <mergeCell ref="N128:P128"/>
+    <mergeCell ref="C129:G129"/>
+    <mergeCell ref="H129:M129"/>
+    <mergeCell ref="N129:P129"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="H107:M107"/>
+    <mergeCell ref="N107:P107"/>
+    <mergeCell ref="C125:G125"/>
+    <mergeCell ref="H125:M125"/>
+    <mergeCell ref="N125:P125"/>
+    <mergeCell ref="C126:G126"/>
+    <mergeCell ref="H126:M126"/>
+    <mergeCell ref="N126:P126"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="H108:M108"/>
+    <mergeCell ref="N108:P108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="H109:M109"/>
+    <mergeCell ref="N109:P109"/>
     <mergeCell ref="C110:G110"/>
     <mergeCell ref="H110:M110"/>
     <mergeCell ref="N110:P110"/>
@@ -8668,15 +9164,6 @@
     <mergeCell ref="C112:G112"/>
     <mergeCell ref="H112:M112"/>
     <mergeCell ref="N112:P112"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="H107:M107"/>
-    <mergeCell ref="N107:P107"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="H108:M108"/>
-    <mergeCell ref="N108:P108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="H109:M109"/>
-    <mergeCell ref="N109:P109"/>
     <mergeCell ref="C104:G104"/>
     <mergeCell ref="H104:M104"/>
     <mergeCell ref="N104:P104"/>
